--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.4%</t>
+          <t>423.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.1%</t>
+          <t>-617.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-108.0%</t>
+          <t>-108.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.7%</t>
+          <t>-323.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-110.1%</t>
+          <t>-106.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>112.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>102.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.447260648070199</v>
+        <v>-3.364319676792658</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.244996090502059</v>
+        <v>1.278172479013076</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8852710322317625</v>
+        <v>0.9190609009675099</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.155419393382944</v>
+        <v>3.175693314624392</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.403057810984299</v>
+        <v>-3.320116839706757</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.268556827864257</v>
+        <v>1.301733216375274</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.929473869317663</v>
+        <v>0.9632637380534104</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.187820698162321</v>
+        <v>3.20809461940377</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.410617476821346</v>
+        <v>-3.327676505543804</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.263942961998685</v>
+        <v>1.297119350509702</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9842772733274823</v>
+        <v>1.01806714206323</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.219112741037461</v>
+        <v>3.239386662278909</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.252326059282074</v>
+        <v>-3.169385088004532</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.378507294197434</v>
+        <v>1.411683682708451</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9842772733274823</v>
+        <v>1.01806714206323</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.2703605062205</v>
+        <v>3.290634427461949</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.044684055647597</v>
+        <v>-2.961743084370056</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.460004800245478</v>
+        <v>1.493181188756495</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.191919276961958</v>
+        <v>1.225709145697706</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.393386412995439</v>
+        <v>3.413660334236888</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.993651962925069</v>
+        <v>-2.910710991647528</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.475365865572759</v>
+        <v>1.508542254083776</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.242951369684486</v>
+        <v>1.276741238420234</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.418953896867226</v>
+        <v>3.439227818108674</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.928427781797863</v>
+        <v>-2.845486810520322</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.518642942116346</v>
+        <v>1.551819330627363</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.308175550811692</v>
+        <v>1.341965419547439</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.475275809636254</v>
+        <v>3.495549730877702</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.89100076172673</v>
+        <v>-2.808059790449188</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.52957472244408</v>
+        <v>1.562751110955097</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.313427088840874</v>
+        <v>1.347216957576621</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.474387704753044</v>
+        <v>3.494661625994492</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.911112417761438</v>
+        <v>-2.828171446483896</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.522786852361437</v>
+        <v>1.555963240872454</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.324454433838293</v>
+        <v>1.35824430257404</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.482260904082735</v>
+        <v>3.502534825324184</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.882699154661554</v>
+        <v>-2.799758183384013</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.694709928622601</v>
+        <v>1.727886317133618</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.265478871091864</v>
+        <v>1.299268739827611</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.607433337456089</v>
+        <v>3.627707258697537</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.807916893636542</v>
+        <v>-2.724975922359</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.844735742250424</v>
+        <v>1.87791213076144</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.340261132116877</v>
+        <v>1.374051000852624</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.772415603288914</v>
+        <v>3.792689524530362</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.781832809372734</v>
+        <v>-2.698891838095192</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.846877351969806</v>
+        <v>1.880053740480822</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.340261132116877</v>
+        <v>1.374051000852624</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.764123579302773</v>
+        <v>3.784397500544221</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.693954896263613</v>
+        <v>-2.611013924986072</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.880221712797233</v>
+        <v>1.91339810130825</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.456186774540228</v>
+        <v>1.489976643275975</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.831872160340563</v>
+        <v>3.852146081582011</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.68506243487033</v>
+        <v>-2.602121463592788</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.901333103081338</v>
+        <v>1.934509491592355</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.456186774540228</v>
+        <v>1.489976643275975</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.849426566067354</v>
+        <v>3.869700487308803</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.853538551840208</v>
+        <v>-2.770597580562666</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.825797703697971</v>
+        <v>1.858974092208988</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.428238938823647</v>
+        <v>1.462028807559394</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.824512912041989</v>
+        <v>3.844786833283438</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.407282359210768</v>
+        <v>-2.324341387933226</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.985569877937609</v>
+        <v>2.018746266448626</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.333520269154014</v>
+        <v>1.367310137889762</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.748951407428072</v>
+        <v>3.76922532866952</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.384561255527615</v>
+        <v>-2.301620284250073</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.985322341907774</v>
+        <v>2.018498730418791</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.333520269154014</v>
+        <v>1.367310137889762</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.739615429924976</v>
+        <v>3.759889351166425</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.513763068821658</v>
+        <v>-2.430822097544116</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.092547742441326</v>
+        <v>2.125724130952343</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.204318455859972</v>
+        <v>1.238108324595719</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.82100046779972</v>
+        <v>3.841274389041168</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.539637467295683</v>
+        <v>-2.456696496018142</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.119275805545363</v>
+        <v>2.152452194056379</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.249230064571713</v>
+        <v>1.283019933307461</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.885025255520411</v>
+        <v>3.90529917676186</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.53258277708051</v>
+        <v>-2.449641805802968</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.118773037620977</v>
+        <v>2.151949426131994</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.256284754786887</v>
+        <v>1.290074623522634</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.885933425639061</v>
+        <v>3.906207346880509</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.505631552754022</v>
+        <v>-2.42269058147648</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.139559680996314</v>
+        <v>2.172736069507331</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.271165100814606</v>
+        <v>1.304954969550354</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.904867786900434</v>
+        <v>3.925141708141882</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.527175780584809</v>
+        <v>-2.444234809307267</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.315045122008959</v>
+        <v>2.348221510519976</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.271165100814606</v>
+        <v>1.304954969550354</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.088970919045393</v>
+        <v>4.109244840286842</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.549583898389681</v>
+        <v>-2.466642927112139</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.298198569790003</v>
+        <v>2.33137495830102</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.271165100814606</v>
+        <v>1.304954969550354</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.081087613948386</v>
+        <v>4.101361535189835</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.577808133967281</v>
+        <v>-2.49486716268974</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.2889628751086</v>
+        <v>2.322139263619617</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.289141853265915</v>
+        <v>1.322931722001662</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.093927664968809</v>
+        <v>4.114201586210258</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.587249059855811</v>
+        <v>-2.50430808857827</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.341440222475036</v>
+        <v>2.374616610986052</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.411568970809306</v>
+        <v>1.445358839545054</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.223637653216691</v>
+        <v>4.243911574458139</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.676125691024285</v>
+        <v>-2.593184719746743</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.308780664552947</v>
+        <v>2.341957053063964</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.322692339640832</v>
+        <v>1.35648220837658</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.173202769060908</v>
+        <v>4.193476690302356</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.752455668625191</v>
+        <v>-2.669514697347649</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.27636048640636</v>
+        <v>2.309536874917376</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.322692339640832</v>
+        <v>1.35648220837658</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.171314581954683</v>
+        <v>4.191588503196131</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.846119613302732</v>
+        <v>-2.763178642025191</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.233715138138206</v>
+        <v>2.266891526649222</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.229028394963291</v>
+        <v>1.262818263699038</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10993644475102</v>
+        <v>4.130210365992469</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.007688038829988</v>
+        <v>-2.924747067552446</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.167521778137456</v>
+        <v>2.200698166648473</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.102245471165411</v>
+        <v>1.136035339901159</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.032300700682445</v>
+        <v>4.052574621923894</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.115988700700107</v>
+        <v>-3.033047729422565</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.137274920255327</v>
+        <v>2.170451308766343</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.102245471165411</v>
+        <v>1.136035339901159</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.045374107548364</v>
+        <v>4.065648028789812</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.133792672420851</v>
+        <v>-3.050851701143309</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.122158528349969</v>
+        <v>2.155334916860986</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.03171084826021</v>
+        <v>1.065500716995958</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.995058530588183</v>
+        <v>4.015332451829631</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.161693459530324</v>
+        <v>-3.078752488252782</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.109522254633182</v>
+        <v>2.142698643144199</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9971139241172757</v>
+        <v>1.030903792853023</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.972824417229424</v>
+        <v>3.993098338470872</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.284219562233218</v>
+        <v>-3.201278590955676</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.057276257529223</v>
+        <v>2.09045264604024</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8745878214143818</v>
+        <v>0.9083776901501293</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.896073199584887</v>
+        <v>3.916347120826335</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.514734058418807</v>
+        <v>-3.431793087141265</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.031776418645491</v>
+        <v>2.064952807156508</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6440733252287931</v>
+        <v>0.6778631939645405</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.824470461464037</v>
+        <v>3.844744382705485</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.863479143643251</v>
+        <v>-3.780538172365709</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.032590103557561</v>
+        <v>2.065766492068577</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.899533408114546</v>
+        <v>3.919807329355994</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.017465561419391</v>
+        <v>-3.934524590141849</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.039975805592745</v>
+        <v>2.073152194103761</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.968513677260185</v>
+        <v>3.988787598501633</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.966943657591725</v>
+        <v>-3.884002686314183</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.046235769243931</v>
+        <v>2.079412157754948</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.954564879380306</v>
+        <v>3.974838800621755</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.219418811599449</v>
+        <v>-4.136477840321907</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.957116196696256</v>
+        <v>1.990292585207273</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.96643536843572</v>
+        <v>3.986709289677169</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.512314568078861</v>
+        <v>-4.429373596801319</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.841168428623435</v>
+        <v>1.874344817134451</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.967645902954664</v>
+        <v>3.987919824196112</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.698978696213669</v>
+        <v>-4.616037724936128</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.770624519596833</v>
+        <v>1.80380090810785</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5085864004853354</v>
+        <v>0.5423762692210828</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.95572426268725</v>
+        <v>3.975998183928698</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.844999383127631</v>
+        <v>-4.76205841185009</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.707294097567437</v>
+        <v>1.740470486078454</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5332931774272258</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.945352260347125</v>
+        <v>3.965626181588573</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.936713392237216</v>
+        <v>-4.853772420959675</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.832812550622648</v>
+        <v>1.865988939133664</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5332931774272258</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.107556317046169</v>
+        <v>4.127830238287618</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.968365051297186</v>
+        <v>-4.885424080019645</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.814998524962474</v>
+        <v>1.84817491347349</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4943348514470383</v>
+        <v>0.5281247201827857</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.099301880663319</v>
+        <v>4.119575801904767</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.050299869566069</v>
+        <v>-4.967358898288528</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.792454015223412</v>
+        <v>1.825630403734428</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4844001058599581</v>
+        <v>0.5181899745957055</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.103570450879562</v>
+        <v>4.123844372121011</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.152275991814476</v>
+        <v>-5.069335020536935</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.760589204779951</v>
+        <v>1.793765593290968</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3824239836115505</v>
+        <v>0.4162138523472979</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.051310415986419</v>
+        <v>4.071584337227868</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.042269708337255</v>
+        <v>-4.959328737059714</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.796744605415015</v>
+        <v>1.829920993926032</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4056285555288257</v>
+        <v>0.4394184242645731</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.057386046380961</v>
+        <v>4.077659967622409</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.899210132596329</v>
+        <v>-4.816269161318788</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.85821844643336</v>
+        <v>1.891394834944376</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.413641982118805</v>
+        <v>0.4474318508545524</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.066444113056922</v>
+        <v>4.086718034298371</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.597763407124491</v>
+        <v>-4.51482243584695</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.986058019504631</v>
+        <v>2.019234408015647</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7488785763263897</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.25457303122256</v>
+        <v>4.274846952464009</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.622353651359675</v>
+        <v>-4.539412680082134</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.977193099563268</v>
+        <v>2.010369488074284</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7488785763263897</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.255544208975271</v>
+        <v>4.275818130216719</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.571315275353155</v>
+        <v>-4.488374304075614</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.998451354345632</v>
+        <v>2.031627742856648</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7488785763263897</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.256387113355027</v>
+        <v>4.276661034596475</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.530175980486524</v>
+        <v>-4.447235009208983</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.03394517116643</v>
+        <v>2.067121559677446</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7562280024572731</v>
+        <v>0.7900178711930205</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.30010878914915</v>
+        <v>4.320382710390599</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.433541068467884</v>
+        <v>-4.350600097190343</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.88878313209782</v>
+        <v>1.921959520608836</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.852862914475913</v>
+        <v>0.8866527832116604</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.174273732484269</v>
+        <v>4.194547653725717</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.564121802998726</v>
+        <v>-4.481180831721185</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.840052882359447</v>
+        <v>1.873229270870464</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7222821799450705</v>
+        <v>0.7560720486808179</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.099427335839728</v>
+        <v>4.119701257081176</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.399625468807765</v>
+        <v>-4.316684497530224</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.890278235111915</v>
+        <v>1.923454623622931</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.9205683828717798</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.182551955430387</v>
+        <v>4.202825876671835</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.322526867265892</v>
+        <v>-4.239585895988351</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.920305386165094</v>
+        <v>1.95348177467611</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.9205683828717798</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.181739665866817</v>
+        <v>4.202013587108265</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.332912062155781</v>
+        <v>-4.24997109087824</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.92602008733421</v>
+        <v>1.959196475845226</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8763933192461431</v>
+        <v>0.9101831879818905</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.185377328057956</v>
+        <v>4.205651249299405</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.351500220878006</v>
+        <v>-4.268559249600465</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.989421829621745</v>
+        <v>2.022598218132762</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8578051605239176</v>
+        <v>0.8915950292596651</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.245061438601046</v>
+        <v>4.265335359842494</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.351798767574042</v>
+        <v>-4.268857796296501</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.986171421761629</v>
+        <v>2.019347810272646</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8575066138278817</v>
+        <v>0.8912964825636291</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.241751321401723</v>
+        <v>4.262025242643171</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.250975633883614</v>
+        <v>-4.168034662606074</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.031031570177192</v>
+        <v>2.064207958688208</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8699708293122356</v>
+        <v>0.903760698047983</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.253760745631727</v>
+        <v>4.274034666873175</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.060194273131208</v>
+        <v>-3.977253301853666</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.107473367956698</v>
+        <v>2.140649756467714</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.060752190064643</v>
+        <v>1.09454205880039</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.368358815561714</v>
+        <v>4.388632736803163</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.953230915281786</v>
+        <v>-3.870289944004244</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.130095556834063</v>
+        <v>2.163271945345079</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.119216798024445</v>
+        <v>1.153006666760192</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.383274426075191</v>
+        <v>4.40354834731664</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.897900327380024</v>
+        <v>-3.814959356102482</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.187194728606826</v>
+        <v>2.220371117117843</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.174547385926207</v>
+        <v>1.208337254661954</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.451439715428307</v>
+        <v>4.471713636669755</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.885846200467061</v>
+        <v>-3.802905229189519</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.185702947273449</v>
+        <v>2.218879335784466</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.186601512839169</v>
+        <v>1.220391381574917</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.452358759477523</v>
+        <v>4.472632680718971</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.927001320035282</v>
+        <v>-3.84406034875774</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.171121529630296</v>
+        <v>2.204297918141314</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.145446393270948</v>
+        <v>1.179236262006696</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.429546317920726</v>
+        <v>4.449820239162174</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.858952757343752</v>
+        <v>-3.77601178606621</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.211191980584791</v>
+        <v>2.244368369095808</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.483226481413526</v>
+        <v>4.503500402654975</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.090553150513253</v>
+        <v>-4.007612179235712</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.138754493490585</v>
+        <v>2.171930882001601</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.50342915158712</v>
+        <v>4.523703072828569</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.140604696042473</v>
+        <v>-4.057663724764931</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.102340111345779</v>
+        <v>2.135516499856796</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.487035387654003</v>
+        <v>4.507309308895451</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.315711528618918</v>
+        <v>-4.232770557341375</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.992549291908667</v>
+        <v>2.025725680419685</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.447287301247469</v>
+        <v>4.467561222488918</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.119611375188395</v>
+        <v>-4.036670403910852</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.078011972277817</v>
+        <v>2.111188360788834</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.409595109393001</v>
+        <v>1.443384978128749</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.571970012302723</v>
+        <v>4.592243933544172</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.966585983075111</v>
+        <v>-3.883645011797568</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.238393128696035</v>
+        <v>2.271569517207052</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.562620501506285</v>
+        <v>1.596410370242033</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.762956247143598</v>
+        <v>4.783230168385046</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.994893296948381</v>
+        <v>-3.911952325670838</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.414536428055019</v>
+        <v>2.447712816566036</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.562620501506285</v>
+        <v>1.596410370242033</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.950422472051891</v>
+        <v>4.970696393293339</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.161486522061903</v>
+        <v>-4.07854555078436</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.317302089363693</v>
+        <v>2.35047847787471</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.396027276392763</v>
+        <v>1.42981714512851</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.81986948833786</v>
+        <v>4.840143409579308</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.138450728700337</v>
+        <v>-4.055509757422795</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.330192809370037</v>
+        <v>2.363369197881054</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.396027276392763</v>
+        <v>1.42981714512851</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.823545890999577</v>
+        <v>4.843819812241025</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.109204748244641</v>
+        <v>-4.026263776967098</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.339509256675811</v>
+        <v>2.372685645186828</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.396027276392763</v>
+        <v>1.42981714512851</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.821163946123072</v>
+        <v>4.841437867364521</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.216130296122492</v>
+        <v>-4.133189324844949</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.294032276682305</v>
+        <v>2.327208665193322</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.289101728514912</v>
+        <v>1.322891597250659</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.754301856553997</v>
+        <v>4.774575777795445</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.36114885462974</v>
+        <v>-4.278207883352198</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.23745365542264</v>
+        <v>2.270630043933657</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.144083170007663</v>
+        <v>1.17787303874341</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.668719523592881</v>
+        <v>4.68899344483433</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.479490620414458</v>
+        <v>-4.396549649136915</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.290048188366506</v>
+        <v>2.323224576877523</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.775062385988369</v>
+        <v>4.795336307229817</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.530901042735166</v>
+        <v>-4.447960071457623</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.267269716564162</v>
+        <v>2.300446105075179</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.772848083114307</v>
+        <v>4.793122004355756</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.610320493942917</v>
+        <v>-4.527379522665375</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.23540506415535</v>
+        <v>2.268581452666368</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.772751211188597</v>
+        <v>4.793025132430046</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.705783491860135</v>
+        <v>-4.622842520582592</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.197213758546507</v>
+        <v>2.230390147057524</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.77274510474664</v>
+        <v>4.793019025988089</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.64140758100942</v>
+        <v>-4.558466609731878</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.221060519449404</v>
+        <v>2.25423690796042</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.219145119421268</v>
+        <v>1.252934988157016</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.80946704781968</v>
+        <v>4.829740969061128</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.696776743141614</v>
+        <v>-4.613835771864071</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.204646672344253</v>
+        <v>2.23782306085527</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.219145119421268</v>
+        <v>1.252934988157016</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.815200865567407</v>
+        <v>4.835474786808855</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.742214522972441</v>
+        <v>-4.659273551694898</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.186009923754854</v>
+        <v>2.219186312265871</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.789032234503443</v>
+        <v>4.809306155744891</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.654007688824863</v>
+        <v>-4.57106671754732</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.241167050264204</v>
+        <v>2.274343438775221</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.808906627353762</v>
+        <v>4.82918054859521</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.547972693619553</v>
+        <v>-4.465031722342011</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.267281748871055</v>
+        <v>2.300458137382073</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.79260732787849</v>
+        <v>4.812881249119938</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.364761030486458</v>
+        <v>-4.281820059208916</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.342997363588339</v>
+        <v>2.376173752099357</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.795038277342536</v>
+        <v>4.815312198583984</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.293039583472607</v>
+        <v>-4.210098612195065</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.337477128241769</v>
+        <v>2.370653516752786</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.248021575756959</v>
+        <v>1.281811444492707</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.803862331398736</v>
+        <v>4.824136252640184</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.270666557864901</v>
+        <v>-4.187725586587359</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.293342084406023</v>
+        <v>2.32651847291704</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.259277326869861</v>
+        <v>1.293067195605608</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.757531527987648</v>
+        <v>4.777805449229096</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.303682853775646</v>
+        <v>-4.220741882498103</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.465333770927081</v>
+        <v>2.498510159438098</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.189839950203109</v>
+        <v>1.223629818938857</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.901067306872952</v>
+        <v>4.921341228114401</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.292155218126037</v>
+        <v>-4.209214246848495</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.461866051015173</v>
+        <v>2.49504243952619</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.248840608404472</v>
+        <v>1.282630477140219</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.928388927622019</v>
+        <v>4.948662848863467</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.389496719468406</v>
+        <v>-4.306555748190863</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.426597563000015</v>
+        <v>2.459773951511032</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.204420426238983</v>
+        <v>1.238210294974731</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.905404930844514</v>
+        <v>4.925678852085963</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.475352748808373</v>
+        <v>-4.39241177753083</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.393506233456866</v>
+        <v>2.426682621967883</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.162044357012848</v>
+        <v>1.195834225748596</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.881230371501672</v>
+        <v>4.90150429274312</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.484189546224492</v>
+        <v>-4.401248574946949</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.37239071631092</v>
+        <v>2.405567104821937</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.154602184371498</v>
+        <v>1.188392053107245</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.859184269737363</v>
+        <v>4.879458190978811</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.575572108789951</v>
+        <v>-4.492631137512408</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.346002202329786</v>
+        <v>2.379178590840803</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.063219621806039</v>
+        <v>1.097009490541787</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.814519243243137</v>
+        <v>4.834793164484586</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.563865390802945</v>
+        <v>-4.480924419525402</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.452813147348857</v>
+        <v>2.485989535859874</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.074926339793046</v>
+        <v>1.108716208528793</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.923671531859609</v>
+        <v>4.943945453101058</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.464201886719282</v>
+        <v>-4.381260915441739</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.495710887713726</v>
+        <v>2.528887276224744</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.138113422996732</v>
+        <v>1.17190329173248</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.964616120513226</v>
+        <v>4.984890041754674</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.474517984885634</v>
+        <v>-4.391577013608091</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.704489281725244</v>
+        <v>2.737665670236261</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.138113422996732</v>
+        <v>1.17190329173248</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.177520953791285</v>
+        <v>5.197794875032733</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.474424016868261</v>
+        <v>-4.391483045590719</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.703705535844283</v>
+        <v>2.736881924355299</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.176921537511765</v>
+        <v>5.197195458753213</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.481642841068106</v>
+        <v>-4.398701869790563</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.695049992108698</v>
+        <v>2.728226380619716</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.171153523456119</v>
+        <v>5.191427444697567</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.480694417950067</v>
+        <v>-4.397753446672525</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.695429361355914</v>
+        <v>2.728605749866931</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.171153523456119</v>
+        <v>5.191427444697567</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.637762876205691</v>
+        <v>-4.554821904928149</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.645329586034756</v>
+        <v>2.678505974545773</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.183881131437211</v>
+        <v>5.204155052678659</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.63177062941688</v>
+        <v>-4.548829658139337</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.649672483174669</v>
+        <v>2.682848871685686</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.185827129861599</v>
+        <v>5.206101051103047</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.45154270308298</v>
+        <v>3.843231234285966</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.535637849864232</v>
+        <v>-4.554067437705619</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.681779731013497</v>
+        <v>2.674407895876942</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.179481265879367</v>
+        <v>5.199755187120815</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-46.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.0%</t>
+          <t>-607.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-108.8%</t>
+          <t>-105.0%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911635</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213491</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -49483,10 +49483,10 @@
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.554067437705619</v>
+        <v>-4.46027169700857</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.674407895876942</v>
+        <v>2.711926192155762</v>
       </c>
       <c r="F2084" t="n">
         <v>1.172273153079798</v>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>138.0%</t>
+          <t>119.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.2%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.6%</t>
+          <t>-615.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-105.0%</t>
+          <t>-127.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.8%</t>
+          <t>-323.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-106.8%</t>
+          <t>-110.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>103.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.6%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911635</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213491</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097814</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.364319676792658</v>
+        <v>-3.447260648070199</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.278172479013076</v>
+        <v>1.244996090502059</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9190609009675099</v>
+        <v>0.8852710322317625</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.175693314624392</v>
+        <v>3.155419393382944</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.320116839706757</v>
+        <v>-3.403057810984299</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.301733216375274</v>
+        <v>1.268556827864257</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9632637380534104</v>
+        <v>0.929473869317663</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.20809461940377</v>
+        <v>3.187820698162321</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.327676505543804</v>
+        <v>-3.410617476821346</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.297119350509702</v>
+        <v>1.263942961998685</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.01806714206323</v>
+        <v>0.9842772733274823</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.239386662278909</v>
+        <v>3.219112741037461</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.169385088004532</v>
+        <v>-3.252326059282074</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.411683682708451</v>
+        <v>1.378507294197434</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.01806714206323</v>
+        <v>0.9842772733274823</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.290634427461949</v>
+        <v>3.2703605062205</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.961743084370056</v>
+        <v>-3.044684055647597</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.493181188756495</v>
+        <v>1.460004800245478</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.225709145697706</v>
+        <v>1.191919276961958</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.413660334236888</v>
+        <v>3.393386412995439</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.910710991647528</v>
+        <v>-2.993651962925069</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.508542254083776</v>
+        <v>1.475365865572759</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.276741238420234</v>
+        <v>1.242951369684486</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.439227818108674</v>
+        <v>3.418953896867226</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.845486810520322</v>
+        <v>-2.928427781797863</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.551819330627363</v>
+        <v>1.518642942116346</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.341965419547439</v>
+        <v>1.308175550811692</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.495549730877702</v>
+        <v>3.475275809636254</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.808059790449188</v>
+        <v>-2.89100076172673</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.562751110955097</v>
+        <v>1.52957472244408</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.347216957576621</v>
+        <v>1.313427088840874</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.494661625994492</v>
+        <v>3.474387704753044</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.828171446483896</v>
+        <v>-2.911112417761438</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.555963240872454</v>
+        <v>1.522786852361437</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.35824430257404</v>
+        <v>1.324454433838293</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.502534825324184</v>
+        <v>3.482260904082735</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.799758183384013</v>
+        <v>-2.882699154661554</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.727886317133618</v>
+        <v>1.694709928622601</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.299268739827611</v>
+        <v>1.265478871091864</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.627707258697537</v>
+        <v>3.607433337456089</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.724975922359</v>
+        <v>-2.807916893636542</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.87791213076144</v>
+        <v>1.844735742250424</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.374051000852624</v>
+        <v>1.340261132116877</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.792689524530362</v>
+        <v>3.772415603288914</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.698891838095192</v>
+        <v>-2.781832809372734</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.880053740480822</v>
+        <v>1.846877351969806</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.374051000852624</v>
+        <v>1.340261132116877</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.784397500544221</v>
+        <v>3.764123579302773</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.611013924986072</v>
+        <v>-2.693954896263613</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.91339810130825</v>
+        <v>1.880221712797233</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.489976643275975</v>
+        <v>1.456186774540228</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.852146081582011</v>
+        <v>3.831872160340563</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.602121463592788</v>
+        <v>-2.68506243487033</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.934509491592355</v>
+        <v>1.901333103081338</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.489976643275975</v>
+        <v>1.456186774540228</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.869700487308803</v>
+        <v>3.849426566067354</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.770597580562666</v>
+        <v>-2.853538551840208</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.858974092208988</v>
+        <v>1.825797703697971</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.462028807559394</v>
+        <v>1.428238938823647</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.844786833283438</v>
+        <v>3.824512912041989</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.324341387933226</v>
+        <v>-2.407282359210768</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.018746266448626</v>
+        <v>1.985569877937609</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.367310137889762</v>
+        <v>1.333520269154014</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.76922532866952</v>
+        <v>3.748951407428072</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.301620284250073</v>
+        <v>-2.384561255527615</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.018498730418791</v>
+        <v>1.985322341907774</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.367310137889762</v>
+        <v>1.333520269154014</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.759889351166425</v>
+        <v>3.739615429924976</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.430822097544116</v>
+        <v>-2.513763068821658</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.125724130952343</v>
+        <v>2.092547742441326</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.238108324595719</v>
+        <v>1.204318455859972</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.841274389041168</v>
+        <v>3.82100046779972</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.456696496018142</v>
+        <v>-2.539637467295683</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.152452194056379</v>
+        <v>2.119275805545363</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.283019933307461</v>
+        <v>1.249230064571713</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.90529917676186</v>
+        <v>3.885025255520411</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.449641805802968</v>
+        <v>-2.53258277708051</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.151949426131994</v>
+        <v>2.118773037620977</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.290074623522634</v>
+        <v>1.256284754786887</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.906207346880509</v>
+        <v>3.885933425639061</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.42269058147648</v>
+        <v>-2.505631552754022</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.172736069507331</v>
+        <v>2.139559680996314</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.304954969550354</v>
+        <v>1.271165100814606</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.925141708141882</v>
+        <v>3.904867786900434</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.444234809307267</v>
+        <v>-2.527175780584809</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.348221510519976</v>
+        <v>2.315045122008959</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.304954969550354</v>
+        <v>1.271165100814606</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.109244840286842</v>
+        <v>4.088970919045393</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.466642927112139</v>
+        <v>-2.549583898389681</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.33137495830102</v>
+        <v>2.298198569790003</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.304954969550354</v>
+        <v>1.271165100814606</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.101361535189835</v>
+        <v>4.081087613948386</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.49486716268974</v>
+        <v>-2.577808133967281</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.322139263619617</v>
+        <v>2.2889628751086</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.322931722001662</v>
+        <v>1.289141853265915</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.114201586210258</v>
+        <v>4.093927664968809</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.50430808857827</v>
+        <v>-2.587249059855811</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.374616610986052</v>
+        <v>2.341440222475036</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.445358839545054</v>
+        <v>1.411568970809306</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.243911574458139</v>
+        <v>4.223637653216691</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.593184719746743</v>
+        <v>-2.676125691024285</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.341957053063964</v>
+        <v>2.308780664552947</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.35648220837658</v>
+        <v>1.322692339640832</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.193476690302356</v>
+        <v>4.173202769060908</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.669514697347649</v>
+        <v>-2.752455668625191</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.309536874917376</v>
+        <v>2.27636048640636</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.35648220837658</v>
+        <v>1.322692339640832</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.191588503196131</v>
+        <v>4.171314581954683</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.763178642025191</v>
+        <v>-2.846119613302732</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.266891526649222</v>
+        <v>2.233715138138206</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.262818263699038</v>
+        <v>1.229028394963291</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.130210365992469</v>
+        <v>4.10993644475102</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.924747067552446</v>
+        <v>-3.007688038829988</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.200698166648473</v>
+        <v>2.167521778137456</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.136035339901159</v>
+        <v>1.102245471165411</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.052574621923894</v>
+        <v>4.032300700682445</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.033047729422565</v>
+        <v>-3.115988700700107</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.170451308766343</v>
+        <v>2.137274920255327</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.136035339901159</v>
+        <v>1.102245471165411</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.065648028789812</v>
+        <v>4.045374107548364</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.050851701143309</v>
+        <v>-3.133792672420851</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.155334916860986</v>
+        <v>2.122158528349969</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.065500716995958</v>
+        <v>1.03171084826021</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.015332451829631</v>
+        <v>3.995058530588183</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.078752488252782</v>
+        <v>-3.161693459530324</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.142698643144199</v>
+        <v>2.109522254633182</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.030903792853023</v>
+        <v>0.9971139241172757</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.993098338470872</v>
+        <v>3.972824417229424</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.201278590955676</v>
+        <v>-3.284219562233218</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.09045264604024</v>
+        <v>2.057276257529223</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9083776901501293</v>
+        <v>0.8745878214143818</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.916347120826335</v>
+        <v>3.896073199584887</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.431793087141265</v>
+        <v>-3.514734058418807</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.064952807156508</v>
+        <v>2.031776418645491</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6778631939645405</v>
+        <v>0.6440733252287931</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.844744382705485</v>
+        <v>3.824470461464037</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.780538172365709</v>
+        <v>-3.863479143643251</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.065766492068577</v>
+        <v>2.032590103557561</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.919807329355994</v>
+        <v>3.899533408114546</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.934524590141849</v>
+        <v>-4.017465561419391</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.073152194103761</v>
+        <v>2.039975805592745</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.988787598501633</v>
+        <v>3.968513677260185</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.884002686314183</v>
+        <v>-3.966943657591725</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.079412157754948</v>
+        <v>2.046235769243931</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.974838800621755</v>
+        <v>3.954564879380306</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.136477840321907</v>
+        <v>-4.219418811599449</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.990292585207273</v>
+        <v>1.957116196696256</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.986709289677169</v>
+        <v>3.96643536843572</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.429373596801319</v>
+        <v>-4.512314568078861</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.874344817134451</v>
+        <v>1.841168428623435</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.987919824196112</v>
+        <v>3.967645902954664</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.616037724936128</v>
+        <v>-4.698978696213669</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.80380090810785</v>
+        <v>1.770624519596833</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5423762692210828</v>
+        <v>0.5085864004853354</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.975998183928698</v>
+        <v>3.95572426268725</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.76205841185009</v>
+        <v>-4.844999383127631</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.740470486078454</v>
+        <v>1.707294097567437</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5332931774272258</v>
+        <v>0.4995033086914784</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.965626181588573</v>
+        <v>3.945352260347125</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.853772420959675</v>
+        <v>-4.936713392237216</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.865988939133664</v>
+        <v>1.832812550622648</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5332931774272258</v>
+        <v>0.4995033086914784</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.127830238287618</v>
+        <v>4.107556317046169</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.885424080019645</v>
+        <v>-4.968365051297186</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.84817491347349</v>
+        <v>1.814998524962474</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5281247201827857</v>
+        <v>0.4943348514470383</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.119575801904767</v>
+        <v>4.099301880663319</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.967358898288528</v>
+        <v>-5.050299869566069</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.825630403734428</v>
+        <v>1.792454015223412</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5181899745957055</v>
+        <v>0.4844001058599581</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.123844372121011</v>
+        <v>4.103570450879562</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.069335020536935</v>
+        <v>-5.152275991814476</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.793765593290968</v>
+        <v>1.760589204779951</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4162138523472979</v>
+        <v>0.3824239836115505</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.071584337227868</v>
+        <v>4.051310415986419</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.959328737059714</v>
+        <v>-5.042269708337255</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.829920993926032</v>
+        <v>1.796744605415015</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4394184242645731</v>
+        <v>0.4056285555288257</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.077659967622409</v>
+        <v>4.057386046380961</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.816269161318788</v>
+        <v>-4.899210132596329</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.891394834944376</v>
+        <v>1.85821844643336</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4474318508545524</v>
+        <v>0.413641982118805</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.086718034298371</v>
+        <v>4.066444113056922</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.51482243584695</v>
+        <v>-4.597763407124491</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.019234408015647</v>
+        <v>1.986058019504631</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7488785763263897</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.274846952464009</v>
+        <v>4.25457303122256</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.638522500516944</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.539412680082134</v>
+        <v>-4.622353651359675</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.010369488074284</v>
+        <v>1.789224615659327</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7488785763263897</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.275818130216719</v>
+        <v>4.06757572507133</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.6393654048967</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.488374304075614</v>
+        <v>-4.571315275353155</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.031627742856648</v>
+        <v>1.810482870441691</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7488785763263897</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.276661034596475</v>
+        <v>4.068418629451085</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.658403503770845</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.447235009208983</v>
+        <v>-4.530175980486524</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.067121559677446</v>
+        <v>1.845976687262489</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7900178711930205</v>
+        <v>0.7562280024572731</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.320382710390599</v>
+        <v>4.11214030524521</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.47458749989478</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.350600097190343</v>
+        <v>-4.433541068467884</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.921959520608836</v>
+        <v>1.700814648193879</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8866527832116604</v>
+        <v>0.852862914475913</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.194547653725717</v>
+        <v>3.986305248580328</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.478089543968744</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.481180831721185</v>
+        <v>-4.564121802998726</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.873229270870464</v>
+        <v>1.652084398455506</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7560720486808179</v>
+        <v>0.7222821799450705</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.119701257081176</v>
+        <v>3.911458851935786</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.462516363044826</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.316684497530224</v>
+        <v>-4.399625468807765</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.923454623622931</v>
+        <v>1.702309751207973</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9205683828717798</v>
+        <v>0.8867785141360324</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.202825876671835</v>
+        <v>3.994583471526446</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.461704073481256</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.239585895988351</v>
+        <v>-4.322526867265892</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.95348177467611</v>
+        <v>1.732336902261152</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9205683828717798</v>
+        <v>0.8867785141360324</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.202013587108265</v>
+        <v>3.993771181962876</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.471572852606328</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.24997109087824</v>
+        <v>-4.332912062155781</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.959196475845226</v>
+        <v>1.738051603430268</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9101831879818905</v>
+        <v>0.8763933192461431</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.205651249299405</v>
+        <v>3.997408844154014</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.542409858382753</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.268559249600465</v>
+        <v>-4.351500220878006</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.022598218132762</v>
+        <v>1.801453345717804</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8915950292596651</v>
+        <v>0.8578051605239176</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.265335359842494</v>
+        <v>4.057092954697104</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.539278869201052</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.268857796296501</v>
+        <v>-4.351798767574042</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.019347810272646</v>
+        <v>1.798202937857688</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8912964825636291</v>
+        <v>0.8575066138278817</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.262025242643171</v>
+        <v>4.053782837497781</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.543809764140443</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.168034662606074</v>
+        <v>-4.250975633883614</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.064207958688208</v>
+        <v>1.84306308627325</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.903760698047983</v>
+        <v>0.8699708293122356</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.274034666873175</v>
+        <v>4.065792261727785</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.543939017618987</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.977253301853666</v>
+        <v>-4.060194273131208</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.140649756467714</v>
+        <v>1.919504884052756</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.09454205880039</v>
+        <v>1.060752190064643</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.388632736803163</v>
+        <v>4.180390331657772</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.523775863356583</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.870289944004244</v>
+        <v>-3.953230915281786</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.163271945345079</v>
+        <v>1.942127072930122</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.153006666760192</v>
+        <v>1.119216798024445</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.40354834731664</v>
+        <v>4.195305942171251</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.558742799968642</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.814959356102482</v>
+        <v>-3.897900327380024</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.220371117117843</v>
+        <v>1.999226244702885</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.208337254661954</v>
+        <v>1.174547385926207</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.471713636669755</v>
+        <v>4.263471231524366</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.552429367870079</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.802905229189519</v>
+        <v>-3.885846200467061</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.218879335784466</v>
+        <v>1.997734463369508</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.220391381574917</v>
+        <v>1.186601512839169</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.472632680718971</v>
+        <v>4.264390275573581</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.554309998054215</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.84406034875774</v>
+        <v>-3.927001320035282</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.204297918141314</v>
+        <v>1.983153045726355</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.179236262006696</v>
+        <v>1.145446393270948</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.449820239162174</v>
+        <v>4.241577834016785</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.567161023932098</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.77601178606621</v>
+        <v>-3.858952757343752</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.244368369095808</v>
+        <v>2.02322349668085</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.503500402654975</v>
+        <v>4.295257997509585</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.587363694105692</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.007612179235712</v>
+        <v>-4.090553150513253</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.171930882001601</v>
+        <v>1.950786009586643</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.523703072828569</v>
+        <v>4.315460667683179</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.570969930172574</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.057663724764931</v>
+        <v>-4.140604696042473</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.135516499856796</v>
+        <v>1.914371627441837</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.507309308895451</v>
+        <v>4.299066903750061</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.531221843766041</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.232770557341375</v>
+        <v>-4.315711528618918</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.025725680419685</v>
+        <v>1.804580808004726</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.467561222488918</v>
+        <v>4.259318817343527</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.538244462762981</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.036670403910852</v>
+        <v>-4.119611375188395</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.111188360788834</v>
+        <v>1.890043488373875</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.443384978128749</v>
+        <v>1.409595109393001</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.592243933544172</v>
+        <v>4.384001528398781</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.637415462335885</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.883645011797568</v>
+        <v>-3.966585983075111</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.271569517207052</v>
+        <v>2.050424644792093</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.596410370242033</v>
+        <v>1.562620501506285</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.783230168385046</v>
+        <v>4.574987763239657</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.824881687244178</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.911952325670838</v>
+        <v>-3.994893296948381</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.447712816566036</v>
+        <v>2.226567944151078</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.596410370242033</v>
+        <v>1.562620501506285</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.970696393293339</v>
+        <v>4.762453988147949</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.79428463859826</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.07854555078436</v>
+        <v>-4.161486522061903</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.35047847787471</v>
+        <v>2.129333605459752</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.42981714512851</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.840143409579308</v>
+        <v>4.631901004433918</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.797961041259978</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.055509757422795</v>
+        <v>-4.138450728700337</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.363369197881054</v>
+        <v>2.142224325466096</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.42981714512851</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.843819812241025</v>
+        <v>4.635577407095636</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.795579096383473</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.026263776967098</v>
+        <v>-4.109204748244641</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.372685645186828</v>
+        <v>2.15154077277187</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.42981714512851</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.841437867364521</v>
+        <v>4.633195462219131</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.792872335541108</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.133189324844949</v>
+        <v>-4.216130296122492</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.327208665193322</v>
+        <v>2.106063792778365</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.322891597250659</v>
+        <v>1.289101728514912</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.774575777795445</v>
+        <v>4.566333372650055</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.794301137684343</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.278207883352198</v>
+        <v>-4.36114885462974</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.270630043933657</v>
+        <v>2.049485171518699</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.17787303874341</v>
+        <v>1.144083170007663</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.68899344483433</v>
+        <v>4.480751039688941</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>3.894232376942095</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.396549649136915</v>
+        <v>-4.479490620414458</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.323224576877523</v>
+        <v>2.102079704462565</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.795336307229817</v>
+        <v>4.587093902084428</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>3.892018074068035</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.447960071457623</v>
+        <v>-4.530901042735166</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.300446105075179</v>
+        <v>2.079301232660221</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.793122004355756</v>
+        <v>4.584879599210367</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>3.891921202142324</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.527379522665375</v>
+        <v>-4.610320493942917</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.268581452666368</v>
+        <v>2.047436580251409</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.793025132430046</v>
+        <v>4.584782727284656</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>3.891915095700367</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.622842520582592</v>
+        <v>-4.705783491860135</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.230390147057524</v>
+        <v>2.009245274642566</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.793019025988089</v>
+        <v>4.584776620842699</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>3.890011492262977</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.558466609731878</v>
+        <v>-4.64140758100942</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.25423690796042</v>
+        <v>2.033092035545462</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.252934988157016</v>
+        <v>1.219145119421268</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.829740969061128</v>
+        <v>4.621498563915739</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>3.895745310010704</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.613835771864071</v>
+        <v>-4.696776743141614</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.23782306085527</v>
+        <v>2.016678188440311</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.252934988157016</v>
+        <v>1.219145119421268</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.835474786808855</v>
+        <v>4.627232381663466</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>3.895283673353636</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.659273551694898</v>
+        <v>-4.742214522972441</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.219186312265871</v>
+        <v>1.998041439850913</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.809306155744891</v>
+        <v>4.601063750599502</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>3.915158066203955</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.57106671754732</v>
+        <v>-4.654007688824863</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.274343438775221</v>
+        <v>2.053198566360263</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.82918054859521</v>
+        <v>4.620938143449821</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>3.898858766728683</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.465031722342011</v>
+        <v>-4.547972693619553</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.300458137382073</v>
+        <v>2.079313264967114</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.812881249119938</v>
+        <v>4.604638843974548</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>3.901289716192729</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.281820059208916</v>
+        <v>-4.364761030486458</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.376173752099357</v>
+        <v>2.155028879684398</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.815312198583984</v>
+        <v>4.607069793438594</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.867080902040619</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.210098612195065</v>
+        <v>-4.293039583472607</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.370653516752786</v>
+        <v>2.149508644337828</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.281811444492707</v>
+        <v>1.248021575756959</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.824136252640184</v>
+        <v>4.615893847494795</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.81399664796179</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.187725586587359</v>
+        <v>-4.270666557864901</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.32651847291704</v>
+        <v>2.105373600502083</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.293067195605608</v>
+        <v>1.259277326869861</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.777805449229096</v>
+        <v>4.569563044083707</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>3.999194852847146</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.220741882498103</v>
+        <v>-4.303682853775646</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.498510159438098</v>
+        <v>2.27736528702314</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.223629818938857</v>
+        <v>1.189839950203109</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.921341228114401</v>
+        <v>4.713098822969012</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>3.991116078675395</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.209214246848495</v>
+        <v>-4.292155218126037</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.49504243952619</v>
+        <v>2.273897567111232</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.282630477140219</v>
+        <v>1.248840608404472</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.948662848863467</v>
+        <v>4.740420443718079</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>3.994784191197184</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.306555748190863</v>
+        <v>-4.389496719468406</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.459773951511032</v>
+        <v>2.238629079096074</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.238210294974731</v>
+        <v>1.204420426238983</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.925678852085963</v>
+        <v>4.717436446940574</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>3.996035273390022</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.39241177753083</v>
+        <v>-4.475352748808373</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.426682621967883</v>
+        <v>2.205537749552925</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.195834225748596</v>
+        <v>1.162044357012848</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.90150429274312</v>
+        <v>4.693261887597731</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>3.978454475210524</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.401248574946949</v>
+        <v>-4.484189546224492</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.405567104821937</v>
+        <v>2.18442223240698</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.188392053107245</v>
+        <v>1.154602184371498</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.879458190978811</v>
+        <v>4.671215785833422</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>3.988618986255573</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.492631137512408</v>
+        <v>-4.575572108789951</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.379178590840803</v>
+        <v>2.158033718425846</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.097009490541787</v>
+        <v>1.063219621806039</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.834793164484586</v>
+        <v>4.626550759339197</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.090747244079841</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.480924419525402</v>
+        <v>-4.563865390802945</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.485989535859874</v>
+        <v>2.264844663444916</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.108716208528793</v>
+        <v>1.074926339793046</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.943945453101058</v>
+        <v>4.735703047955669</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.093779582811246</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.381260915441739</v>
+        <v>-4.464201886719282</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.528887276224744</v>
+        <v>2.307742403809786</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.17190329173248</v>
+        <v>1.138113422996732</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.984890041754674</v>
+        <v>4.776647636609286</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.306684416089304</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.391577013608091</v>
+        <v>-4.474517984885634</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.737665670236261</v>
+        <v>2.516520797821303</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.17190329173248</v>
+        <v>1.138113422996732</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.197794875032733</v>
+        <v>4.989552469887344</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.305863083001394</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.391483045590719</v>
+        <v>-4.474424016868261</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.736881924355299</v>
+        <v>2.515737051940342</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.197195458753213</v>
+        <v>4.988953053607824</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.300095068945748</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.398701869790563</v>
+        <v>-4.481642841068106</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.728226380619716</v>
+        <v>2.507081508204758</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.191427444697567</v>
+        <v>4.983185039552178</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.300095068945748</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.397753446672525</v>
+        <v>-4.480694417950067</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.728605749866931</v>
+        <v>2.507460877451973</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.191427444697567</v>
+        <v>4.983185039552178</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.31282267692684</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.554821904928149</v>
+        <v>-4.637762876205691</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.678505974545773</v>
+        <v>2.457361102130815</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.204155052678659</v>
+        <v>4.99591264753327</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.502737159255168</v>
+        <v>4.314768675351227</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.548829658139337</v>
+        <v>-4.63177062941688</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.682848871685686</v>
+        <v>2.461703999270728</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.206101051103047</v>
+        <v>4.997858645957658</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.843231234285966</v>
+        <v>3.897017113655675</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.496391295272937</v>
+        <v>4.308422811368996</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.46027169700857</v>
+        <v>-4.543212668286112</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.711926192155762</v>
+        <v>2.490781319740804</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.199755187120815</v>
+        <v>4.991512781975427</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,17 +786,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>131.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-616.8%</t>
+          <t>-605.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>427.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.9%</t>
+          <t>-613.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-247.1%</t>
+          <t>-242.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.1%</t>
+          <t>-125.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.0%</t>
+          <t>-323.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-110.1%</t>
+          <t>-106.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2084"/>
+  <dimension ref="A1:G2085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.5415284190966594</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.859135855474547</v>
+        <v>2.904360970374315</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.530139182441858</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.861516346255708</v>
+        <v>2.906741461155476</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.7826170768612639</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.758452079993008</v>
+        <v>2.803677194892777</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.072748743466695</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.642265629949757</v>
+        <v>2.687490744849526</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.280752801819773</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.563956151162452</v>
+        <v>2.60918126606222</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.342931212980743</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.57939135793582</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911635</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.708999940125395</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.426048166384408</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213491</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-1.91749072157708</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.362990143542503</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.164691906342302</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.272208420044982</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.657076934366399</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>2.076360800879076</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.155320112545891</v>
+        <v>-3.042257325296471</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.875606068420142</v>
+        <v>1.92083118331991</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.405190792560473</v>
+        <v>-3.292128005311053</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.777426919868925</v>
+        <v>1.822652034768694</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.611702569447494</v>
+        <v>-3.498639782198074</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.690928267770375</v>
+        <v>1.736153382670143</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.931046644527996</v>
+        <v>-3.817983857278576</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.564963564438434</v>
+        <v>1.610188679338202</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.31725647580377</v>
+        <v>-4.20419368855435</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.396812519395528</v>
+        <v>1.442037634295296</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.551950469936322</v>
+        <v>-4.438887682686903</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.291219696744598</v>
+        <v>1.336444811644366</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.887613117166775</v>
+        <v>-4.774550329917355</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.155535229508382</v>
+        <v>1.20076034440815</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.964057447369647</v>
+        <v>-4.850994660120227</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.131445057661475</v>
+        <v>1.176670172561243</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.329184830008393</v>
+        <v>-5.216122042758974</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9846486196118076</v>
+        <v>1.029873734511576</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.737773607189072</v>
+        <v>-5.624710819939652</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8199746527542953</v>
+        <v>0.8651997676540635</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.851534019211937</v>
+        <v>-5.738471231962517</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7696559204166098</v>
+        <v>0.814881035316378</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.267925893498934</v>
+        <v>-6.154863106249515</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6010932213106881</v>
+        <v>0.6463183362104563</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.516036736066503</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4668824600525721</v>
+        <v>0.5121075749523403</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-6.859295255709521</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3256786173410595</v>
+        <v>0.3709037322408277</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-6.907498072951865</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3048024104991232</v>
+        <v>0.3500275253988914</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.187369520175647</v>
+        <v>-7.074306732926227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2418579224385864</v>
+        <v>0.2870830373383546</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.7822719436345955</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.37408922848495</v>
+        <v>-7.26102644123553</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1631437345804621</v>
+        <v>0.2083688494802303</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.7822719436345955</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.757090617227581</v>
+        <v>-7.644027829978161</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.009841077761825634</v>
+        <v>0.05506619266159385</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.7822719436345955</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.761577062428969</v>
+        <v>-7.64851427517955</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.01061801565270049</v>
+        <v>0.0558431305524687</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.7867583888359841</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.121107384932973</v>
+        <v>-8.008044597683551</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1278438100508503</v>
+        <v>-0.08261869515108167</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.7867583888359841</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.171456448387195</v>
+        <v>-8.058393661137771</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1400674154753618</v>
+        <v>-0.09484230057559273</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8371074522902062</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.269075725808591</v>
+        <v>-8.156012938559167</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1760733758221513</v>
+        <v>-0.1308482609223822</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9347267297116029</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.32314722531695</v>
+        <v>-8.210084438067526</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1948084193039228</v>
+        <v>-0.1495833044041537</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.9887982292199623</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.326723011408697</v>
+        <v>-8.213660224159273</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1907255366219793</v>
+        <v>-0.1455004217222102</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.014327151136455</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.360375849917171</v>
+        <v>-8.247313062667747</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1997041175409326</v>
+        <v>-0.1544790026411635</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.114740519053492</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.499461964536028</v>
+        <v>-8.386399177286604</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2399668618950543</v>
+        <v>-0.1947417469952857</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.253826633672349</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.674586381922571</v>
+        <v>-8.561523594673147</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2954614081021552</v>
+        <v>-0.2502362932023861</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.428951051058893</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.909038475937061</v>
+        <v>-8.795975688687637</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3964614106095468</v>
+        <v>-0.3512362957097781</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.428951051058893</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.013413206963508</v>
+        <v>-8.900350419714083</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4448834937941015</v>
+        <v>-0.3996583788943329</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.533325782085339</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.175926672662092</v>
+        <v>-9.062863885412668</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5087730902349792</v>
+        <v>-0.4635479753352101</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.630959212504025</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.301963466030381</v>
+        <v>-9.188900678780957</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5564940789531803</v>
+        <v>-0.5112689640534112</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.605707589694283</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.24489169413445</v>
+        <v>-9.131828906885026</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5296750345084069</v>
+        <v>-0.4844499196086378</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.605707589694283</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.386563535858571</v>
+        <v>-9.273500748609147</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5878189980967967</v>
+        <v>-0.5425938831970276</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.605707589694283</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.336972691433736</v>
+        <v>-9.223909904184312</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5529292501619909</v>
+        <v>-0.5077041352622218</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.556116745269449</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.18805435696188</v>
+        <v>-9.074991569712456</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5064130500199311</v>
+        <v>-0.461187935120162</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.524867154534276</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-8.849146416993046</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.3612708009961896</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.482940478947112</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-8.724567760655454</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.310300193905094</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.482940478947112</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-8.699531079086944</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.297651747115582</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.457611391396377</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.627397903799062</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.2630647727617932</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.457611391396377</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.556031511189415</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.2442554781117994</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.386244998786729</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.462572477204191</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.2167553458306171</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.386244998786729</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.451919295650759</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.2143286337086185</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.386244998786729</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.354012256974269</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.1754661332114829</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.318259248926172</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.330058715998311</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.1652162106756063</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.294305707950215</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.065998777675514</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.07285255150823966</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.030245769627419</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.358919154170676</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.2071922642333948</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.030245769627419</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.318734855804485</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.2236096074677123</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9900614712612278</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.155334984865123</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.2883363770642142</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.8266616003218653</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-6.921853762635524</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.3896532947939062</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5931803780922668</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-6.772187371628009</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.4466276408839529</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.5002768868497308</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.639911897997123</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.400798616343462</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.3680014132188442</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581113469681644</v>
+        <v>-6.46805068243222</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.427133048357291</v>
+        <v>0.4723581632570601</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1961401976539413</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.496148802952325</v>
+        <v>-6.383086015702901</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4740252562726774</v>
+        <v>0.5192503711724465</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.1111755309246217</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.601738792725429</v>
+        <v>-6.488676005476005</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3038133307642168</v>
+        <v>0.3490384456639859</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.2167655206977261</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.533504208100002</v>
+        <v>-6.420441420850578</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3796515064914745</v>
+        <v>0.4248766213912432</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1983501978251901</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.385564166692403</v>
+        <v>-6.272501379442978</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3222067144161072</v>
+        <v>0.3674318293158758</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1780292819166325</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.332594644438414</v>
+        <v>-6.21953185718899</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3346805370642243</v>
+        <v>0.379905651963993</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.1250597596626437</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.166806448478123</v>
+        <v>-6.053743661228699</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3940352033532473</v>
+        <v>0.4392603182530164</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.1250597596626437</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.133443241999355</v>
+        <v>-6.02038045474993</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.421842840325898</v>
+        <v>0.4670679552256667</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.1250597596626437</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.025184104876833</v>
+        <v>-5.912121317627409</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4596786156341017</v>
+        <v>0.5049037305338708</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.1250597596626437</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.901892970059702</v>
+        <v>-5.788830182810278</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5064931635715308</v>
+        <v>0.5517182784712999</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.001768624845513156</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849196102928411</v>
+        <v>-5.736133315678987</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5352728886613725</v>
+        <v>0.5804980035611416</v>
       </c>
       <c r="F1916" t="n">
         <v>0.05092824228577802</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605430660944966</v>
+        <v>-5.571030944944226</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6285597738018009</v>
+        <v>0.6423196602020962</v>
       </c>
       <c r="F1917" t="n">
         <v>0.05092824228577802</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.515654988568494</v>
+        <v>-5.481255272567754</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6665943566724057</v>
+        <v>0.6803542430727014</v>
       </c>
       <c r="F1918" t="n">
         <v>0.112527687200088</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.26580459461942</v>
+        <v>-5.23140487861868</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7592765892357378</v>
+        <v>0.7730364756360331</v>
       </c>
       <c r="F1919" t="n">
         <v>0.112527687200088</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.089912502151988</v>
+        <v>-5.055512786151247</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8332325497433595</v>
+        <v>0.8469924361436547</v>
       </c>
       <c r="F1920" t="n">
         <v>0.112527687200088</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392982</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.918466039129524</v>
+        <v>-4.884066323128784</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9151386410068985</v>
+        <v>0.9288985274071939</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2839741502225512</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632776</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.838443752020403</v>
+        <v>-4.804044036019663</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9461680334668439</v>
+        <v>0.9599279198671393</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3639964373316721</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.774808009786469</v>
+        <v>-4.740408293785729</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.976317131414735</v>
+        <v>0.9900770178150302</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4276321795656067</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.681110691570074</v>
+        <v>-4.646710975569333</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9949903174850887</v>
+        <v>1.008750203885384</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4276321795656067</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.691613314635362</v>
+        <v>-4.657213598634622</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9925323448838506</v>
+        <v>1.006292231284146</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4171295565003178</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.579127053966488</v>
+        <v>-4.544727337965748</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04145616298622</v>
+        <v>1.055216049386516</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4171295565003178</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.561413367088623</v>
+        <v>-4.527013651087882</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.049220221654707</v>
+        <v>1.062980108055002</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4203108853972346</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.437939095775604</v>
+        <v>-4.403539379774864</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.095608001399907</v>
+        <v>1.109367887800203</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4203108853972346</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.217918297738594</v>
+        <v>-4.183518581737854</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.185195357625326</v>
+        <v>1.198955244025621</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5615307304652148</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.085050608675316</v>
+        <v>-4.050650892674576</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.25423661605246</v>
+        <v>1.267996502452756</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5615307304652148</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.964877525310817</v>
+        <v>-3.930477809310077</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.303451693838561</v>
+        <v>1.317211580238857</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6817038138297138</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.82962416398084</v>
+        <v>-3.7952244479801</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.367641140931992</v>
+        <v>1.381401027332287</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8169571751596909</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.889498991338533</v>
+        <v>-3.855099275337793</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.329728701390341</v>
+        <v>1.343488587790636</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7570823478019988</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.769678760427695</v>
+        <v>-3.735279044426955</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.392945962988885</v>
+        <v>1.40670584938918</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7570823478019988</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.772148466889501</v>
+        <v>-3.737748750888761</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.299602279726604</v>
+        <v>1.313362166126899</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7546126413401926</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.840518653213511</v>
+        <v>-3.806118937212771</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191516066682301</v>
+        <v>1.205275953082596</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7638883403764075</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.952390932839662</v>
+        <v>-3.917991216838922</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.137203863463732</v>
+        <v>1.150963749864027</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7638883403764075</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.007911008732251</v>
+        <v>-3.973511292731511</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.252026669798899</v>
+        <v>1.265786556199194</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7638883403764075</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.832436748939782</v>
+        <v>-3.798037032939042</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.326783605707674</v>
+        <v>1.34054349210797</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7638883403764075</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.824512374354868</v>
+        <v>-3.790112658354128</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.305695384302847</v>
+        <v>1.319455270703142</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7638883403764075</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.818234171785019</v>
+        <v>-3.783834455784279</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.236744978732236</v>
+        <v>1.250504865132532</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7701665429462565</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.758381552581296</v>
+        <v>-3.723981836580556</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.270858412845858</v>
+        <v>1.284618299246153</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7701665429462565</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.672138089554918</v>
+        <v>-3.637738373554178</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.300302068630269</v>
+        <v>1.314061955030565</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7701665429462565</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.717444908953898</v>
+        <v>-3.683045192953158</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.273955116315203</v>
+        <v>1.287715002715498</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7293563799370257</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.7464780136562</v>
+        <v>-3.71207829765546</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.262893747467384</v>
+        <v>1.276653633867679</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7293563799370257</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.653667532205341</v>
+        <v>-3.619267816204601</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.229290631939093</v>
+        <v>1.243050518339389</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8221668613878851</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.698057001534768</v>
+        <v>-3.663657285534028</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.213408320131923</v>
+        <v>1.227168206532218</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7777773920584574</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.677553307649271</v>
+        <v>-3.643153591648531</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.216685506197845</v>
+        <v>1.23044539259814</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7982810859439547</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.717477402231843</v>
+        <v>-3.683077686231103</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.206207164195483</v>
+        <v>1.219967050595778</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.745257800133196</v>
+        <v>-3.710858084132456</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.206592206803481</v>
+        <v>1.220352093203776</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.863638472863335</v>
+        <v>-3.829238756862595</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.997595657712079</v>
+        <v>1.011355544112374</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.972252551306666</v>
+        <v>-3.937852835305926</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.074299687053952</v>
+        <v>1.088059573454248</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.936843513058523</v>
+        <v>-3.902443797057783</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.102976328455532</v>
+        <v>1.116736214855828</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.898459850500372</v>
+        <v>-3.864060134499632</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.115749234821161</v>
+        <v>1.129509121221457</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.721343520465206</v>
+        <v>-3.686943804464466</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.18332479568053</v>
+        <v>1.197084682080825</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.766435765298751</v>
+        <v>-3.732036049298011</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.165971289509025</v>
+        <v>1.17973117590932</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.587060344059983</v>
+        <v>-3.552660628059243</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.231508433310946</v>
+        <v>1.245268319711242</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.63207455758059</v>
+        <v>-3.597674841579849</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.194310203234293</v>
+        <v>1.208070089634589</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.899079067853025</v>
+        <v>-3.864679351852285</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.093199961464265</v>
+        <v>1.10695984786456</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.000276849290198</v>
+        <v>-3.965877133289458</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.051924770785897</v>
+        <v>1.065684657186193</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.993765882675885</v>
+        <v>-3.959366166675145</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.052129118985939</v>
+        <v>1.065889005386234</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.974727754968588</v>
+        <v>-3.940328038967848</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.056269089277103</v>
+        <v>1.070028975677398</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.027243557243408</v>
+        <v>-3.992843841242668</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.154557170001365</v>
+        <v>1.168317056401661</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.041110318577326</v>
+        <v>-4.006710602576585</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.149843794453931</v>
+        <v>1.163603680854227</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4473849384832159</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.000627326654982</v>
+        <v>-3.96622761065424</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.172045521619795</v>
+        <v>1.185805408020091</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4473849384832159</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.85288435641998</v>
+        <v>-3.818484640419238</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.129092930990996</v>
+        <v>1.142852817391291</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6151922957180991</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.936705577694678</v>
+        <v>-3.902305861693936</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.098358064012597</v>
+        <v>1.112117950412893</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6151922957180991</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.930552871641893</v>
+        <v>-3.896153155641152</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.10148149482537</v>
+        <v>1.115241381225665</v>
       </c>
       <c r="F1968" t="n">
         <v>0.6213450017708834</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.947362169792395</v>
+        <v>-3.912962453791653</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.093838252305279</v>
+        <v>1.107598138705575</v>
       </c>
       <c r="F1969" t="n">
         <v>0.6045357036203818</v>
@@ -46861,10 +46861,10 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.885064171016273</v>
+        <v>-3.850664455015532</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.185093005612549</v>
+        <v>1.198852892012845</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6498299678948238</v>
@@ -46884,10 +46884,10 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.683273973351115</v>
+        <v>-3.648874257350374</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.068101086392739</v>
+        <v>1.081860972793035</v>
       </c>
       <c r="F1971" t="n">
         <v>0.8478481600639782</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.73416068603731</v>
+        <v>-3.699760970036568</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.118036633640436</v>
+        <v>1.131796520040732</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7969614473777837</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.647549943387502</v>
+        <v>-3.613150227386761</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.167308666816403</v>
+        <v>1.181068553216699</v>
       </c>
       <c r="F1973" t="n">
         <v>0.875587178582942</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.707759241392787</v>
+        <v>-3.673359525392045</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.141760928438961</v>
+        <v>1.155520814839257</v>
       </c>
       <c r="F1974" t="n">
         <v>0.8153778805776575</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.658572592708436</v>
+        <v>-3.624172876707694</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.15992720595263</v>
+        <v>1.173687092352926</v>
       </c>
       <c r="F1975" t="n">
         <v>0.8153778805776575</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.614199461069867</v>
+        <v>-3.579799745069125</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.177539326043494</v>
+        <v>1.191299212443789</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8597510122162261</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.636679811928752</v>
+        <v>-3.60228009592801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.16294097983853</v>
+        <v>1.176700866238826</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8597510122162261</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.589024081367696</v>
+        <v>-3.554624365366955</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.188385029090757</v>
+        <v>1.202144915491053</v>
       </c>
       <c r="F1978" t="n">
         <v>0.9074067427772817</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.488505922868942</v>
+        <v>-3.4541062068682</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.233484665864984</v>
+        <v>1.247244552265279</v>
       </c>
       <c r="F1979" t="n">
         <v>1.007924901276036</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.472600593436589</v>
+        <v>-3.438200877435848</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.226601470113797</v>
+        <v>1.240361356514093</v>
       </c>
       <c r="F1980" t="n">
         <v>0.9288122405667973</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.427762191828191</v>
+        <v>-3.39336247582745</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.248634533367785</v>
+        <v>1.26239441976808</v>
       </c>
       <c r="F1981" t="n">
         <v>0.9333556735116668</v>
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.447260648070199</v>
+        <v>-3.329919960791916</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.244996090502059</v>
+        <v>1.291932365413372</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8852710322317625</v>
+        <v>0.9190609009675099</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.155419393382944</v>
+        <v>3.175693314624392</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.403057810984299</v>
+        <v>-3.285717123706016</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.268556827864257</v>
+        <v>1.315493102775569</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.929473869317663</v>
+        <v>0.9632637380534104</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.187820698162321</v>
+        <v>3.20809461940377</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.410617476821346</v>
+        <v>-3.293276789543063</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.263942961998685</v>
+        <v>1.310879236909998</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9842772733274823</v>
+        <v>1.01806714206323</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.219112741037461</v>
+        <v>3.239386662278909</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284874</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.252326059282074</v>
+        <v>-3.13498537200379</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.378507294197434</v>
+        <v>1.425443569108746</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9842772733274823</v>
+        <v>1.01806714206323</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.2703605062205</v>
+        <v>3.290634427461949</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.044684055647597</v>
+        <v>-2.927343368369314</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.460004800245478</v>
+        <v>1.50694107515679</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.191919276961958</v>
+        <v>1.225709145697706</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.393386412995439</v>
+        <v>3.413660334236888</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.993651962925069</v>
+        <v>-2.876311275646786</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.475365865572759</v>
+        <v>1.522302140484071</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.242951369684486</v>
+        <v>1.276741238420234</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.418953896867226</v>
+        <v>3.439227818108674</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.928427781797863</v>
+        <v>-2.81108709451958</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.518642942116346</v>
+        <v>1.565579217027659</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.308175550811692</v>
+        <v>1.341965419547439</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.475275809636254</v>
+        <v>3.495549730877702</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.89100076172673</v>
+        <v>-2.773660074448447</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.52957472244408</v>
+        <v>1.576510997355393</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.313427088840874</v>
+        <v>1.347216957576621</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.474387704753044</v>
+        <v>3.494661625994492</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.911112417761438</v>
+        <v>-2.793771730483155</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.522786852361437</v>
+        <v>1.569723127272749</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.324454433838293</v>
+        <v>1.35824430257404</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.482260904082735</v>
+        <v>3.502534825324184</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.882699154661554</v>
+        <v>-2.765358467383271</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.694709928622601</v>
+        <v>1.741646203533914</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.265478871091864</v>
+        <v>1.299268739827611</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.607433337456089</v>
+        <v>3.627707258697537</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.807916893636542</v>
+        <v>-2.690576206358259</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.844735742250424</v>
+        <v>1.891672017161736</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.340261132116877</v>
+        <v>1.374051000852624</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.772415603288914</v>
+        <v>3.792689524530362</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998749</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.781832809372734</v>
+        <v>-2.664492122094451</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.846877351969806</v>
+        <v>1.893813626881118</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.340261132116877</v>
+        <v>1.374051000852624</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.764123579302773</v>
+        <v>3.784397500544221</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.693954896263613</v>
+        <v>-2.57661420898533</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.880221712797233</v>
+        <v>1.927157987708546</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.456186774540228</v>
+        <v>1.489976643275975</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.831872160340563</v>
+        <v>3.852146081582011</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.68506243487033</v>
+        <v>-2.567721747592047</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.901333103081338</v>
+        <v>1.94826937799265</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.456186774540228</v>
+        <v>1.489976643275975</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.849426566067354</v>
+        <v>3.869700487308803</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.853538551840208</v>
+        <v>-2.736197864561924</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.825797703697971</v>
+        <v>1.872733978609283</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.428238938823647</v>
+        <v>1.462028807559394</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.824512912041989</v>
+        <v>3.844786833283438</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.407282359210768</v>
+        <v>-2.289941671932485</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.985569877937609</v>
+        <v>2.032506152848921</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.333520269154014</v>
+        <v>1.367310137889762</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.748951407428072</v>
+        <v>3.76922532866952</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.384561255527615</v>
+        <v>-2.267220568249332</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.985322341907774</v>
+        <v>2.032258616819087</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.333520269154014</v>
+        <v>1.367310137889762</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.739615429924976</v>
+        <v>3.759889351166425</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.513763068821658</v>
+        <v>-2.396422381543375</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.092547742441326</v>
+        <v>2.139484017352639</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.204318455859972</v>
+        <v>1.238108324595719</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.82100046779972</v>
+        <v>3.841274389041168</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.539637467295683</v>
+        <v>-2.4222967800174</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.119275805545363</v>
+        <v>2.166212080456675</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.249230064571713</v>
+        <v>1.283019933307461</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.885025255520411</v>
+        <v>3.90529917676186</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.53258277708051</v>
+        <v>-2.415242089802227</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.118773037620977</v>
+        <v>2.165709312532289</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.256284754786887</v>
+        <v>1.290074623522634</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.885933425639061</v>
+        <v>3.906207346880509</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.505631552754022</v>
+        <v>-2.388290865475739</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.139559680996314</v>
+        <v>2.186495955907626</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.271165100814606</v>
+        <v>1.304954969550354</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.904867786900434</v>
+        <v>3.925141708141882</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.527175780584809</v>
+        <v>-2.409835093306526</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.315045122008959</v>
+        <v>2.361981396920271</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.271165100814606</v>
+        <v>1.304954969550354</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.088970919045393</v>
+        <v>4.109244840286842</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.549583898389681</v>
+        <v>-2.432243211111398</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.298198569790003</v>
+        <v>2.345134844701316</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.271165100814606</v>
+        <v>1.304954969550354</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.081087613948386</v>
+        <v>4.101361535189835</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.577808133967281</v>
+        <v>-2.460467446688998</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.2889628751086</v>
+        <v>2.335899150019913</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.289141853265915</v>
+        <v>1.322931722001662</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.093927664968809</v>
+        <v>4.114201586210258</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.72945228516197</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.587249059855811</v>
+        <v>-2.469908372577528</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.341440222475036</v>
+        <v>2.388376497386348</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.411568970809306</v>
+        <v>1.445358839545054</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.223637653216691</v>
+        <v>4.243911574458139</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321627</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.676125691024285</v>
+        <v>-2.558785003746002</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.308780664552947</v>
+        <v>2.355716939464259</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.322692339640832</v>
+        <v>1.35648220837658</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.173202769060908</v>
+        <v>4.193476690302356</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.752455668625191</v>
+        <v>-2.635114981346908</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.27636048640636</v>
+        <v>2.323296761317672</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.322692339640832</v>
+        <v>1.35648220837658</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.171314581954683</v>
+        <v>4.191588503196131</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.846119613302732</v>
+        <v>-2.728778926024449</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.233715138138206</v>
+        <v>2.280651413049518</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.229028394963291</v>
+        <v>1.262818263699038</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10993644475102</v>
+        <v>4.130210365992469</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343059</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.007688038829988</v>
+        <v>-2.890347351551704</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.167521778137456</v>
+        <v>2.214458053048769</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.102245471165411</v>
+        <v>1.136035339901159</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.032300700682445</v>
+        <v>4.052574621923894</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389342</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.115988700700107</v>
+        <v>-2.998648013421824</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.137274920255327</v>
+        <v>2.184211195166639</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.102245471165411</v>
+        <v>1.136035339901159</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.045374107548364</v>
+        <v>4.065648028789812</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378385</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.133792672420851</v>
+        <v>-3.016451985142568</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.122158528349969</v>
+        <v>2.169094803261281</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.03171084826021</v>
+        <v>1.065500716995958</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.995058530588183</v>
+        <v>4.015332451829631</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006969</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.161693459530324</v>
+        <v>-3.044352772252041</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.109522254633182</v>
+        <v>2.156458529544494</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9971139241172757</v>
+        <v>1.030903792853023</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.972824417229424</v>
+        <v>3.993098338470872</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.284219562233218</v>
+        <v>-3.166878874954935</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.057276257529223</v>
+        <v>2.104212532440536</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8745878214143818</v>
+        <v>0.9083776901501293</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.896073199584887</v>
+        <v>3.916347120826335</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585932</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.514734058418807</v>
+        <v>-3.397393371140524</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.031776418645491</v>
+        <v>2.078712693556803</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6440733252287931</v>
+        <v>0.6778631939645405</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.824470461464037</v>
+        <v>3.844744382705485</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814659</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.863479143643251</v>
+        <v>-3.746138456364967</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.032590103557561</v>
+        <v>2.079526378468873</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.899533408114546</v>
+        <v>3.919807329355994</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.017465561419391</v>
+        <v>-3.900124874141108</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.039975805592745</v>
+        <v>2.086912080504057</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.968513677260185</v>
+        <v>3.988787598501633</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.966943657591725</v>
+        <v>-3.849602970313442</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.046235769243931</v>
+        <v>2.093172044155244</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.954564879380306</v>
+        <v>3.974838800621755</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.219418811599449</v>
+        <v>-4.102078124321166</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.957116196696256</v>
+        <v>2.004052471607568</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.96643536843572</v>
+        <v>3.986709289677169</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.512314568078861</v>
+        <v>-4.394973880800578</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.841168428623435</v>
+        <v>1.888104703534747</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5691152400456427</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.967645902954664</v>
+        <v>3.987919824196112</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.698978696213669</v>
+        <v>-4.581638008935387</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.770624519596833</v>
+        <v>1.817560794508145</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5085864004853354</v>
+        <v>0.5423762692210828</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.95572426268725</v>
+        <v>3.975998183928698</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916195</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.844999383127631</v>
+        <v>-4.727658695849349</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.707294097567437</v>
+        <v>1.75423037247875</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5332931774272258</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.945352260347125</v>
+        <v>3.965626181588573</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830322</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.936713392237216</v>
+        <v>-4.819372704958933</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.832812550622648</v>
+        <v>1.87974882553396</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5332931774272258</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.107556317046169</v>
+        <v>4.127830238287618</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071545</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.968365051297186</v>
+        <v>-4.851024364018903</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.814998524962474</v>
+        <v>1.861934799873787</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4943348514470383</v>
+        <v>0.5281247201827857</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.099301880663319</v>
+        <v>4.119575801904767</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.050299869566069</v>
+        <v>-4.932959182287786</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.792454015223412</v>
+        <v>1.839390290134724</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4844001058599581</v>
+        <v>0.5181899745957055</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.103570450879562</v>
+        <v>4.123844372121011</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.152275991814476</v>
+        <v>-5.034935304536194</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.760589204779951</v>
+        <v>1.807525479691264</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3824239836115505</v>
+        <v>0.4162138523472979</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.051310415986419</v>
+        <v>4.071584337227868</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.042269708337255</v>
+        <v>-4.924929021058972</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.796744605415015</v>
+        <v>1.843680880326328</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4056285555288257</v>
+        <v>0.4394184242645731</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.057386046380961</v>
+        <v>4.077659967622409</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.899210132596329</v>
+        <v>-4.781869445318046</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.85821844643336</v>
+        <v>1.905154721344672</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.413641982118805</v>
+        <v>0.4474318508545524</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.066444113056922</v>
+        <v>4.086718034298371</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.597763407124491</v>
+        <v>-4.480422719846208</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.986058019504631</v>
+        <v>2.032994294415944</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7488785763263897</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.25457303122256</v>
+        <v>4.274846952464009</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.638522500516944</v>
+        <v>3.64563575897759</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.622353651359675</v>
+        <v>-4.505012964081392</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789224615659327</v>
+        <v>1.843274149031285</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7488785763263897</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.06757572507133</v>
+        <v>4.094962904773424</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.6393654048967</v>
+        <v>3.646478663357345</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.571315275353155</v>
+        <v>-4.453974588074872</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810482870441691</v>
+        <v>1.864532403813648</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7488785763263897</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.068418629451085</v>
+        <v>4.095805809153179</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.658403503770845</v>
+        <v>3.665516762231491</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.530175980486524</v>
+        <v>-4.412835293208241</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.845976687262489</v>
+        <v>1.900026220634446</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7562280024572731</v>
+        <v>0.7900178711930205</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.11214030524521</v>
+        <v>4.139527484947303</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.47458749989478</v>
+        <v>3.481700758355425</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.433541068467884</v>
+        <v>-4.316200381189601</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.700814648193879</v>
+        <v>1.754864181565837</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.852862914475913</v>
+        <v>0.8866527832116604</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.986305248580328</v>
+        <v>4.013692428282422</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.478089543968744</v>
+        <v>3.485202802429389</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.564121802998726</v>
+        <v>-4.446781115720444</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.652084398455506</v>
+        <v>1.706133931827464</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7222821799450705</v>
+        <v>0.7560720486808179</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.911458851935786</v>
+        <v>3.93884603163788</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.462516363044826</v>
+        <v>3.469629621505471</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.399625468807765</v>
+        <v>-4.282284781529482</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702309751207973</v>
+        <v>1.756359284579931</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.9205683828717798</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.994583471526446</v>
+        <v>4.021970651228539</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.461704073481256</v>
+        <v>3.468817331941901</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.322526867265892</v>
+        <v>-4.205186179987609</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.732336902261152</v>
+        <v>1.786386435633109</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.9205683828717798</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.993771181962876</v>
+        <v>4.021158361664969</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.471572852606328</v>
+        <v>3.478686111066974</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.332912062155781</v>
+        <v>-4.215571374877499</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.738051603430268</v>
+        <v>1.792101136802226</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8763933192461431</v>
+        <v>0.9101831879818905</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.997408844154014</v>
+        <v>4.024796023856108</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.542409858382753</v>
+        <v>3.549523116843399</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.351500220878006</v>
+        <v>-4.234159533599724</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.801453345717804</v>
+        <v>1.855502879089761</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8578051605239176</v>
+        <v>0.8915950292596651</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.057092954697104</v>
+        <v>4.084480134399198</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.539278869201052</v>
+        <v>3.546392127661697</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.351798767574042</v>
+        <v>-4.234458080295759</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.798202937857688</v>
+        <v>1.852252471229646</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8575066138278817</v>
+        <v>0.8912964825636291</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.053782837497781</v>
+        <v>4.081170017199875</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.543809764140443</v>
+        <v>3.550923022601089</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.250975633883614</v>
+        <v>-4.133634946605332</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.84306308627325</v>
+        <v>1.897112619645208</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8699708293122356</v>
+        <v>0.903760698047983</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.065792261727785</v>
+        <v>4.093179441429879</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.543939017618987</v>
+        <v>3.551052276079632</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.060194273131208</v>
+        <v>-3.942853585852924</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.919504884052756</v>
+        <v>1.973554417424714</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.060752190064643</v>
+        <v>1.09454205880039</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.180390331657772</v>
+        <v>4.207777511359867</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.523775863356583</v>
+        <v>3.530889121817228</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.953230915281786</v>
+        <v>-3.835890228003502</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.942127072930122</v>
+        <v>1.99617660630208</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.119216798024445</v>
+        <v>1.153006666760192</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.195305942171251</v>
+        <v>4.222693121873344</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.558742799968642</v>
+        <v>3.565856058429287</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.897900327380024</v>
+        <v>-3.78055964010174</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.999226244702885</v>
+        <v>2.053275778074843</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.174547385926207</v>
+        <v>1.208337254661954</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.263471231524366</v>
+        <v>4.290858411226459</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.552429367870079</v>
+        <v>3.559542626330725</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.885846200467061</v>
+        <v>-3.768505513188777</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.997734463369508</v>
+        <v>2.051783996741466</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.186601512839169</v>
+        <v>1.220391381574917</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.264390275573581</v>
+        <v>4.291777455275675</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.554309998054215</v>
+        <v>3.56142325651486</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.927001320035282</v>
+        <v>-3.809660632756998</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.983153045726355</v>
+        <v>2.037202579098313</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.145446393270948</v>
+        <v>1.179236262006696</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.241577834016785</v>
+        <v>4.268965013718878</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.567161023932098</v>
+        <v>3.574274282392743</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.858952757343752</v>
+        <v>-3.741612070065468</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.02322349668085</v>
+        <v>2.077273030052807</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.295257997509585</v>
+        <v>4.322645177211679</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.587363694105692</v>
+        <v>3.594476952566337</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.090553150513253</v>
+        <v>-3.97321246323497</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.950786009586643</v>
+        <v>2.004835542958602</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.315460667683179</v>
+        <v>4.342847847385273</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.570969930172574</v>
+        <v>3.578083188633219</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.140604696042473</v>
+        <v>-4.023264008764189</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.914371627441837</v>
+        <v>1.968421160813796</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.299066903750061</v>
+        <v>4.326454083452155</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.531221843766041</v>
+        <v>3.538335102226686</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.315711528618918</v>
+        <v>-4.198370841340633</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.804580808004726</v>
+        <v>1.858630341376684</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.213494955962478</v>
+        <v>1.247284824698226</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.259318817343527</v>
+        <v>4.286705997045622</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.538244462762981</v>
+        <v>3.545357721223626</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.119611375188395</v>
+        <v>-4.00227068791011</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.890043488373875</v>
+        <v>1.944093021745834</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.409595109393001</v>
+        <v>1.443384978128749</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.384001528398781</v>
+        <v>4.411388708100875</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.637415462335885</v>
+        <v>3.64452872079653</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.966585983075111</v>
+        <v>-3.849245295796826</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.050424644792093</v>
+        <v>2.104474178164052</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.562620501506285</v>
+        <v>1.596410370242033</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.574987763239657</v>
+        <v>4.60237494294175</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.824881687244178</v>
+        <v>3.831994945704823</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.994893296948381</v>
+        <v>-3.877552609670096</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.226567944151078</v>
+        <v>2.280617477523037</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.562620501506285</v>
+        <v>1.596410370242033</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.762453988147949</v>
+        <v>4.789841167850042</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.79428463859826</v>
+        <v>3.801397897058906</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.161486522061903</v>
+        <v>-4.044145834783619</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.129333605459752</v>
+        <v>2.18338313883171</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.396027276392763</v>
+        <v>1.42981714512851</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.631901004433918</v>
+        <v>4.659288184136011</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.797961041259978</v>
+        <v>3.805074299720623</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.138450728700337</v>
+        <v>-4.021110041422053</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.142224325466096</v>
+        <v>2.196273858838054</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.396027276392763</v>
+        <v>1.42981714512851</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.635577407095636</v>
+        <v>4.662964586797729</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.795579096383473</v>
+        <v>3.802692354844118</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.109204748244641</v>
+        <v>-3.991864060966356</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.15154077277187</v>
+        <v>2.205590306143828</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.396027276392763</v>
+        <v>1.42981714512851</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.633195462219131</v>
+        <v>4.660582641921225</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.792872335541108</v>
+        <v>3.799985594001754</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.216130296122492</v>
+        <v>-4.098789608844208</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.106063792778365</v>
+        <v>2.160113326150322</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.289101728514912</v>
+        <v>1.322891597250659</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.566333372650055</v>
+        <v>4.593720552352149</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.794301137684343</v>
+        <v>3.801414396144988</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.36114885462974</v>
+        <v>-4.243808167351457</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.049485171518699</v>
+        <v>2.103534704890657</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.144083170007663</v>
+        <v>1.17787303874341</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.480751039688941</v>
+        <v>4.508138219391034</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.894232376942095</v>
+        <v>3.901345635402741</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.479490620414458</v>
+        <v>-4.362149933136174</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.102079704462565</v>
+        <v>2.156129237834523</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.587093902084428</v>
+        <v>4.614481081786521</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.892018074068035</v>
+        <v>3.89913133252868</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.530901042735166</v>
+        <v>-4.413560355456882</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.079301232660221</v>
+        <v>2.133350766032179</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.584879599210367</v>
+        <v>4.612266778912461</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.891921202142324</v>
+        <v>3.899034460602969</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.610320493942917</v>
+        <v>-4.492979806664634</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.047436580251409</v>
+        <v>2.101486113623368</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.584782727284656</v>
+        <v>4.612169906986749</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.891915095700367</v>
+        <v>3.899028354161012</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.705783491860135</v>
+        <v>-4.588442804581851</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.009245274642566</v>
+        <v>2.063294808014524</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.154769208570553</v>
+        <v>1.188559077306301</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.584776620842699</v>
+        <v>4.612163800544793</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.890011492262977</v>
+        <v>3.897124750723623</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.64140758100942</v>
+        <v>-4.524066893731137</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.033092035545462</v>
+        <v>2.08714156891742</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.219145119421268</v>
+        <v>1.252934988157016</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.621498563915739</v>
+        <v>4.648885743617832</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.895745310010704</v>
+        <v>3.902858568471349</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.696776743141614</v>
+        <v>-4.57943605586333</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.016678188440311</v>
+        <v>2.070727721812269</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.219145119421268</v>
+        <v>1.252934988157016</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.627232381663466</v>
+        <v>4.654619561365559</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.895283673353636</v>
+        <v>3.902396931814282</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.742214522972441</v>
+        <v>-4.624873835694157</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.998041439850913</v>
+        <v>2.052090973222871</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.601063750599502</v>
+        <v>4.628450930301596</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.915158066203955</v>
+        <v>3.9222713246646</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.654007688824863</v>
+        <v>-4.536667001546579</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.053198566360263</v>
+        <v>2.107248099732221</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.620938143449821</v>
+        <v>4.648325323151914</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.898858766728683</v>
+        <v>3.905972025189328</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.547972693619553</v>
+        <v>-4.43063200634127</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.079313264967114</v>
+        <v>2.133362798339072</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.604638843974548</v>
+        <v>4.632026023676642</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.901289716192729</v>
+        <v>3.908402974653374</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.364761030486458</v>
+        <v>-4.247420343208175</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.155028879684398</v>
+        <v>2.209078413056356</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.176300128743109</v>
+        <v>1.210089997478856</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.607069793438594</v>
+        <v>4.634456973140688</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.867080902040619</v>
+        <v>3.874194160501264</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.293039583472607</v>
+        <v>-4.175698896194324</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.149508644337828</v>
+        <v>2.203558177709787</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.248021575756959</v>
+        <v>1.281811444492707</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.615893847494795</v>
+        <v>4.643281027196888</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.81399664796179</v>
+        <v>3.821109906422436</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.270666557864901</v>
+        <v>-4.153325870586618</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.105373600502083</v>
+        <v>2.159423133874041</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.259277326869861</v>
+        <v>1.293067195605608</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.569563044083707</v>
+        <v>4.596950223785801</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.999194852847146</v>
+        <v>4.006308111307791</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.303682853775646</v>
+        <v>-4.186342166497362</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.27736528702314</v>
+        <v>2.331414820395098</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.189839950203109</v>
+        <v>1.223629818938857</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.713098822969012</v>
+        <v>4.740486002671106</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.991116078675395</v>
+        <v>3.99822933713604</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.292155218126037</v>
+        <v>-4.174814530847754</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.273897567111232</v>
+        <v>2.327947100483191</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.248840608404472</v>
+        <v>1.282630477140219</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.740420443718079</v>
+        <v>4.767807623420172</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.994784191197184</v>
+        <v>4.001897449657829</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.389496719468406</v>
+        <v>-4.272156032190122</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.238629079096074</v>
+        <v>2.292678612468032</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.204420426238983</v>
+        <v>1.238210294974731</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.717436446940574</v>
+        <v>4.744823626642668</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.996035273390022</v>
+        <v>4.003148531850667</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.475352748808373</v>
+        <v>-4.358012061530089</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.205537749552925</v>
+        <v>2.259587282924883</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.162044357012848</v>
+        <v>1.195834225748596</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.693261887597731</v>
+        <v>4.720649067299825</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.978454475210524</v>
+        <v>3.985567733671169</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.484189546224492</v>
+        <v>-4.366848858946208</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.18442223240698</v>
+        <v>2.238471765778938</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.154602184371498</v>
+        <v>1.188392053107245</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.671215785833422</v>
+        <v>4.698602965535516</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.988618986255573</v>
+        <v>3.995732244716218</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.575572108789951</v>
+        <v>-4.458231421511667</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.158033718425846</v>
+        <v>2.212083251797804</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.063219621806039</v>
+        <v>1.097009490541787</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.626550759339197</v>
+        <v>4.653937939041291</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.090747244079841</v>
+        <v>4.097860502540486</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.563865390802945</v>
+        <v>-4.446524703524661</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.264844663444916</v>
+        <v>2.318894196816874</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.074926339793046</v>
+        <v>1.108716208528793</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.735703047955669</v>
+        <v>4.763090227657763</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.093779582811246</v>
+        <v>4.100892841271891</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.464201886719282</v>
+        <v>-4.346861199440998</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.307742403809786</v>
+        <v>2.361791937181744</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.138113422996732</v>
+        <v>1.17190329173248</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.776647636609286</v>
+        <v>4.804034816311379</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.306684416089304</v>
+        <v>4.313797674549949</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.474517984885634</v>
+        <v>-4.35717729760735</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.516520797821303</v>
+        <v>2.570570331193261</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.138113422996732</v>
+        <v>1.17190329173248</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.989552469887344</v>
+        <v>5.016939649589437</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.305863083001394</v>
+        <v>4.312976341462039</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.474424016868261</v>
+        <v>-4.357083329589978</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.515737051940342</v>
+        <v>2.5697865853123</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.988953053607824</v>
+        <v>5.016340233309918</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.300095068945748</v>
+        <v>4.307208327406393</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.481642841068106</v>
+        <v>-4.364302153789822</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.507081508204758</v>
+        <v>2.561131041576716</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.983185039552178</v>
+        <v>5.010572219254271</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.300095068945748</v>
+        <v>4.307208327406393</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.480694417950067</v>
+        <v>-4.363353730671784</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.507460877451973</v>
+        <v>2.561510410823931</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.983185039552178</v>
+        <v>5.010572219254271</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.31282267692684</v>
+        <v>4.319935935387485</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.637762876205691</v>
+        <v>-4.520422188927407</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.457361102130815</v>
+        <v>2.511410635502774</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.99591264753327</v>
+        <v>5.023299827235364</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.314768675351227</v>
+        <v>4.321881933811873</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.63177062941688</v>
+        <v>-4.514429942138595</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.461703999270728</v>
+        <v>2.515753532642687</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.997858645957658</v>
+        <v>5.025245825659751</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,45 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.897017113655675</v>
+        <v>3.741942347149211</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.308422811368996</v>
+        <v>4.315536069829641</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.543212668286112</v>
+        <v>-4.518738178481166</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.490781319740804</v>
+        <v>2.507684374123427</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.13848328434405</v>
+        <v>1.172273153079798</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.991512781975427</v>
+        <v>5.01889996167752</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="2" t="n">
+        <v>45547</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>3.844758409525132</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>4.426764229990658</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>-4.518738178481166</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>2.507684374123427</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>1.172273153079798</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>4.419828026977026</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>131.0%</t>
+          <t>149.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-605.5%</t>
+          <t>-603.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.0%</t>
+          <t>427.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.4%</t>
+          <t>-602.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.6%</t>
+          <t>-241.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.5%</t>
+          <t>-102.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.8%</t>
+          <t>-323.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-106.8%</t>
+          <t>-110.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5415284190966594</v>
+        <v>-0.5179537032344321</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.904360970374315</v>
+        <v>2.913790856719206</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.530139182441858</v>
+        <v>-0.5065644665796307</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.906741461155476</v>
+        <v>2.916171347500367</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7826170768612639</v>
+        <v>-0.7590423609990367</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.803677194892777</v>
+        <v>2.813107081237667</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.072748743466695</v>
+        <v>-1.049174027604468</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.687490744849526</v>
+        <v>2.696920631194417</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.280752801819773</v>
+        <v>-1.257178085957545</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.60918126606222</v>
+        <v>2.618611152407111</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.342931212980743</v>
+        <v>-1.319356497118515</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.57939135793582</v>
+        <v>2.588821244280711</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.708999940125395</v>
+        <v>-1.685425224263168</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.426048166384408</v>
+        <v>2.435478052729299</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.91749072157708</v>
+        <v>-1.893916005714853</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.362990143542503</v>
+        <v>2.372420029887393</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.164691906342302</v>
+        <v>-2.141117190480075</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.272208420044982</v>
+        <v>2.281638306389874</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.657076934366399</v>
+        <v>-2.633502218504172</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.076360800879076</v>
+        <v>2.085790687223967</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.042257325296471</v>
+        <v>-3.018682609434244</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.92083118331991</v>
+        <v>1.930261069664801</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.292128005311053</v>
+        <v>-3.268553289448826</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.822652034768694</v>
+        <v>1.832081921113585</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.498639782198074</v>
+        <v>-3.475065066335847</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.736153382670143</v>
+        <v>1.745583269015034</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.817983857278576</v>
+        <v>-3.794409141416348</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.610188679338202</v>
+        <v>1.619618565683093</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.20419368855435</v>
+        <v>-4.180618972692123</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.442037634295296</v>
+        <v>1.451467520640187</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.438887682686903</v>
+        <v>-4.415312966824676</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.336444811644366</v>
+        <v>1.345874697989257</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.774550329917355</v>
+        <v>-4.750975614055128</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.20076034440815</v>
+        <v>1.210190230753041</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.850994660120227</v>
+        <v>-4.827419944258</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.176670172561243</v>
+        <v>1.186100058906134</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.216122042758974</v>
+        <v>-5.192547326896746</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.029873734511576</v>
+        <v>1.039303620856467</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.624710819939652</v>
+        <v>-5.601136104077424</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8651997676540635</v>
+        <v>0.8746296539989546</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.738471231962517</v>
+        <v>-5.714896516100289</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.814881035316378</v>
+        <v>0.8243109216612692</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.154863106249515</v>
+        <v>-6.131288390387287</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6463183362104563</v>
+        <v>0.6557482225553475</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.516036736066503</v>
+        <v>-6.492462020204274</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5121075749523403</v>
+        <v>0.5215374612972314</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.859295255709521</v>
+        <v>-6.835720539847293</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3709037322408277</v>
+        <v>0.3803336185857193</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.907498072951865</v>
+        <v>-6.883923357089637</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3500275253988914</v>
+        <v>0.3594574117437825</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.074306732926227</v>
+        <v>-7.050732017063999</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2870830373383546</v>
+        <v>0.2965129236832458</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.7822719436345955</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.26102644123553</v>
+        <v>-7.237451725373302</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2083688494802303</v>
+        <v>0.2177987358251219</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.7822719436345955</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.644027829978161</v>
+        <v>-7.620453114115933</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.05506619266159385</v>
+        <v>0.06449607900648502</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.7822719436345955</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.64851427517955</v>
+        <v>-7.624939559317322</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.0558431305524687</v>
+        <v>0.06527301689735987</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.7867583888359841</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.008044597683551</v>
+        <v>-7.984469881821323</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.08261869515108167</v>
+        <v>-0.0731888088061905</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.7867583888359841</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.058393661137771</v>
+        <v>-8.034818945275545</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.09484230057559273</v>
+        <v>-0.08541241423070156</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8371074522902062</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.156012938559167</v>
+        <v>-8.13243822269694</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1308482609223822</v>
+        <v>-0.1214183745774911</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9347267297116029</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.210084438067526</v>
+        <v>-8.186509722205299</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1495833044041537</v>
+        <v>-0.1401534180592625</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.9887982292199623</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.213660224159273</v>
+        <v>-8.190085508297047</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1455004217222102</v>
+        <v>-0.1360705353773191</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.014327151136455</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.247313062667747</v>
+        <v>-8.22373834680552</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1544790026411635</v>
+        <v>-0.1450491162962724</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.114740519053492</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.386399177286604</v>
+        <v>-8.362824461424378</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1947417469952857</v>
+        <v>-0.1853118606503941</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.253826633672349</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.561523594673147</v>
+        <v>-8.537948878810921</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2502362932023861</v>
+        <v>-0.2408064068574949</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.428951051058893</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.795975688687637</v>
+        <v>-8.772400972825411</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3512362957097781</v>
+        <v>-0.3418064093648865</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.428951051058893</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.900350419714083</v>
+        <v>-8.876775703851857</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3996583788943329</v>
+        <v>-0.3902284925494413</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.533325782085339</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.062863885412668</v>
+        <v>-9.039289169550441</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4635479753352101</v>
+        <v>-0.4541180889903189</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.630959212504025</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.188900678780957</v>
+        <v>-9.165325962918731</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5112689640534112</v>
+        <v>-0.50183907770852</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.605707589694283</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.131828906885026</v>
+        <v>-9.1082541910228</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4844499196086378</v>
+        <v>-0.4750200332637466</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.605707589694283</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.273500748609147</v>
+        <v>-9.24992603274692</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5425938831970276</v>
+        <v>-0.5331639968521364</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.605707589694283</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.223909904184312</v>
+        <v>-9.200335188322086</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5077041352622218</v>
+        <v>-0.4982742489173306</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.556116745269449</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.074991569712456</v>
+        <v>-9.051416853850229</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.461187935120162</v>
+        <v>-0.4517580487752708</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.524867154534276</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.849146416993046</v>
+        <v>-8.825571701130819</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3612708009961896</v>
+        <v>-0.3518409146512984</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.482940478947112</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.724567760655454</v>
+        <v>-8.700993044793227</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.310300193905094</v>
+        <v>-0.3008703075602024</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.482940478947112</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.699531079086944</v>
+        <v>-8.675956363224717</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.297651747115582</v>
+        <v>-0.2882218607706908</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.457611391396377</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.627397903799062</v>
+        <v>-8.603823187936836</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2630647727617932</v>
+        <v>-0.253634886416902</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.457611391396377</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.556031511189415</v>
+        <v>-8.532456795327189</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2442554781117994</v>
+        <v>-0.2348255917669082</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.386244998786729</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.462572477204191</v>
+        <v>-8.438997761341964</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2167553458306171</v>
+        <v>-0.2073254594857259</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.386244998786729</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.451919295650759</v>
+        <v>-8.428344579788533</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2143286337086185</v>
+        <v>-0.2048987473637269</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.386244998786729</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.354012256974269</v>
+        <v>-8.330437541112042</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1754661332114829</v>
+        <v>-0.1660362468665917</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.318259248926172</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.330058715998311</v>
+        <v>-8.306484000136084</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1652162106756063</v>
+        <v>-0.1557863243307147</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.294305707950215</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.065998777675514</v>
+        <v>-8.042424061813287</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.07285255150823966</v>
+        <v>-0.06342266516334849</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.030245769627419</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.358919154170676</v>
+        <v>-7.335344438308449</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2071922642333948</v>
+        <v>0.2166221505782859</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.030245769627419</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.318734855804485</v>
+        <v>-7.295160139942259</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2236096074677123</v>
+        <v>0.2330394938126035</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9900614712612278</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.155334984865123</v>
+        <v>-7.131760269002896</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2883363770642142</v>
+        <v>0.2977662634091054</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.8266616003218653</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.921853762635524</v>
+        <v>-6.898279046773298</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3896532947939062</v>
+        <v>0.3990831811387974</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5931803780922668</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.772187371628009</v>
+        <v>-6.748612655765783</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4466276408839529</v>
+        <v>0.4560575272288441</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.5002768868497308</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.639911897997123</v>
+        <v>-6.616337182134896</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.400798616343462</v>
+        <v>0.4102285026883536</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.3680014132188442</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.46805068243222</v>
+        <v>-6.444475966569994</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4723581632570601</v>
+        <v>0.4817880496019513</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1961401976539413</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.383086015702901</v>
+        <v>-6.359511299840674</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5192503711724465</v>
+        <v>0.5286802575173377</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.1111755309246217</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.488676005476005</v>
+        <v>-6.465101289613779</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3490384456639859</v>
+        <v>0.3584683320088771</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.2167655206977261</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.420441420850578</v>
+        <v>-6.396866704988351</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4248766213912432</v>
+        <v>0.4343065077361343</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1983501978251901</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.272501379442978</v>
+        <v>-6.248926663580752</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3674318293158758</v>
+        <v>0.376861715660767</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1780292819166325</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.21953185718899</v>
+        <v>-6.195957141326764</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.379905651963993</v>
+        <v>0.3893355383088846</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.1250597596626437</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.053743661228699</v>
+        <v>-6.030168945366473</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4392603182530164</v>
+        <v>0.4486902045979075</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.1250597596626437</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.02038045474993</v>
+        <v>-5.996805738887704</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4670679552256667</v>
+        <v>0.4764978415705583</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.1250597596626437</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.912121317627409</v>
+        <v>-5.888546601765182</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5049037305338708</v>
+        <v>0.514333616878762</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.1250597596626437</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.788830182810278</v>
+        <v>-5.765255466948052</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5517182784712999</v>
+        <v>0.5611481648161911</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.001768624845513156</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.736133315678987</v>
+        <v>-5.71255859981676</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5804980035611416</v>
+        <v>0.5899278899060327</v>
       </c>
       <c r="F1916" t="n">
         <v>0.05092824228577802</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.571030944944226</v>
+        <v>-5.468793157833316</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6423196602020962</v>
+        <v>0.6832147750464612</v>
       </c>
       <c r="F1917" t="n">
         <v>0.05092824228577802</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.481255272567754</v>
+        <v>-5.379017485456844</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6803542430727014</v>
+        <v>0.721249357917066</v>
       </c>
       <c r="F1918" t="n">
         <v>0.112527687200088</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.23140487861868</v>
+        <v>-5.129167091507769</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7730364756360331</v>
+        <v>0.8139315904803981</v>
       </c>
       <c r="F1919" t="n">
         <v>0.112527687200088</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.055512786151247</v>
+        <v>-4.953274999040337</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8469924361436547</v>
+        <v>0.8878875509880197</v>
       </c>
       <c r="F1920" t="n">
         <v>0.112527687200088</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.884066323128784</v>
+        <v>-4.781828536017874</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9288985274071939</v>
+        <v>0.9697936422515587</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2839741502225512</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.804044036019663</v>
+        <v>-4.701806248908753</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9599279198671393</v>
+        <v>1.000823034711504</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3639964373316721</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.740408293785729</v>
+        <v>-4.638170506674818</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9900770178150302</v>
+        <v>1.030972132659395</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4276321795656067</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.646710975569333</v>
+        <v>-4.544473188458423</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.008750203885384</v>
+        <v>1.049645318729749</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4276321795656067</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.657213598634622</v>
+        <v>-4.554975811523712</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.006292231284146</v>
+        <v>1.047187346128511</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4171295565003178</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.544727337965748</v>
+        <v>-4.442489550854837</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.055216049386516</v>
+        <v>1.096111164230881</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4171295565003178</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.527013651087882</v>
+        <v>-4.424775863976972</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.062980108055002</v>
+        <v>1.103875222899367</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4203108853972346</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.403539379774864</v>
+        <v>-4.301301592663954</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.109367887800203</v>
+        <v>1.150263002644567</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4203108853972346</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.183518581737854</v>
+        <v>-4.081280794626943</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.198955244025621</v>
+        <v>1.239850358869986</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5615307304652148</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.050650892674576</v>
+        <v>-3.948413105563665</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.267996502452756</v>
+        <v>1.308891617297121</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5615307304652148</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.930477809310077</v>
+        <v>-3.828240022199166</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.317211580238857</v>
+        <v>1.358106695083222</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6817038138297138</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.7952244479801</v>
+        <v>-3.692986660869189</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.381401027332287</v>
+        <v>1.422296142176653</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8169571751596909</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.855099275337793</v>
+        <v>-3.752861488226881</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.343488587790636</v>
+        <v>1.384383702635002</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7570823478019988</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.735279044426955</v>
+        <v>-3.633041257316044</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.40670584938918</v>
+        <v>1.447600964233545</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7570823478019988</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.737748750888761</v>
+        <v>-3.63551096377785</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.313362166126899</v>
+        <v>1.354257280971264</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7546126413401926</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.806118937212771</v>
+        <v>-3.70388115010186</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.205275953082596</v>
+        <v>1.246171067926962</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7638883403764075</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.917991216838922</v>
+        <v>-3.81575342972801</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.150963749864027</v>
+        <v>1.191858864708393</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7638883403764075</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.973511292731511</v>
+        <v>-3.8712735056206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.265786556199194</v>
+        <v>1.306681671043559</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7638883403764075</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.798037032939042</v>
+        <v>-3.695799245828131</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.34054349210797</v>
+        <v>1.381438606952335</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7638883403764075</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.790112658354128</v>
+        <v>-3.687874871243217</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.319455270703142</v>
+        <v>1.360350385547508</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7638883403764075</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.783834455784279</v>
+        <v>-3.681596668673368</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.250504865132532</v>
+        <v>1.291399979976897</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7701665429462565</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.723981836580556</v>
+        <v>-3.621744049469644</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.284618299246153</v>
+        <v>1.325513414090518</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7701665429462565</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.637738373554178</v>
+        <v>-3.535500586443267</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.314061955030565</v>
+        <v>1.35495706987493</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7701665429462565</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.683045192953158</v>
+        <v>-3.580807405842247</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.287715002715498</v>
+        <v>1.328610117559863</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7293563799370257</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.71207829765546</v>
+        <v>-3.609840510544549</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.276653633867679</v>
+        <v>1.317548748712044</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7293563799370257</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.619267816204601</v>
+        <v>-3.517030029093689</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.243050518339389</v>
+        <v>1.283945633183754</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8221668613878851</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.663657285534028</v>
+        <v>-3.561419498423117</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.227168206532218</v>
+        <v>1.268063321376584</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7777773920584574</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.643153591648531</v>
+        <v>-3.54091580453762</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.23044539259814</v>
+        <v>1.271340507442505</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7982810859439547</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.683077686231103</v>
+        <v>-3.580839899120192</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.219967050595778</v>
+        <v>1.260862165440144</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.710858084132456</v>
+        <v>-3.608620297021545</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.220352093203776</v>
+        <v>1.261247208048142</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.829238756862595</v>
+        <v>-3.727000969751683</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.011355544112374</v>
+        <v>1.05225065895674</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.937852835305926</v>
+        <v>-3.835615048195014</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.088059573454248</v>
+        <v>1.128954688298613</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.902443797057783</v>
+        <v>-3.800206009946872</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.116736214855828</v>
+        <v>1.157631329700193</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.864060134499632</v>
+        <v>-3.76182234738872</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.129509121221457</v>
+        <v>1.170404236065822</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.686943804464466</v>
+        <v>-3.584706017353554</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.197084682080825</v>
+        <v>1.23797979692519</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.732036049298011</v>
+        <v>-3.6297982621871</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.17973117590932</v>
+        <v>1.220626290753685</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.552660628059243</v>
+        <v>-3.450422840948332</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.245268319711242</v>
+        <v>1.286163434555607</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.597674841579849</v>
+        <v>-3.495437054468938</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.208070089634589</v>
+        <v>1.248965204478954</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.864679351852285</v>
+        <v>-3.762441564741374</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.10695984786456</v>
+        <v>1.147854962708926</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.965877133289458</v>
+        <v>-3.863639346178546</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.065684657186193</v>
+        <v>1.106579772030558</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.959366166675145</v>
+        <v>-3.857128379564234</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.065889005386234</v>
+        <v>1.1067841202306</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.940328038967848</v>
+        <v>-3.838090251856936</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.070028975677398</v>
+        <v>1.110924090521763</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.992843841242668</v>
+        <v>-3.890606054131756</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.168317056401661</v>
+        <v>1.209212171246026</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.006710602576585</v>
+        <v>-3.904472815465674</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.163603680854227</v>
+        <v>1.204498795698592</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4473849384832159</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.96622761065424</v>
+        <v>-3.863989823543329</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.185805408020091</v>
+        <v>1.226700522864456</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4473849384832159</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.818484640419238</v>
+        <v>-3.716246853308327</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.142852817391291</v>
+        <v>1.183747932235657</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6151922957180991</v>
@@ -46792,10 +46792,10 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.902305861693936</v>
+        <v>-3.800068074583025</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.112117950412893</v>
+        <v>1.153013065257258</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6151922957180991</v>
@@ -46815,10 +46815,10 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.896153155641152</v>
+        <v>-3.793915368530241</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.115241381225665</v>
+        <v>1.15613649607003</v>
       </c>
       <c r="F1968" t="n">
         <v>0.6213450017708834</v>
@@ -46838,10 +46838,10 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.912962453791653</v>
+        <v>-3.810724666680742</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.107598138705575</v>
+        <v>1.14849325354994</v>
       </c>
       <c r="F1969" t="n">
         <v>0.6045357036203818</v>
@@ -46861,10 +46861,10 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.850664455015532</v>
+        <v>-3.74842666790462</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.198852892012845</v>
+        <v>1.23974800685721</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6498299678948238</v>
@@ -46884,10 +46884,10 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.648874257350374</v>
+        <v>-3.546636470239462</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.081860972793035</v>
+        <v>1.1227560876374</v>
       </c>
       <c r="F1971" t="n">
         <v>0.8478481600639782</v>
@@ -46907,10 +46907,10 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.699760970036568</v>
+        <v>-3.597523182925657</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.131796520040732</v>
+        <v>1.172691634885097</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7969614473777837</v>
@@ -46930,10 +46930,10 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.613150227386761</v>
+        <v>-3.51091244027585</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.181068553216699</v>
+        <v>1.221963668061064</v>
       </c>
       <c r="F1973" t="n">
         <v>0.875587178582942</v>
@@ -46953,10 +46953,10 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.673359525392045</v>
+        <v>-3.571121738281134</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.155520814839257</v>
+        <v>1.196415929683622</v>
       </c>
       <c r="F1974" t="n">
         <v>0.8153778805776575</v>
@@ -46976,10 +46976,10 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.624172876707694</v>
+        <v>-3.521935089596783</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.173687092352926</v>
+        <v>1.214582207197291</v>
       </c>
       <c r="F1975" t="n">
         <v>0.8153778805776575</v>
@@ -46999,10 +46999,10 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.579799745069125</v>
+        <v>-3.477561957958214</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.191299212443789</v>
+        <v>1.232194327288155</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8597510122162261</v>
@@ -47022,10 +47022,10 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.60228009592801</v>
+        <v>-3.500042308817099</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.176700866238826</v>
+        <v>1.217595981083191</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8597510122162261</v>
@@ -47045,10 +47045,10 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.554624365366955</v>
+        <v>-3.452386578256044</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.202144915491053</v>
+        <v>1.243040030335418</v>
       </c>
       <c r="F1978" t="n">
         <v>0.9074067427772817</v>
@@ -47068,10 +47068,10 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.4541062068682</v>
+        <v>-3.351868419757289</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.247244552265279</v>
+        <v>1.288139667109645</v>
       </c>
       <c r="F1979" t="n">
         <v>1.007924901276036</v>
@@ -47091,10 +47091,10 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.438200877435848</v>
+        <v>-3.335963090324936</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.240361356514093</v>
+        <v>1.281256471358458</v>
       </c>
       <c r="F1980" t="n">
         <v>0.9288122405667973</v>
@@ -47114,10 +47114,10 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.39336247582745</v>
+        <v>-3.291124688716538</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.26239441976808</v>
+        <v>1.303289534612446</v>
       </c>
       <c r="F1981" t="n">
         <v>0.9333556735116668</v>
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.329919960791916</v>
+        <v>-3.310623144958547</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.291932365413372</v>
+        <v>1.29965109174672</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9190609009675099</v>
+        <v>0.8852710322317625</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.175693314624392</v>
+        <v>3.155419393382944</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.285717123706016</v>
+        <v>-3.266420307872646</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.315493102775569</v>
+        <v>1.323211829108918</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9632637380534104</v>
+        <v>0.929473869317663</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.20809461940377</v>
+        <v>3.187820698162321</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.293276789543063</v>
+        <v>-3.273979973709693</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.310879236909998</v>
+        <v>1.318597963243346</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.01806714206323</v>
+        <v>0.9842772733274823</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.239386662278909</v>
+        <v>3.219112741037461</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.13498537200379</v>
+        <v>-3.115688556170421</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.425443569108746</v>
+        <v>1.433162295442095</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.01806714206323</v>
+        <v>0.9842772733274823</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.290634427461949</v>
+        <v>3.2703605062205</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.927343368369314</v>
+        <v>-2.908046552535945</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.50694107515679</v>
+        <v>1.514659801490139</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.225709145697706</v>
+        <v>1.191919276961958</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.413660334236888</v>
+        <v>3.393386412995439</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.876311275646786</v>
+        <v>-2.857014459813417</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.522302140484071</v>
+        <v>1.53002086681742</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.276741238420234</v>
+        <v>1.242951369684486</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.439227818108674</v>
+        <v>3.418953896867226</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.81108709451958</v>
+        <v>-2.791790278686211</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.565579217027659</v>
+        <v>1.573297943361007</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.341965419547439</v>
+        <v>1.308175550811692</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.495549730877702</v>
+        <v>3.475275809636254</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.773660074448447</v>
+        <v>-2.754363258615077</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.576510997355393</v>
+        <v>1.584229723688741</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.347216957576621</v>
+        <v>1.313427088840874</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.494661625994492</v>
+        <v>3.474387704753044</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.793771730483155</v>
+        <v>-2.774474914649785</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.569723127272749</v>
+        <v>1.577441853606098</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.35824430257404</v>
+        <v>1.324454433838293</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.502534825324184</v>
+        <v>3.482260904082735</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.765358467383271</v>
+        <v>-2.746061651549902</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.741646203533914</v>
+        <v>1.749364929867262</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.299268739827611</v>
+        <v>1.265478871091864</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.627707258697537</v>
+        <v>3.607433337456089</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.690576206358259</v>
+        <v>-2.671279390524889</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.891672017161736</v>
+        <v>1.899390743495085</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.374051000852624</v>
+        <v>1.340261132116877</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.792689524530362</v>
+        <v>3.772415603288914</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.664492122094451</v>
+        <v>-2.645195306261081</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.893813626881118</v>
+        <v>1.901532353214467</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.374051000852624</v>
+        <v>1.340261132116877</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.784397500544221</v>
+        <v>3.764123579302773</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.57661420898533</v>
+        <v>-2.557317393151961</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.927157987708546</v>
+        <v>1.934876714041894</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.489976643275975</v>
+        <v>1.456186774540228</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.852146081582011</v>
+        <v>3.831872160340563</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.567721747592047</v>
+        <v>-2.548424931758677</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.94826937799265</v>
+        <v>1.955988104325999</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.489976643275975</v>
+        <v>1.456186774540228</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.869700487308803</v>
+        <v>3.849426566067354</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.736197864561924</v>
+        <v>-2.716901048728555</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.872733978609283</v>
+        <v>1.880452704942632</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.462028807559394</v>
+        <v>1.428238938823647</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.844786833283438</v>
+        <v>3.824512912041989</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.289941671932485</v>
+        <v>-2.270644856099115</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.032506152848921</v>
+        <v>2.040224879182269</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.367310137889762</v>
+        <v>1.333520269154014</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.76922532866952</v>
+        <v>3.748951407428072</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.267220568249332</v>
+        <v>-2.247923752415963</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.032258616819087</v>
+        <v>2.039977343152435</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.367310137889762</v>
+        <v>1.333520269154014</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.759889351166425</v>
+        <v>3.739615429924976</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.396422381543375</v>
+        <v>-2.377125565710005</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.139484017352639</v>
+        <v>2.147202743685988</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.238108324595719</v>
+        <v>1.204318455859972</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.841274389041168</v>
+        <v>3.82100046779972</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.4222967800174</v>
+        <v>-2.402999964184031</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.166212080456675</v>
+        <v>2.173930806790024</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.283019933307461</v>
+        <v>1.249230064571713</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.90529917676186</v>
+        <v>3.885025255520411</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.415242089802227</v>
+        <v>-2.395945273968857</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.165709312532289</v>
+        <v>2.173428038865638</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.290074623522634</v>
+        <v>1.256284754786887</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.906207346880509</v>
+        <v>3.885933425639061</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.388290865475739</v>
+        <v>-2.368994049642369</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.186495955907626</v>
+        <v>2.194214682240975</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.304954969550354</v>
+        <v>1.271165100814606</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.925141708141882</v>
+        <v>3.904867786900434</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.409835093306526</v>
+        <v>-2.390538277473156</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.361981396920271</v>
+        <v>2.36970012325362</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.304954969550354</v>
+        <v>1.271165100814606</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.109244840286842</v>
+        <v>4.088970919045393</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.432243211111398</v>
+        <v>-2.412946395278028</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.345134844701316</v>
+        <v>2.352853571034664</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.304954969550354</v>
+        <v>1.271165100814606</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.101361535189835</v>
+        <v>4.081087613948386</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.460467446688998</v>
+        <v>-2.441170630855629</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.335899150019913</v>
+        <v>2.343617876353261</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.322931722001662</v>
+        <v>1.289141853265915</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.114201586210258</v>
+        <v>4.093927664968809</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.469908372577528</v>
+        <v>-2.450611556744159</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.388376497386348</v>
+        <v>2.396095223719696</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.445358839545054</v>
+        <v>1.411568970809306</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.243911574458139</v>
+        <v>4.223637653216691</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.558785003746002</v>
+        <v>-2.539488187912633</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.355716939464259</v>
+        <v>2.363435665797608</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.35648220837658</v>
+        <v>1.322692339640832</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.193476690302356</v>
+        <v>4.173202769060908</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.635114981346908</v>
+        <v>-2.615818165513538</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.323296761317672</v>
+        <v>2.331015487651021</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.35648220837658</v>
+        <v>1.322692339640832</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.191588503196131</v>
+        <v>4.171314581954683</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.728778926024449</v>
+        <v>-2.70948211019108</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.280651413049518</v>
+        <v>2.288370139382867</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.262818263699038</v>
+        <v>1.229028394963291</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.130210365992469</v>
+        <v>4.10993644475102</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.890347351551704</v>
+        <v>-2.871050535718335</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.214458053048769</v>
+        <v>2.222176779382117</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.136035339901159</v>
+        <v>1.102245471165411</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.052574621923894</v>
+        <v>4.032300700682445</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.998648013421824</v>
+        <v>-2.979351197588454</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.184211195166639</v>
+        <v>2.191929921499987</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.136035339901159</v>
+        <v>1.102245471165411</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.065648028789812</v>
+        <v>4.045374107548364</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.016451985142568</v>
+        <v>-2.997155169309198</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.169094803261281</v>
+        <v>2.17681352959463</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.065500716995958</v>
+        <v>1.03171084826021</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.015332451829631</v>
+        <v>3.995058530588183</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.044352772252041</v>
+        <v>-3.025055956418671</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.156458529544494</v>
+        <v>2.164177255877843</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.030903792853023</v>
+        <v>0.9971139241172757</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.993098338470872</v>
+        <v>3.972824417229424</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.166878874954935</v>
+        <v>-3.147582059121565</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.104212532440536</v>
+        <v>2.111931258773884</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9083776901501293</v>
+        <v>0.8745878214143818</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.916347120826335</v>
+        <v>3.896073199584887</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585932</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.397393371140524</v>
+        <v>-3.378096555307154</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.078712693556803</v>
+        <v>2.086431419890152</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6778631939645405</v>
+        <v>0.6440733252287931</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.844744382705485</v>
+        <v>3.824470461464037</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.746138456364967</v>
+        <v>-3.726841640531598</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.079526378468873</v>
+        <v>2.087245104802221</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.919807329355994</v>
+        <v>3.899533408114546</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.900124874141108</v>
+        <v>-3.880828058307738</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.086912080504057</v>
+        <v>2.094630806837405</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.988787598501633</v>
+        <v>3.968513677260185</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.849602970313442</v>
+        <v>-3.830306154480073</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.093172044155244</v>
+        <v>2.100890770488593</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.974838800621755</v>
+        <v>3.954564879380306</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.102078124321166</v>
+        <v>-4.082781308487797</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.004052471607568</v>
+        <v>2.011771197940917</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.986709289677169</v>
+        <v>3.96643536843572</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.394973880800578</v>
+        <v>-4.375677064967209</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.888104703534747</v>
+        <v>1.895823429868096</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5691152400456427</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.987919824196112</v>
+        <v>3.967645902954664</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.581638008935387</v>
+        <v>-4.562341193102017</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.817560794508145</v>
+        <v>1.825279520841494</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5423762692210828</v>
+        <v>0.5085864004853354</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.975998183928698</v>
+        <v>3.95572426268725</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.727658695849349</v>
+        <v>-4.708361880015979</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.75423037247875</v>
+        <v>1.761949098812098</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5332931774272258</v>
+        <v>0.4995033086914784</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.965626181588573</v>
+        <v>3.945352260347125</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.819372704958933</v>
+        <v>-4.800075889125564</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.87974882553396</v>
+        <v>1.887467551867309</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5332931774272258</v>
+        <v>0.4995033086914784</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.127830238287618</v>
+        <v>4.107556317046169</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.851024364018903</v>
+        <v>-4.831727548185533</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.861934799873787</v>
+        <v>1.869653526207135</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5281247201827857</v>
+        <v>0.4943348514470383</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.119575801904767</v>
+        <v>4.099301880663319</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.932959182287786</v>
+        <v>-4.913662366454417</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.839390290134724</v>
+        <v>1.847109016468073</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5181899745957055</v>
+        <v>0.4844001058599581</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.123844372121011</v>
+        <v>4.103570450879562</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.034935304536194</v>
+        <v>-5.015638488702824</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.807525479691264</v>
+        <v>1.815244206024612</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4162138523472979</v>
+        <v>0.3824239836115505</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.071584337227868</v>
+        <v>4.051310415986419</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.924929021058972</v>
+        <v>-4.905632205225603</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.843680880326328</v>
+        <v>1.851399606659676</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4394184242645731</v>
+        <v>0.4056285555288257</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.077659967622409</v>
+        <v>4.057386046380961</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.781869445318046</v>
+        <v>-4.762572629484676</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.905154721344672</v>
+        <v>1.912873447678021</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4474318508545524</v>
+        <v>0.413641982118805</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.086718034298371</v>
+        <v>4.066444113056922</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.480422719846208</v>
+        <v>-4.461125904012839</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.032994294415944</v>
+        <v>2.040713020749292</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7488785763263897</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.274846952464009</v>
+        <v>4.25457303122256</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.64563575897759</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.505012964081392</v>
+        <v>-4.485716148248023</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.843274149031285</v>
+        <v>2.031848100807929</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7488785763263897</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.094962904773424</v>
+        <v>4.255544208975271</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.646478663357345</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.453974588074872</v>
+        <v>-4.434677772241503</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.864532403813648</v>
+        <v>2.053106355590293</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7488785763263897</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.095805809153179</v>
+        <v>4.256387113355027</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.665516762231491</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.412835293208241</v>
+        <v>-4.393538477374872</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.900026220634446</v>
+        <v>2.08860017241109</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7900178711930205</v>
+        <v>0.7562280024572731</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.139527484947303</v>
+        <v>4.30010878914915</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.481700758355425</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.316200381189601</v>
+        <v>-4.296903565356232</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.754864181565837</v>
+        <v>1.943438133342481</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8866527832116604</v>
+        <v>0.852862914475913</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.013692428282422</v>
+        <v>4.174273732484269</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.485202802429389</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.446781115720444</v>
+        <v>-4.427484299887074</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.706133931827464</v>
+        <v>1.894707883604108</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7560720486808179</v>
+        <v>0.7222821799450705</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.93884603163788</v>
+        <v>4.099427335839728</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.469629621505471</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.282284781529482</v>
+        <v>-4.262987965696112</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.756359284579931</v>
+        <v>1.944933236356575</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9205683828717798</v>
+        <v>0.8867785141360324</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.021970651228539</v>
+        <v>4.182551955430387</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.468817331941901</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.205186179987609</v>
+        <v>-4.18588936415424</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.786386435633109</v>
+        <v>1.974960387409754</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9205683828717798</v>
+        <v>0.8867785141360324</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.021158361664969</v>
+        <v>4.181739665866817</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.478686111066974</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.215571374877499</v>
+        <v>-4.196274559044129</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.792101136802226</v>
+        <v>1.980675088578871</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9101831879818905</v>
+        <v>0.8763933192461431</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.024796023856108</v>
+        <v>4.185377328057956</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.549523116843399</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.234159533599724</v>
+        <v>-4.214862717766354</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.855502879089761</v>
+        <v>2.044076830866406</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8915950292596651</v>
+        <v>0.8578051605239176</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.084480134399198</v>
+        <v>4.245061438601046</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.546392127661697</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.234458080295759</v>
+        <v>-4.21516126446239</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.852252471229646</v>
+        <v>2.04082642300629</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8912964825636291</v>
+        <v>0.8575066138278817</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.081170017199875</v>
+        <v>4.241751321401723</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.550923022601089</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.133634946605332</v>
+        <v>-4.114338130771962</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.897112619645208</v>
+        <v>2.085686571421853</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.903760698047983</v>
+        <v>0.8699708293122356</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.093179441429879</v>
+        <v>4.253760745631727</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.551052276079632</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.942853585852924</v>
+        <v>-3.923556770019555</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.973554417424714</v>
+        <v>2.162128369201359</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.09454205880039</v>
+        <v>1.060752190064643</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.207777511359867</v>
+        <v>4.368358815561714</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.530889121817228</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.835890228003502</v>
+        <v>-3.816593412170133</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.99617660630208</v>
+        <v>2.184750558078724</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.153006666760192</v>
+        <v>1.119216798024445</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.222693121873344</v>
+        <v>4.383274426075191</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.565856058429287</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.78055964010174</v>
+        <v>-3.761262824268371</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.053275778074843</v>
+        <v>2.241849729851487</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.208337254661954</v>
+        <v>1.174547385926207</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.290858411226459</v>
+        <v>4.451439715428307</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.559542626330725</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.768505513188777</v>
+        <v>-3.749208697355408</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.051783996741466</v>
+        <v>2.240357948518111</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.220391381574917</v>
+        <v>1.186601512839169</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.291777455275675</v>
+        <v>4.452358759477523</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.56142325651486</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.809660632756998</v>
+        <v>-3.790363816923629</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.037202579098313</v>
+        <v>2.225776530874958</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.179236262006696</v>
+        <v>1.145446393270948</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.268965013718878</v>
+        <v>4.429546317920726</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.574274282392743</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.741612070065468</v>
+        <v>-3.722315254232099</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.077273030052807</v>
+        <v>2.265846981829452</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.322645177211679</v>
+        <v>4.483226481413526</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.594476952566337</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.97321246323497</v>
+        <v>-3.9539156474016</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.004835542958602</v>
+        <v>2.193409494735246</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.342847847385273</v>
+        <v>4.50342915158712</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.578083188633219</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.023264008764189</v>
+        <v>-4.003967192930819</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.968421160813796</v>
+        <v>2.15699511259044</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.326454083452155</v>
+        <v>4.487035387654003</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.538335102226686</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.198370841340633</v>
+        <v>-4.179074025507264</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.858630341376684</v>
+        <v>2.047204293153329</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.247284824698226</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.286705997045622</v>
+        <v>4.447287301247469</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.545357721223626</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.00227068791011</v>
+        <v>-3.982973872076741</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.944093021745834</v>
+        <v>2.132666973522478</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.443384978128749</v>
+        <v>1.409595109393001</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.411388708100875</v>
+        <v>4.571970012302723</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.64452872079653</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.849245295796826</v>
+        <v>-3.829948479963457</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.104474178164052</v>
+        <v>2.293048129940696</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.596410370242033</v>
+        <v>1.562620501506285</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.60237494294175</v>
+        <v>4.762956247143598</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.831994945704823</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.877552609670096</v>
+        <v>-3.858255793836727</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.280617477523037</v>
+        <v>2.469191429299681</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.596410370242033</v>
+        <v>1.562620501506285</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.789841167850042</v>
+        <v>4.950422472051891</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.801397897058906</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.044145834783619</v>
+        <v>-4.024849018950249</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.18338313883171</v>
+        <v>2.371957090608354</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.42981714512851</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.659288184136011</v>
+        <v>4.81986948833786</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.805074299720623</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.021110041422053</v>
+        <v>-4.001813225588684</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.196273858838054</v>
+        <v>2.384847810614698</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.42981714512851</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.662964586797729</v>
+        <v>4.823545890999577</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.802692354844118</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.991864060966356</v>
+        <v>-3.972567245132988</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.205590306143828</v>
+        <v>2.394164257920472</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.42981714512851</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.660582641921225</v>
+        <v>4.821163946123072</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.799985594001754</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.098789608844208</v>
+        <v>-4.079492793010839</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.160113326150322</v>
+        <v>2.348687277926966</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.322891597250659</v>
+        <v>1.289101728514912</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.593720552352149</v>
+        <v>4.754301856553997</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.801414396144988</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.243808167351457</v>
+        <v>-4.224511351518088</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.103534704890657</v>
+        <v>2.292108656667301</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.17787303874341</v>
+        <v>1.144083170007663</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.508138219391034</v>
+        <v>4.668719523592881</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.901345635402741</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.362149933136174</v>
+        <v>-4.342853117302806</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.156129237834523</v>
+        <v>2.344703189611167</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.614481081786521</v>
+        <v>4.775062385988369</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.89913133252868</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.413560355456882</v>
+        <v>-4.394263539623513</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.133350766032179</v>
+        <v>2.321924717808822</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.612266778912461</v>
+        <v>4.772848083114307</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.899034460602969</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.492979806664634</v>
+        <v>-4.473682990831265</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.101486113623368</v>
+        <v>2.290060065400011</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.612169906986749</v>
+        <v>4.772751211188597</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.899028354161012</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.588442804581851</v>
+        <v>-4.569145988748483</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.063294808014524</v>
+        <v>2.251868759791168</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.188559077306301</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.612163800544793</v>
+        <v>4.77274510474664</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.897124750723623</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.524066893731137</v>
+        <v>-4.504770077897768</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.08714156891742</v>
+        <v>2.275715520694065</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.252934988157016</v>
+        <v>1.219145119421268</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.648885743617832</v>
+        <v>4.80946704781968</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.902858568471349</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.57943605586333</v>
+        <v>-4.560139240029962</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.070727721812269</v>
+        <v>2.259301673588913</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.252934988157016</v>
+        <v>1.219145119421268</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.654619561365559</v>
+        <v>4.815200865567407</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.902396931814282</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.624873835694157</v>
+        <v>-4.605577019860789</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.052090973222871</v>
+        <v>2.240664924999515</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.628450930301596</v>
+        <v>4.789032234503443</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.9222713246646</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.536667001546579</v>
+        <v>-4.517370185713211</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.107248099732221</v>
+        <v>2.295822051508865</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.648325323151914</v>
+        <v>4.808906627353762</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.905972025189328</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.43063200634127</v>
+        <v>-4.411335190507901</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.133362798339072</v>
+        <v>2.321936750115717</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.632026023676642</v>
+        <v>4.79260732787849</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.908402974653374</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.247420343208175</v>
+        <v>-4.228123527374806</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.209078413056356</v>
+        <v>2.397652364833</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.210089997478856</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.634456973140688</v>
+        <v>4.795038277342536</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.874194160501264</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.175698896194324</v>
+        <v>-4.156402080360955</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.203558177709787</v>
+        <v>2.39213212948643</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.281811444492707</v>
+        <v>1.248021575756959</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.643281027196888</v>
+        <v>4.803862331398736</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.821109906422436</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.153325870586618</v>
+        <v>-4.134029054753249</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.159423133874041</v>
+        <v>2.347997085650684</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.293067195605608</v>
+        <v>1.259277326869861</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.596950223785801</v>
+        <v>4.757531527987648</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.006308111307791</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.186342166497362</v>
+        <v>-4.167045350663994</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.331414820395098</v>
+        <v>2.519988772171742</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.223629818938857</v>
+        <v>1.189839950203109</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.740486002671106</v>
+        <v>4.901067306872952</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.99822933713604</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.174814530847754</v>
+        <v>-4.155517715014385</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.327947100483191</v>
+        <v>2.516521052259834</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.282630477140219</v>
+        <v>1.248840608404472</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.767807623420172</v>
+        <v>4.928388927622019</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.001897449657829</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.272156032190122</v>
+        <v>-4.252859216356754</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.292678612468032</v>
+        <v>2.481252564244675</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.238210294974731</v>
+        <v>1.204420426238983</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.744823626642668</v>
+        <v>4.905404930844514</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.003148531850667</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.358012061530089</v>
+        <v>-4.33871524569672</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.259587282924883</v>
+        <v>2.448161234701527</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.195834225748596</v>
+        <v>1.162044357012848</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.720649067299825</v>
+        <v>4.881230371501672</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.985567733671169</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.366848858946208</v>
+        <v>-4.34755204311284</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.238471765778938</v>
+        <v>2.427045717555581</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.188392053107245</v>
+        <v>1.154602184371498</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.698602965535516</v>
+        <v>4.859184269737363</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.995732244716218</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.458231421511667</v>
+        <v>-4.438934605678298</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.212083251797804</v>
+        <v>2.400657203574447</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.097009490541787</v>
+        <v>1.063219621806039</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.653937939041291</v>
+        <v>4.814519243243137</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.097860502540486</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.446524703524661</v>
+        <v>-4.427227887691292</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.318894196816874</v>
+        <v>2.507468148593517</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.108716208528793</v>
+        <v>1.074926339793046</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.763090227657763</v>
+        <v>4.923671531859609</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.100892841271891</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.346861199440998</v>
+        <v>-4.32756438360763</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.361791937181744</v>
+        <v>2.550365888958387</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.17190329173248</v>
+        <v>1.138113422996732</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.804034816311379</v>
+        <v>4.964616120513226</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.313797674549949</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.35717729760735</v>
+        <v>-4.337880481773982</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.570570331193261</v>
+        <v>2.759144282969904</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.17190329173248</v>
+        <v>1.138113422996732</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.016939649589437</v>
+        <v>5.177520953791285</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.312976341462039</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.357083329589978</v>
+        <v>-4.337786513756609</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.5697865853123</v>
+        <v>2.758360537088944</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.016340233309918</v>
+        <v>5.176921537511765</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.307208327406393</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.364302153789822</v>
+        <v>-4.345005337956453</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.561131041576716</v>
+        <v>2.749704993353359</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.010572219254271</v>
+        <v>5.171153523456119</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.307208327406393</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.363353730671784</v>
+        <v>-4.344056914838415</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.561510410823931</v>
+        <v>2.750084362600575</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.010572219254271</v>
+        <v>5.171153523456119</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.319935935387485</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.520422188927407</v>
+        <v>-4.501125373094039</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.511410635502774</v>
+        <v>2.699984587279417</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.023299827235364</v>
+        <v>5.183881131437211</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.321881933811873</v>
+        <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.514429942138595</v>
+        <v>-4.495133126305228</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.515753532642687</v>
+        <v>2.70432748441933</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.025245825659751</v>
+        <v>5.185827129861599</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149211</v>
+        <v>3.741942347149213</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.315536069829641</v>
+        <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.518738178481166</v>
+        <v>-4.40657516517446</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.507684374123427</v>
+        <v>2.733404804889406</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.01889996167752</v>
+        <v>5.179481265879367</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.844758409525132</v>
+        <v>3.844758409525133</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.426764229990658</v>
+        <v>4.607619455433952</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.518738178481166</v>
+        <v>-4.40657516517446</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.507684374123427</v>
+        <v>2.733404804889406</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.172273153079798</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.419828026977026</v>
+        <v>4.60068325242032</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>101.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>149.1%</t>
+          <t>136.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-603.1%</t>
+          <t>-616.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-46.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.6%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-602.2%</t>
+          <t>-615.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-241.6%</t>
+          <t>-247.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-102.9%</t>
+          <t>-115.4%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.4%</t>
+          <t>-324.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5179537032344321</v>
+        <v>-0.6545912063460799</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.913790856719206</v>
+        <v>2.859135855474547</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5065644665796307</v>
+        <v>-0.6432019696912785</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.916171347500367</v>
+        <v>2.861516346255708</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7590423609990367</v>
+        <v>-0.8956798641106845</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.813107081237667</v>
+        <v>2.758452079993008</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.049174027604468</v>
+        <v>-1.185811530716116</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.696920631194417</v>
+        <v>2.642265629949757</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.257178085957545</v>
+        <v>-1.393815589069193</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.618611152407111</v>
+        <v>2.563956151162452</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.319356497118515</v>
+        <v>-1.455994000230163</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.588821244280711</v>
+        <v>2.534166243036052</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.685425224263168</v>
+        <v>-1.822062727374816</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.435478052729299</v>
+        <v>2.38082305148464</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.893916005714853</v>
+        <v>-2.0305535088265</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.372420029887393</v>
+        <v>2.317765028642734</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.141117190480075</v>
+        <v>-2.277754693591722</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.281638306389874</v>
+        <v>2.226983305145214</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.633502218504172</v>
+        <v>-2.770139721615819</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.085790687223967</v>
+        <v>2.031135685979308</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.018682609434244</v>
+        <v>-3.155320112545891</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.930261069664801</v>
+        <v>1.875606068420142</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.268553289448826</v>
+        <v>-3.405190792560473</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.832081921113585</v>
+        <v>1.777426919868925</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.475065066335847</v>
+        <v>-3.611702569447494</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.745583269015034</v>
+        <v>1.690928267770375</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.794409141416348</v>
+        <v>-3.931046644527996</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.619618565683093</v>
+        <v>1.564963564438434</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.180618972692123</v>
+        <v>-4.31725647580377</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.451467520640187</v>
+        <v>1.396812519395528</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.415312966824676</v>
+        <v>-4.551950469936322</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.345874697989257</v>
+        <v>1.291219696744598</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.750975614055128</v>
+        <v>-4.887613117166775</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.210190230753041</v>
+        <v>1.155535229508382</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.827419944258</v>
+        <v>-4.964057447369647</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.186100058906134</v>
+        <v>1.131445057661475</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.192547326896746</v>
+        <v>-5.329184830008393</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.039303620856467</v>
+        <v>0.9846486196118076</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.601136104077424</v>
+        <v>-5.737773607189072</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8746296539989546</v>
+        <v>0.8199746527542953</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.714896516100289</v>
+        <v>-5.851534019211937</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8243109216612692</v>
+        <v>0.7696559204166098</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.131288390387287</v>
+        <v>-6.267925893498934</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6557482225553475</v>
+        <v>0.6010932213106881</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.492462020204274</v>
+        <v>-6.629099523315922</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5215374612972314</v>
+        <v>0.4668824600525721</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.835720539847293</v>
+        <v>-6.972358042958941</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3803336185857193</v>
+        <v>0.3256786173410595</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.883923357089637</v>
+        <v>-7.020560860201285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3594574117437825</v>
+        <v>0.3048024104991232</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.050732017063999</v>
+        <v>-7.187369520175647</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2965129236832458</v>
+        <v>0.2418579224385864</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.7822719436345955</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.237451725373302</v>
+        <v>-7.37408922848495</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2177987358251219</v>
+        <v>0.1631437345804621</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.7822719436345955</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.620453114115933</v>
+        <v>-7.757090617227581</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.06449607900648502</v>
+        <v>0.009841077761825634</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.7822719436345955</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.624939559317322</v>
+        <v>-7.761577062428969</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.06527301689735987</v>
+        <v>0.01061801565270049</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.7867583888359841</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.984469881821323</v>
+        <v>-8.121107384932973</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.0731888088061905</v>
+        <v>-0.1278438100508503</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.7867583888359841</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.034818945275545</v>
+        <v>-8.171456448387195</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.08541241423070156</v>
+        <v>-0.1400674154753618</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8371074522902062</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.13243822269694</v>
+        <v>-8.269075725808591</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1214183745774911</v>
+        <v>-0.1760733758221513</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9347267297116029</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.186509722205299</v>
+        <v>-8.32314722531695</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1401534180592625</v>
+        <v>-0.1948084193039228</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.9887982292199623</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.190085508297047</v>
+        <v>-8.326723011408697</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1360705353773191</v>
+        <v>-0.1907255366219793</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.014327151136455</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.22373834680552</v>
+        <v>-8.360375849917171</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1450491162962724</v>
+        <v>-0.1997041175409326</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.114740519053492</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.362824461424378</v>
+        <v>-8.499461964536028</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1853118606503941</v>
+        <v>-0.2399668618950543</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.253826633672349</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.537948878810921</v>
+        <v>-8.674586381922571</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2408064068574949</v>
+        <v>-0.2954614081021552</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.428951051058893</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.772400972825411</v>
+        <v>-8.909038475937061</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3418064093648865</v>
+        <v>-0.3964614106095468</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.428951051058893</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.876775703851857</v>
+        <v>-9.013413206963508</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3902284925494413</v>
+        <v>-0.4448834937941015</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.533325782085339</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.039289169550441</v>
+        <v>-9.175926672662092</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4541180889903189</v>
+        <v>-0.5087730902349792</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.630959212504025</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.165325962918731</v>
+        <v>-9.301963466030381</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.50183907770852</v>
+        <v>-0.5564940789531803</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.605707589694283</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.1082541910228</v>
+        <v>-9.24489169413445</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4750200332637466</v>
+        <v>-0.5296750345084069</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.605707589694283</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.24992603274692</v>
+        <v>-9.386563535858571</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5331639968521364</v>
+        <v>-0.5878189980967967</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.605707589694283</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.200335188322086</v>
+        <v>-9.336972691433736</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4982742489173306</v>
+        <v>-0.5529292501619909</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.556116745269449</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.051416853850229</v>
+        <v>-9.18805435696188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4517580487752708</v>
+        <v>-0.5064130500199311</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.524867154534276</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.825571701130819</v>
+        <v>-8.96220920424247</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3518409146512984</v>
+        <v>-0.4064959158959582</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.482940478947112</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.700993044793227</v>
+        <v>-8.837630547904878</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3008703075602024</v>
+        <v>-0.3555253088048627</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.482940478947112</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.675956363224717</v>
+        <v>-8.812593866336368</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2882218607706908</v>
+        <v>-0.3428768620153511</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.457611391396377</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.603823187936836</v>
+        <v>-8.740460691048487</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.253634886416902</v>
+        <v>-0.3082898876615623</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.457611391396377</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.532456795327189</v>
+        <v>-8.669094298438839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2348255917669082</v>
+        <v>-0.2894805930115685</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.386244998786729</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.438997761341964</v>
+        <v>-8.575635264453615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2073254594857259</v>
+        <v>-0.2619804607303862</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.386244998786729</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.428344579788533</v>
+        <v>-8.564982082900183</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2048987473637269</v>
+        <v>-0.2595537486083872</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.386244998786729</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.330437541112042</v>
+        <v>-8.467075044223693</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1660362468665917</v>
+        <v>-0.220691248111252</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.318259248926172</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.306484000136084</v>
+        <v>-8.443121503247735</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1557863243307147</v>
+        <v>-0.210441325575375</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.294305707950215</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.042424061813287</v>
+        <v>-8.179061564924938</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06342266516334849</v>
+        <v>-0.1180776664080083</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.030245769627419</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.335344438308449</v>
+        <v>-7.4719819414201</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2166221505782859</v>
+        <v>0.1619671493336261</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.030245769627419</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.295160139942259</v>
+        <v>-7.431797643053909</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2330394938126035</v>
+        <v>0.1783844925679436</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9900614712612278</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.131760269002896</v>
+        <v>-7.268397772114547</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2977662634091054</v>
+        <v>0.2431112621644456</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.8266616003218653</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.898279046773298</v>
+        <v>-7.034916549884948</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3990831811387974</v>
+        <v>0.3444281798941371</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5931803780922668</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.748612655765783</v>
+        <v>-6.885250158877433</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4560575272288441</v>
+        <v>0.4014025259841842</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.5002768868497308</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.616337182134896</v>
+        <v>-6.752974685246547</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4102285026883536</v>
+        <v>0.3555735014436934</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.3680014132188442</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.444475966569994</v>
+        <v>-6.581113469681644</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4817880496019513</v>
+        <v>0.427133048357291</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1961401976539413</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.359511299840674</v>
+        <v>-6.496148802952325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5286802575173377</v>
+        <v>0.4740252562726774</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.1111755309246217</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.465101289613779</v>
+        <v>-6.601738792725429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3584683320088771</v>
+        <v>0.3038133307642168</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.2167655206977261</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.396866704988351</v>
+        <v>-6.533504208100002</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4343065077361343</v>
+        <v>0.3796515064914745</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1983501978251901</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.248926663580752</v>
+        <v>-6.385564166692403</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.376861715660767</v>
+        <v>0.3222067144161072</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1780292819166325</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.195957141326764</v>
+        <v>-6.332594644438414</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3893355383088846</v>
+        <v>0.3346805370642243</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.1250597596626437</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.030168945366473</v>
+        <v>-6.166806448478123</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4486902045979075</v>
+        <v>0.3940352033532473</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.1250597596626437</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.996805738887704</v>
+        <v>-6.133443241999355</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4764978415705583</v>
+        <v>0.421842840325898</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.1250597596626437</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.888546601765182</v>
+        <v>-6.025184104876833</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.514333616878762</v>
+        <v>0.4596786156341017</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.1250597596626437</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.765255466948052</v>
+        <v>-5.901892970059702</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5611481648161911</v>
+        <v>0.5064931635715308</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.001768624845513156</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.71255859981676</v>
+        <v>-5.849196102928411</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5899278899060327</v>
+        <v>0.5352728886613725</v>
       </c>
       <c r="F1916" t="n">
         <v>0.05092824228577802</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.468793157833316</v>
+        <v>-5.605430660944966</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6832147750464612</v>
+        <v>0.6285597738018009</v>
       </c>
       <c r="F1917" t="n">
         <v>0.05092824228577802</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.379017485456844</v>
+        <v>-5.515654988568494</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.721249357917066</v>
+        <v>0.6665943566724057</v>
       </c>
       <c r="F1918" t="n">
         <v>0.112527687200088</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.129167091507769</v>
+        <v>-5.26580459461942</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8139315904803981</v>
+        <v>0.7592765892357378</v>
       </c>
       <c r="F1919" t="n">
         <v>0.112527687200088</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.953274999040337</v>
+        <v>-5.089912502151988</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8878875509880197</v>
+        <v>0.8332325497433595</v>
       </c>
       <c r="F1920" t="n">
         <v>0.112527687200088</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.781828536017874</v>
+        <v>-4.918466039129524</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9697936422515587</v>
+        <v>0.9151386410068985</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2839741502225512</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.701806248908753</v>
+        <v>-4.838443752020403</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.000823034711504</v>
+        <v>0.9461680334668439</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3639964373316721</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.638170506674818</v>
+        <v>-4.774808009786469</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.030972132659395</v>
+        <v>0.976317131414735</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4276321795656067</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.544473188458423</v>
+        <v>-4.681110691570074</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.049645318729749</v>
+        <v>0.9949903174850887</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4276321795656067</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.554975811523712</v>
+        <v>-4.691613314635362</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.047187346128511</v>
+        <v>0.9925323448838506</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4171295565003178</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.442489550854837</v>
+        <v>-4.579127053966488</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.096111164230881</v>
+        <v>1.04145616298622</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4171295565003178</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.424775863976972</v>
+        <v>-4.561413367088623</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.103875222899367</v>
+        <v>1.049220221654707</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4203108853972346</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.301301592663954</v>
+        <v>-4.437939095775604</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.150263002644567</v>
+        <v>1.095608001399907</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4203108853972346</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.081280794626943</v>
+        <v>-4.217918297738594</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.239850358869986</v>
+        <v>1.185195357625326</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5615307304652148</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948413105563665</v>
+        <v>-4.085050608675316</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.308891617297121</v>
+        <v>1.25423661605246</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5615307304652148</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828240022199166</v>
+        <v>-3.964877525310817</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.358106695083222</v>
+        <v>1.303451693838561</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6817038138297138</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.692986660869189</v>
+        <v>-3.82962416398084</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.422296142176653</v>
+        <v>1.367641140931992</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8169571751596909</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.752861488226881</v>
+        <v>-3.889498991338533</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.384383702635002</v>
+        <v>1.329728701390341</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7570823478019988</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.633041257316044</v>
+        <v>-3.769678760427695</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.447600964233545</v>
+        <v>1.392945962988885</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7570823478019988</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.63551096377785</v>
+        <v>-3.772148466889501</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.354257280971264</v>
+        <v>1.299602279726604</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7546126413401926</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.70388115010186</v>
+        <v>-3.840518653213511</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.246171067926962</v>
+        <v>1.191516066682301</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7638883403764075</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.81575342972801</v>
+        <v>-3.952390932839662</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.191858864708393</v>
+        <v>1.137203863463732</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7638883403764075</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.8712735056206</v>
+        <v>-4.007911008732251</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.306681671043559</v>
+        <v>1.252026669798899</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7638883403764075</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.695799245828131</v>
+        <v>-3.832436748939782</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.381438606952335</v>
+        <v>1.326783605707674</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7638883403764075</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.687874871243217</v>
+        <v>-3.824512374354868</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.360350385547508</v>
+        <v>1.305695384302847</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7638883403764075</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.681596668673368</v>
+        <v>-3.818234171785019</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.291399979976897</v>
+        <v>1.236744978732236</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7701665429462565</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.621744049469644</v>
+        <v>-3.758381552581296</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.325513414090518</v>
+        <v>1.270858412845858</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7701665429462565</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.535500586443267</v>
+        <v>-3.672138089554918</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.35495706987493</v>
+        <v>1.300302068630269</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7701665429462565</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.580807405842247</v>
+        <v>-3.717444908953898</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.328610117559863</v>
+        <v>1.273955116315203</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7293563799370257</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.609840510544549</v>
+        <v>-3.7464780136562</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.317548748712044</v>
+        <v>1.262893747467384</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7293563799370257</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.517030029093689</v>
+        <v>-3.653667532205341</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.283945633183754</v>
+        <v>1.229290631939093</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8221668613878851</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.561419498423117</v>
+        <v>-3.698057001534768</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.268063321376584</v>
+        <v>1.213408320131923</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7777773920584574</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.54091580453762</v>
+        <v>-3.677553307649271</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.271340507442505</v>
+        <v>1.216685506197845</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7982810859439547</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.580839899120192</v>
+        <v>-3.717477402231843</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.260862165440144</v>
+        <v>1.206207164195483</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.608620297021545</v>
+        <v>-3.745257800133196</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.261247208048142</v>
+        <v>1.206592206803481</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.727000969751683</v>
+        <v>-3.863638472863335</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.05225065895674</v>
+        <v>0.997595657712079</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.835615048195014</v>
+        <v>-3.972252551306666</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.128954688298613</v>
+        <v>1.074299687053952</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.800206009946872</v>
+        <v>-3.936843513058523</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.157631329700193</v>
+        <v>1.102976328455532</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.76182234738872</v>
+        <v>-3.898459850500372</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.170404236065822</v>
+        <v>1.115749234821161</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.584706017353554</v>
+        <v>-3.721343520465206</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.23797979692519</v>
+        <v>1.18332479568053</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.6297982621871</v>
+        <v>-3.766435765298751</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.220626290753685</v>
+        <v>1.165971289509025</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.450422840948332</v>
+        <v>-3.587060344059983</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.286163434555607</v>
+        <v>1.231508433310946</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.495437054468938</v>
+        <v>-3.63207455758059</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.248965204478954</v>
+        <v>1.194310203234293</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.762441564741374</v>
+        <v>-3.899079067853025</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.147854962708926</v>
+        <v>1.093199961464265</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.863639346178546</v>
+        <v>-4.000276849290198</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.106579772030558</v>
+        <v>1.051924770785897</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.857128379564234</v>
+        <v>-3.993765882675885</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.1067841202306</v>
+        <v>1.052129118985939</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.838090251856936</v>
+        <v>-3.974727754968588</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.110924090521763</v>
+        <v>1.056269089277103</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.890606054131756</v>
+        <v>-4.027243557243408</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.209212171246026</v>
+        <v>1.154557170001365</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.904472815465674</v>
+        <v>-4.041110318577326</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.204498795698592</v>
+        <v>1.149843794453931</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4473849384832159</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.863989823543329</v>
+        <v>-4.000627326654982</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.226700522864456</v>
+        <v>1.172045521619795</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4473849384832159</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.716246853308327</v>
+        <v>-3.85288435641998</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.183747932235657</v>
+        <v>1.129092930990996</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6151922957180991</v>
@@ -46792,10 +46792,10 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.800068074583025</v>
+        <v>-3.936705577694678</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.153013065257258</v>
+        <v>1.098358064012597</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6151922957180991</v>
@@ -46815,10 +46815,10 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.793915368530241</v>
+        <v>-3.930552871641893</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.15613649607003</v>
+        <v>1.10148149482537</v>
       </c>
       <c r="F1968" t="n">
         <v>0.6213450017708834</v>
@@ -46838,10 +46838,10 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.810724666680742</v>
+        <v>-3.947362169792395</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.14849325354994</v>
+        <v>1.093838252305279</v>
       </c>
       <c r="F1969" t="n">
         <v>0.6045357036203818</v>
@@ -46861,10 +46861,10 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.74842666790462</v>
+        <v>-3.885064171016273</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.23974800685721</v>
+        <v>1.185093005612549</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6498299678948238</v>
@@ -46884,10 +46884,10 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.546636470239462</v>
+        <v>-3.683273973351115</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.1227560876374</v>
+        <v>1.068101086392739</v>
       </c>
       <c r="F1971" t="n">
         <v>0.8478481600639782</v>
@@ -46907,10 +46907,10 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.597523182925657</v>
+        <v>-3.73416068603731</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.172691634885097</v>
+        <v>1.118036633640436</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7969614473777837</v>
@@ -46930,10 +46930,10 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.51091244027585</v>
+        <v>-3.647549943387502</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.221963668061064</v>
+        <v>1.167308666816403</v>
       </c>
       <c r="F1973" t="n">
         <v>0.875587178582942</v>
@@ -46953,10 +46953,10 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.571121738281134</v>
+        <v>-3.707759241392787</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.196415929683622</v>
+        <v>1.141760928438961</v>
       </c>
       <c r="F1974" t="n">
         <v>0.8153778805776575</v>
@@ -46976,10 +46976,10 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.521935089596783</v>
+        <v>-3.658572592708436</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.214582207197291</v>
+        <v>1.15992720595263</v>
       </c>
       <c r="F1975" t="n">
         <v>0.8153778805776575</v>
@@ -46999,10 +46999,10 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.477561957958214</v>
+        <v>-3.614199461069867</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.232194327288155</v>
+        <v>1.177539326043494</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8597510122162261</v>
@@ -47022,10 +47022,10 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.500042308817099</v>
+        <v>-3.636679811928752</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.217595981083191</v>
+        <v>1.16294097983853</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8597510122162261</v>
@@ -47045,10 +47045,10 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.452386578256044</v>
+        <v>-3.589024081367696</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.243040030335418</v>
+        <v>1.188385029090757</v>
       </c>
       <c r="F1978" t="n">
         <v>0.9074067427772817</v>
@@ -47068,10 +47068,10 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.351868419757289</v>
+        <v>-3.488505922868942</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.288139667109645</v>
+        <v>1.233484665864984</v>
       </c>
       <c r="F1979" t="n">
         <v>1.007924901276036</v>
@@ -47091,10 +47091,10 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.335963090324936</v>
+        <v>-3.472600593436589</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.281256471358458</v>
+        <v>1.226601470113797</v>
       </c>
       <c r="F1980" t="n">
         <v>0.9288122405667973</v>
@@ -47114,10 +47114,10 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.291124688716538</v>
+        <v>-3.427762191828191</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.303289534612446</v>
+        <v>1.248634533367785</v>
       </c>
       <c r="F1981" t="n">
         <v>0.9333556735116668</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.310623144958547</v>
+        <v>-3.447260648070199</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.29965109174672</v>
+        <v>1.244996090502059</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8852710322317625</v>
@@ -47160,10 +47160,10 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.266420307872646</v>
+        <v>-3.403057810984299</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.323211829108918</v>
+        <v>1.268556827864257</v>
       </c>
       <c r="F1983" t="n">
         <v>0.929473869317663</v>
@@ -47183,10 +47183,10 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.273979973709693</v>
+        <v>-3.410617476821346</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.318597963243346</v>
+        <v>1.263942961998685</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9842772733274823</v>
@@ -47206,10 +47206,10 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.115688556170421</v>
+        <v>-3.252326059282074</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.433162295442095</v>
+        <v>1.378507294197434</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9842772733274823</v>
@@ -47229,10 +47229,10 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.908046552535945</v>
+        <v>-3.044684055647597</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.514659801490139</v>
+        <v>1.460004800245478</v>
       </c>
       <c r="F1986" t="n">
         <v>1.191919276961958</v>
@@ -47252,10 +47252,10 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.857014459813417</v>
+        <v>-2.993651962925069</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.53002086681742</v>
+        <v>1.475365865572759</v>
       </c>
       <c r="F1987" t="n">
         <v>1.242951369684486</v>
@@ -47275,10 +47275,10 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.791790278686211</v>
+        <v>-2.928427781797863</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.573297943361007</v>
+        <v>1.518642942116346</v>
       </c>
       <c r="F1988" t="n">
         <v>1.308175550811692</v>
@@ -47298,10 +47298,10 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.754363258615077</v>
+        <v>-2.89100076172673</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.584229723688741</v>
+        <v>1.52957472244408</v>
       </c>
       <c r="F1989" t="n">
         <v>1.313427088840874</v>
@@ -47321,10 +47321,10 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.774474914649785</v>
+        <v>-2.911112417761438</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.577441853606098</v>
+        <v>1.522786852361437</v>
       </c>
       <c r="F1990" t="n">
         <v>1.324454433838293</v>
@@ -47344,10 +47344,10 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.746061651549902</v>
+        <v>-2.882699154661554</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.749364929867262</v>
+        <v>1.694709928622601</v>
       </c>
       <c r="F1991" t="n">
         <v>1.265478871091864</v>
@@ -47367,10 +47367,10 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.671279390524889</v>
+        <v>-2.807916893636542</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.899390743495085</v>
+        <v>1.844735742250424</v>
       </c>
       <c r="F1992" t="n">
         <v>1.340261132116877</v>
@@ -47390,10 +47390,10 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.645195306261081</v>
+        <v>-2.781832809372734</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.901532353214467</v>
+        <v>1.846877351969806</v>
       </c>
       <c r="F1993" t="n">
         <v>1.340261132116877</v>
@@ -47413,10 +47413,10 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.557317393151961</v>
+        <v>-2.693954896263613</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.934876714041894</v>
+        <v>1.880221712797233</v>
       </c>
       <c r="F1994" t="n">
         <v>1.456186774540228</v>
@@ -47436,10 +47436,10 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.548424931758677</v>
+        <v>-2.68506243487033</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.955988104325999</v>
+        <v>1.901333103081338</v>
       </c>
       <c r="F1995" t="n">
         <v>1.456186774540228</v>
@@ -47459,10 +47459,10 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.716901048728555</v>
+        <v>-2.853538551840208</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.880452704942632</v>
+        <v>1.825797703697971</v>
       </c>
       <c r="F1996" t="n">
         <v>1.428238938823647</v>
@@ -47482,10 +47482,10 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.270644856099115</v>
+        <v>-2.407282359210768</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.040224879182269</v>
+        <v>1.985569877937609</v>
       </c>
       <c r="F1997" t="n">
         <v>1.333520269154014</v>
@@ -47505,10 +47505,10 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.247923752415963</v>
+        <v>-2.384561255527615</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.039977343152435</v>
+        <v>1.985322341907774</v>
       </c>
       <c r="F1998" t="n">
         <v>1.333520269154014</v>
@@ -47528,10 +47528,10 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.377125565710005</v>
+        <v>-2.513763068821658</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.147202743685988</v>
+        <v>2.092547742441326</v>
       </c>
       <c r="F1999" t="n">
         <v>1.204318455859972</v>
@@ -47551,10 +47551,10 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.402999964184031</v>
+        <v>-2.539637467295683</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.173930806790024</v>
+        <v>2.119275805545363</v>
       </c>
       <c r="F2000" t="n">
         <v>1.249230064571713</v>
@@ -47574,10 +47574,10 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.395945273968857</v>
+        <v>-2.53258277708051</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.173428038865638</v>
+        <v>2.118773037620977</v>
       </c>
       <c r="F2001" t="n">
         <v>1.256284754786887</v>
@@ -47597,10 +47597,10 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.368994049642369</v>
+        <v>-2.505631552754022</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.194214682240975</v>
+        <v>2.139559680996314</v>
       </c>
       <c r="F2002" t="n">
         <v>1.271165100814606</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.390538277473156</v>
+        <v>-2.527175780584809</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.36970012325362</v>
+        <v>2.315045122008959</v>
       </c>
       <c r="F2003" t="n">
         <v>1.271165100814606</v>
@@ -47643,10 +47643,10 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.412946395278028</v>
+        <v>-2.549583898389681</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.352853571034664</v>
+        <v>2.298198569790003</v>
       </c>
       <c r="F2004" t="n">
         <v>1.271165100814606</v>
@@ -47666,10 +47666,10 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.441170630855629</v>
+        <v>-2.577808133967281</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.343617876353261</v>
+        <v>2.2889628751086</v>
       </c>
       <c r="F2005" t="n">
         <v>1.289141853265915</v>
@@ -47689,10 +47689,10 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.450611556744159</v>
+        <v>-2.587249059855811</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.396095223719696</v>
+        <v>2.341440222475036</v>
       </c>
       <c r="F2006" t="n">
         <v>1.411568970809306</v>
@@ -47712,10 +47712,10 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.539488187912633</v>
+        <v>-2.676125691024285</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.363435665797608</v>
+        <v>2.308780664552947</v>
       </c>
       <c r="F2007" t="n">
         <v>1.322692339640832</v>
@@ -47735,10 +47735,10 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.615818165513538</v>
+        <v>-2.752455668625191</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.331015487651021</v>
+        <v>2.27636048640636</v>
       </c>
       <c r="F2008" t="n">
         <v>1.322692339640832</v>
@@ -47758,10 +47758,10 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.70948211019108</v>
+        <v>-2.846119613302732</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.288370139382867</v>
+        <v>2.233715138138206</v>
       </c>
       <c r="F2009" t="n">
         <v>1.229028394963291</v>
@@ -47781,10 +47781,10 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.871050535718335</v>
+        <v>-3.007688038829988</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.222176779382117</v>
+        <v>2.167521778137456</v>
       </c>
       <c r="F2010" t="n">
         <v>1.102245471165411</v>
@@ -47804,10 +47804,10 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.979351197588454</v>
+        <v>-3.115988700700107</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.191929921499987</v>
+        <v>2.137274920255327</v>
       </c>
       <c r="F2011" t="n">
         <v>1.102245471165411</v>
@@ -47827,10 +47827,10 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.997155169309198</v>
+        <v>-3.133792672420851</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.17681352959463</v>
+        <v>2.122158528349969</v>
       </c>
       <c r="F2012" t="n">
         <v>1.03171084826021</v>
@@ -47850,10 +47850,10 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.025055956418671</v>
+        <v>-3.161693459530324</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.164177255877843</v>
+        <v>2.109522254633182</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9971139241172757</v>
@@ -47873,10 +47873,10 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.147582059121565</v>
+        <v>-3.284219562233218</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.111931258773884</v>
+        <v>2.057276257529223</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8745878214143818</v>
@@ -47896,10 +47896,10 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.378096555307154</v>
+        <v>-3.514734058418807</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.086431419890152</v>
+        <v>2.031776418645491</v>
       </c>
       <c r="F2015" t="n">
         <v>0.6440733252287931</v>
@@ -47919,10 +47919,10 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.726841640531598</v>
+        <v>-3.863479143643251</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.087245104802221</v>
+        <v>2.032590103557561</v>
       </c>
       <c r="F2016" t="n">
         <v>0.5353253713098953</v>
@@ -47942,10 +47942,10 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.880828058307738</v>
+        <v>-4.017465561419391</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.094630806837405</v>
+        <v>2.039975805592745</v>
       </c>
       <c r="F2017" t="n">
         <v>0.5353253713098953</v>
@@ -47965,10 +47965,10 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.830306154480073</v>
+        <v>-3.966943657591725</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.100890770488593</v>
+        <v>2.046235769243931</v>
       </c>
       <c r="F2018" t="n">
         <v>0.5353253713098953</v>
@@ -47988,10 +47988,10 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.082781308487797</v>
+        <v>-4.219418811599449</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.011771197940917</v>
+        <v>1.957116196696256</v>
       </c>
       <c r="F2019" t="n">
         <v>0.5353253713098953</v>
@@ -48011,10 +48011,10 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.375677064967209</v>
+        <v>-4.512314568078861</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.895823429868096</v>
+        <v>1.841168428623435</v>
       </c>
       <c r="F2020" t="n">
         <v>0.5353253713098953</v>
@@ -48034,10 +48034,10 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.562341193102017</v>
+        <v>-4.698978696213669</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.825279520841494</v>
+        <v>1.770624519596833</v>
       </c>
       <c r="F2021" t="n">
         <v>0.5085864004853354</v>
@@ -48057,10 +48057,10 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.708361880015979</v>
+        <v>-4.844999383127631</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.761949098812098</v>
+        <v>1.707294097567437</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4995033086914784</v>
@@ -48080,10 +48080,10 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.800075889125564</v>
+        <v>-4.936713392237216</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.887467551867309</v>
+        <v>1.832812550622648</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4995033086914784</v>
@@ -48103,10 +48103,10 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.831727548185533</v>
+        <v>-4.968365051297186</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.869653526207135</v>
+        <v>1.814998524962474</v>
       </c>
       <c r="F2024" t="n">
         <v>0.4943348514470383</v>
@@ -48126,10 +48126,10 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.913662366454417</v>
+        <v>-5.050299869566069</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.847109016468073</v>
+        <v>1.792454015223412</v>
       </c>
       <c r="F2025" t="n">
         <v>0.4844001058599581</v>
@@ -48149,10 +48149,10 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.015638488702824</v>
+        <v>-5.152275991814476</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.815244206024612</v>
+        <v>1.760589204779951</v>
       </c>
       <c r="F2026" t="n">
         <v>0.3824239836115505</v>
@@ -48172,10 +48172,10 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.905632205225603</v>
+        <v>-5.042269708337255</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.851399606659676</v>
+        <v>1.796744605415015</v>
       </c>
       <c r="F2027" t="n">
         <v>0.4056285555288257</v>
@@ -48195,10 +48195,10 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.762572629484676</v>
+        <v>-4.899210132596329</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.912873447678021</v>
+        <v>1.85821844643336</v>
       </c>
       <c r="F2028" t="n">
         <v>0.413641982118805</v>
@@ -48218,10 +48218,10 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.461125904012839</v>
+        <v>-4.597763407124491</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.040713020749292</v>
+        <v>1.986058019504631</v>
       </c>
       <c r="F2029" t="n">
         <v>0.7150887075906422</v>
@@ -48241,10 +48241,10 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.485716148248023</v>
+        <v>-4.622353651359675</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.031848100807929</v>
+        <v>1.977193099563268</v>
       </c>
       <c r="F2030" t="n">
         <v>0.7150887075906422</v>
@@ -48264,10 +48264,10 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.434677772241503</v>
+        <v>-4.571315275353155</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.053106355590293</v>
+        <v>1.998451354345632</v>
       </c>
       <c r="F2031" t="n">
         <v>0.7150887075906422</v>
@@ -48287,10 +48287,10 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.393538477374872</v>
+        <v>-4.530175980486524</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.08860017241109</v>
+        <v>2.03394517116643</v>
       </c>
       <c r="F2032" t="n">
         <v>0.7562280024572731</v>
@@ -48310,10 +48310,10 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.296903565356232</v>
+        <v>-4.433541068467884</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.943438133342481</v>
+        <v>1.88878313209782</v>
       </c>
       <c r="F2033" t="n">
         <v>0.852862914475913</v>
@@ -48333,10 +48333,10 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.427484299887074</v>
+        <v>-4.564121802998726</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.894707883604108</v>
+        <v>1.840052882359447</v>
       </c>
       <c r="F2034" t="n">
         <v>0.7222821799450705</v>
@@ -48356,10 +48356,10 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.262987965696112</v>
+        <v>-4.399625468807765</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.944933236356575</v>
+        <v>1.890278235111915</v>
       </c>
       <c r="F2035" t="n">
         <v>0.8867785141360324</v>
@@ -48379,10 +48379,10 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.18588936415424</v>
+        <v>-4.322526867265892</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.974960387409754</v>
+        <v>1.920305386165094</v>
       </c>
       <c r="F2036" t="n">
         <v>0.8867785141360324</v>
@@ -48402,10 +48402,10 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.196274559044129</v>
+        <v>-4.332912062155781</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.980675088578871</v>
+        <v>1.92602008733421</v>
       </c>
       <c r="F2037" t="n">
         <v>0.8763933192461431</v>
@@ -48425,10 +48425,10 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.214862717766354</v>
+        <v>-4.351500220878006</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.044076830866406</v>
+        <v>1.989421829621745</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8578051605239176</v>
@@ -48448,10 +48448,10 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.21516126446239</v>
+        <v>-4.351798767574042</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.04082642300629</v>
+        <v>1.986171421761629</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8575066138278817</v>
@@ -48471,10 +48471,10 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.114338130771962</v>
+        <v>-4.250975633883614</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.085686571421853</v>
+        <v>2.031031570177192</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8699708293122356</v>
@@ -48494,10 +48494,10 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.923556770019555</v>
+        <v>-4.060194273131208</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.162128369201359</v>
+        <v>2.107473367956698</v>
       </c>
       <c r="F2041" t="n">
         <v>1.060752190064643</v>
@@ -48517,10 +48517,10 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.816593412170133</v>
+        <v>-3.953230915281786</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.184750558078724</v>
+        <v>2.130095556834063</v>
       </c>
       <c r="F2042" t="n">
         <v>1.119216798024445</v>
@@ -48540,10 +48540,10 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.761262824268371</v>
+        <v>-3.897900327380024</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.241849729851487</v>
+        <v>2.187194728606826</v>
       </c>
       <c r="F2043" t="n">
         <v>1.174547385926207</v>
@@ -48563,10 +48563,10 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.749208697355408</v>
+        <v>-3.885846200467061</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.240357948518111</v>
+        <v>2.185702947273449</v>
       </c>
       <c r="F2044" t="n">
         <v>1.186601512839169</v>
@@ -48586,10 +48586,10 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.790363816923629</v>
+        <v>-3.927001320035282</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.225776530874958</v>
+        <v>2.171121529630296</v>
       </c>
       <c r="F2045" t="n">
         <v>1.145446393270948</v>
@@ -48609,10 +48609,10 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.722315254232099</v>
+        <v>-3.858952757343752</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.265846981829452</v>
+        <v>2.211191980584791</v>
       </c>
       <c r="F2046" t="n">
         <v>1.213494955962478</v>
@@ -48632,10 +48632,10 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.9539156474016</v>
+        <v>-4.090553150513253</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.193409494735246</v>
+        <v>2.138754493490585</v>
       </c>
       <c r="F2047" t="n">
         <v>1.213494955962478</v>
@@ -48655,10 +48655,10 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.003967192930819</v>
+        <v>-4.140604696042473</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.15699511259044</v>
+        <v>2.102340111345779</v>
       </c>
       <c r="F2048" t="n">
         <v>1.213494955962478</v>
@@ -48678,10 +48678,10 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.179074025507264</v>
+        <v>-4.315711528618918</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.047204293153329</v>
+        <v>1.992549291908667</v>
       </c>
       <c r="F2049" t="n">
         <v>1.213494955962478</v>
@@ -48701,10 +48701,10 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-3.982973872076741</v>
+        <v>-4.119611375188395</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.132666973522478</v>
+        <v>2.078011972277817</v>
       </c>
       <c r="F2050" t="n">
         <v>1.409595109393001</v>
@@ -48724,10 +48724,10 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.829948479963457</v>
+        <v>-3.966585983075111</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.293048129940696</v>
+        <v>2.238393128696035</v>
       </c>
       <c r="F2051" t="n">
         <v>1.562620501506285</v>
@@ -48747,10 +48747,10 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.858255793836727</v>
+        <v>-3.994893296948381</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.469191429299681</v>
+        <v>2.414536428055019</v>
       </c>
       <c r="F2052" t="n">
         <v>1.562620501506285</v>
@@ -48770,10 +48770,10 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.024849018950249</v>
+        <v>-4.161486522061903</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.371957090608354</v>
+        <v>2.317302089363693</v>
       </c>
       <c r="F2053" t="n">
         <v>1.396027276392763</v>
@@ -48793,10 +48793,10 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.001813225588684</v>
+        <v>-4.138450728700337</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.384847810614698</v>
+        <v>2.330192809370037</v>
       </c>
       <c r="F2054" t="n">
         <v>1.396027276392763</v>
@@ -48816,10 +48816,10 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.972567245132988</v>
+        <v>-4.109204748244641</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.394164257920472</v>
+        <v>2.339509256675811</v>
       </c>
       <c r="F2055" t="n">
         <v>1.396027276392763</v>
@@ -48839,10 +48839,10 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.079492793010839</v>
+        <v>-4.216130296122492</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.348687277926966</v>
+        <v>2.294032276682305</v>
       </c>
       <c r="F2056" t="n">
         <v>1.289101728514912</v>
@@ -48862,10 +48862,10 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.224511351518088</v>
+        <v>-4.36114885462974</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.292108656667301</v>
+        <v>2.23745365542264</v>
       </c>
       <c r="F2057" t="n">
         <v>1.144083170007663</v>
@@ -48885,10 +48885,10 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.342853117302806</v>
+        <v>-4.479490620414458</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.344703189611167</v>
+        <v>2.290048188366506</v>
       </c>
       <c r="F2058" t="n">
         <v>1.154769208570553</v>
@@ -48908,10 +48908,10 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.394263539623513</v>
+        <v>-4.530901042735166</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.321924717808822</v>
+        <v>2.267269716564162</v>
       </c>
       <c r="F2059" t="n">
         <v>1.154769208570553</v>
@@ -48931,10 +48931,10 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.473682990831265</v>
+        <v>-4.610320493942917</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.290060065400011</v>
+        <v>2.23540506415535</v>
       </c>
       <c r="F2060" t="n">
         <v>1.154769208570553</v>
@@ -48954,10 +48954,10 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.569145988748483</v>
+        <v>-4.705783491860135</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.251868759791168</v>
+        <v>2.197213758546507</v>
       </c>
       <c r="F2061" t="n">
         <v>1.154769208570553</v>
@@ -48977,10 +48977,10 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.504770077897768</v>
+        <v>-4.64140758100942</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.275715520694065</v>
+        <v>2.221060519449404</v>
       </c>
       <c r="F2062" t="n">
         <v>1.219145119421268</v>
@@ -49000,10 +49000,10 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.560139240029962</v>
+        <v>-4.696776743141614</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.259301673588913</v>
+        <v>2.204646672344253</v>
       </c>
       <c r="F2063" t="n">
         <v>1.219145119421268</v>
@@ -49023,10 +49023,10 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.605577019860789</v>
+        <v>-4.742214522972441</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.240664924999515</v>
+        <v>2.186009923754854</v>
       </c>
       <c r="F2064" t="n">
         <v>1.176300128743109</v>
@@ -49046,10 +49046,10 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.517370185713211</v>
+        <v>-4.654007688824863</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.295822051508865</v>
+        <v>2.241167050264204</v>
       </c>
       <c r="F2065" t="n">
         <v>1.176300128743109</v>
@@ -49069,10 +49069,10 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.411335190507901</v>
+        <v>-4.547972693619553</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.321936750115717</v>
+        <v>2.267281748871055</v>
       </c>
       <c r="F2066" t="n">
         <v>1.176300128743109</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.228123527374806</v>
+        <v>-4.364761030486458</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.397652364833</v>
+        <v>2.342997363588339</v>
       </c>
       <c r="F2067" t="n">
         <v>1.176300128743109</v>
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.98447283409158</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.156402080360955</v>
+        <v>-4.293039583472607</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.39213212948643</v>
+        <v>2.26690057638879</v>
       </c>
       <c r="F2068" t="n">
         <v>1.248021575756959</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.803862331398736</v>
+        <v>4.733285779545756</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.931388580012752</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.134029054753249</v>
+        <v>-4.270666557864901</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.347997085650684</v>
+        <v>2.222765532553044</v>
       </c>
       <c r="F2069" t="n">
         <v>1.259277326869861</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.757531527987648</v>
+        <v>4.686954976134668</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.116586784898107</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.167045350663994</v>
+        <v>-4.303682853775646</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.519988772171742</v>
+        <v>2.394757219074101</v>
       </c>
       <c r="F2070" t="n">
         <v>1.189839950203109</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.901067306872952</v>
+        <v>4.830490755019973</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.108508010726356</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.155517715014385</v>
+        <v>-4.292155218126037</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.516521052259834</v>
+        <v>2.391289499162194</v>
       </c>
       <c r="F2071" t="n">
         <v>1.248840608404472</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.928388927622019</v>
+        <v>4.85781237576904</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.112176123248145</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.252859216356754</v>
+        <v>-4.389496719468406</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.481252564244675</v>
+        <v>2.356021011147035</v>
       </c>
       <c r="F2072" t="n">
         <v>1.204420426238983</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.905404930844514</v>
+        <v>4.834828378991535</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.113427205440983</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.33871524569672</v>
+        <v>-4.475352748808373</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.448161234701527</v>
+        <v>2.322929681603886</v>
       </c>
       <c r="F2073" t="n">
         <v>1.162044357012848</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.881230371501672</v>
+        <v>4.810653819648692</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>4.095846407261485</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.34755204311284</v>
+        <v>-4.484189546224492</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.427045717555581</v>
+        <v>2.301814164457941</v>
       </c>
       <c r="F2074" t="n">
         <v>1.154602184371498</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.859184269737363</v>
+        <v>4.788607717884384</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>4.106010918306534</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.438934605678298</v>
+        <v>-4.575572108789951</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.400657203574447</v>
+        <v>2.275425650476807</v>
       </c>
       <c r="F2075" t="n">
         <v>1.063219621806039</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.814519243243137</v>
+        <v>4.743942691390158</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.208139176130802</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.427227887691292</v>
+        <v>-4.563865390802945</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.507468148593517</v>
+        <v>2.382236595495876</v>
       </c>
       <c r="F2076" t="n">
         <v>1.074926339793046</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.923671531859609</v>
+        <v>4.853094980006629</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.211171514862206</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.32756438360763</v>
+        <v>-4.464201886719282</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.550365888958387</v>
+        <v>2.425134335860746</v>
       </c>
       <c r="F2077" t="n">
         <v>1.138113422996732</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.964616120513226</v>
+        <v>4.894039568660246</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.424076348140265</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.337880481773982</v>
+        <v>-4.474517984885634</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.759144282969904</v>
+        <v>2.633912729872264</v>
       </c>
       <c r="F2078" t="n">
         <v>1.138113422996732</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.177520953791285</v>
+        <v>5.106944401938304</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.423255015052354</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.337786513756609</v>
+        <v>-4.474424016868261</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.758360537088944</v>
+        <v>2.633128983991302</v>
       </c>
       <c r="F2079" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.176921537511765</v>
+        <v>5.106344985658785</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.417487000996708</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.345005337956453</v>
+        <v>-4.481642841068106</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.749704993353359</v>
+        <v>2.624473440255718</v>
       </c>
       <c r="F2080" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.171153523456119</v>
+        <v>5.100576971603139</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.417487000996708</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.344056914838415</v>
+        <v>-4.480694417950067</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.750084362600575</v>
+        <v>2.624852809502934</v>
       </c>
       <c r="F2081" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.171153523456119</v>
+        <v>5.100576971603139</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.4302146089778</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.501125373094039</v>
+        <v>-4.637762876205691</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.699984587279417</v>
+        <v>2.574753034181776</v>
       </c>
       <c r="F2082" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.183881131437211</v>
+        <v>5.113304579584231</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.502737159255168</v>
+        <v>4.432160607402188</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.495133126305228</v>
+        <v>-4.63177062941688</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.70432748441933</v>
+        <v>2.579095931321689</v>
       </c>
       <c r="F2083" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.185827129861599</v>
+        <v>5.115250578008618</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149213</v>
+        <v>3.741942347149212</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.496391295272937</v>
+        <v>4.425814743419957</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.40657516517446</v>
+        <v>-4.543212668286112</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.733404804889406</v>
+        <v>2.608173251791764</v>
       </c>
       <c r="F2084" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.179481265879367</v>
+        <v>5.108904714026387</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.844758409525133</v>
+        <v>3.630254641626907</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.607619455433952</v>
+        <v>4.483372627658114</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.40657516517446</v>
+        <v>-4.543212668286112</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.733404804889406</v>
+        <v>2.608173251791764</v>
       </c>
       <c r="F2085" t="n">
         <v>1.13848328434405</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.60068325242032</v>
+        <v>4.476436424644482</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.2%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>144.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>423.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.9%</t>
+          <t>-613.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-115.4%</t>
+          <t>-107.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.7%</t>
+          <t>-324.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-110.1%</t>
+          <t>-104.8%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.717477402231843</v>
+        <v>-3.687861467446691</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.206207164195483</v>
+        <v>1.218053538109544</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.745257800133196</v>
+        <v>-3.715641865348044</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.206592206803481</v>
+        <v>1.218438580717542</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.863638472863335</v>
+        <v>-3.834022538078182</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.997595657712079</v>
+        <v>1.00944203162614</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.972252551306666</v>
+        <v>-3.942636616521514</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.074299687053952</v>
+        <v>1.086146060968013</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.936843513058523</v>
+        <v>-3.907227578273371</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.102976328455532</v>
+        <v>1.114822702369593</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.898459850500372</v>
+        <v>-3.86884391571522</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.115749234821161</v>
+        <v>1.127595608735222</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.721343520465206</v>
+        <v>-3.691727585680054</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.18332479568053</v>
+        <v>1.195171169594591</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.766435765298751</v>
+        <v>-3.736819830513599</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.165971289509025</v>
+        <v>1.177817663423085</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.587060344059983</v>
+        <v>-3.557444409274831</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.231508433310946</v>
+        <v>1.243354807225007</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.63207455758059</v>
+        <v>-3.602458622795437</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.194310203234293</v>
+        <v>1.206156577148354</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.899079067853025</v>
+        <v>-3.869463133067873</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.093199961464265</v>
+        <v>1.105046335378326</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.000276849290198</v>
+        <v>-3.970660914505046</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.051924770785897</v>
+        <v>1.063771144699958</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.993765882675885</v>
+        <v>-3.964149947890733</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.052129118985939</v>
+        <v>1.0639754929</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.974727754968588</v>
+        <v>-3.945111820183436</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.056269089277103</v>
+        <v>1.068115463191164</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.027243557243408</v>
+        <v>-3.997627622458256</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.154557170001365</v>
+        <v>1.166403543915426</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.041110318577326</v>
+        <v>-4.011494383792173</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.149843794453931</v>
+        <v>1.161690168367993</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4473849384832159</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.000627326654982</v>
+        <v>-3.971011391869828</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.172045521619795</v>
+        <v>1.183891895533856</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4473849384832159</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.85288435641998</v>
+        <v>-3.823268421634826</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.129092930990996</v>
+        <v>1.140939304905057</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6151922957180991</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.936705577694678</v>
+        <v>-3.907089642909524</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.098358064012597</v>
+        <v>1.110204437926659</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6151922957180991</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.930552871641893</v>
+        <v>-3.90093693685674</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.10148149482537</v>
+        <v>1.113327868739431</v>
       </c>
       <c r="F1968" t="n">
         <v>0.6213450017708834</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.947362169792395</v>
+        <v>-3.917746235007241</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.093838252305279</v>
+        <v>1.10568462621934</v>
       </c>
       <c r="F1969" t="n">
         <v>0.6045357036203818</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.885064171016273</v>
+        <v>-3.85544823623112</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.185093005612549</v>
+        <v>1.19693937952661</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6498299678948238</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.683273973351115</v>
+        <v>-3.653658038565962</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.068101086392739</v>
+        <v>1.0799474603068</v>
       </c>
       <c r="F1971" t="n">
         <v>0.8478481600639782</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.73416068603731</v>
+        <v>-3.704544751252156</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.118036633640436</v>
+        <v>1.129883007554498</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7969614473777837</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.647549943387502</v>
+        <v>-3.617934008602349</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.167308666816403</v>
+        <v>1.179155040730464</v>
       </c>
       <c r="F1973" t="n">
         <v>0.875587178582942</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.707759241392787</v>
+        <v>-3.678143306607633</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.141760928438961</v>
+        <v>1.153607302353022</v>
       </c>
       <c r="F1974" t="n">
         <v>0.8153778805776575</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.658572592708436</v>
+        <v>-3.628956657923282</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.15992720595263</v>
+        <v>1.171773579866691</v>
       </c>
       <c r="F1975" t="n">
         <v>0.8153778805776575</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.614199461069867</v>
+        <v>-3.584583526284713</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.177539326043494</v>
+        <v>1.189385699957555</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8597510122162261</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.636679811928752</v>
+        <v>-3.607063877143598</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.16294097983853</v>
+        <v>1.174787353752591</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8597510122162261</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.589024081367696</v>
+        <v>-3.559408146582543</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.188385029090757</v>
+        <v>1.200231403004818</v>
       </c>
       <c r="F1978" t="n">
         <v>0.9074067427772817</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.488505922868942</v>
+        <v>-3.458889988083788</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.233484665864984</v>
+        <v>1.245331039779045</v>
       </c>
       <c r="F1979" t="n">
         <v>1.007924901276036</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.472600593436589</v>
+        <v>-3.442984658651436</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.226601470113797</v>
+        <v>1.238447844027858</v>
       </c>
       <c r="F1980" t="n">
         <v>0.9288122405667973</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.427762191828191</v>
+        <v>-3.398146257043038</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.248634533367785</v>
+        <v>1.260480907281846</v>
       </c>
       <c r="F1981" t="n">
         <v>0.9333556735116668</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917052</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.447260648070199</v>
+        <v>-3.417644713285046</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.244996090502059</v>
+        <v>1.256842464416121</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8852710322317625</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.403057810984299</v>
+        <v>-3.373441876199145</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.268556827864257</v>
+        <v>1.280403201778318</v>
       </c>
       <c r="F1983" t="n">
         <v>0.929473869317663</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.410617476821346</v>
+        <v>-3.381001542036192</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.263942961998685</v>
+        <v>1.275789335912747</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9842772733274823</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284874</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.252326059282074</v>
+        <v>-3.22271012449692</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.378507294197434</v>
+        <v>1.390353668111495</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9842772733274823</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.044684055647597</v>
+        <v>-3.015068120862444</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.460004800245478</v>
+        <v>1.471851174159539</v>
       </c>
       <c r="F1986" t="n">
         <v>1.191919276961958</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.993651962925069</v>
+        <v>-2.964036028139916</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.475365865572759</v>
+        <v>1.48721223948682</v>
       </c>
       <c r="F1987" t="n">
         <v>1.242951369684486</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.928427781797863</v>
+        <v>-2.89881184701271</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.518642942116346</v>
+        <v>1.530489316030407</v>
       </c>
       <c r="F1988" t="n">
         <v>1.308175550811692</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688255</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.89100076172673</v>
+        <v>-2.861384826941576</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.52957472244408</v>
+        <v>1.541421096358141</v>
       </c>
       <c r="F1989" t="n">
         <v>1.313427088840874</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992653</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.911112417761438</v>
+        <v>-2.881496482976285</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.522786852361437</v>
+        <v>1.534633226275498</v>
       </c>
       <c r="F1990" t="n">
         <v>1.324454433838293</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636279</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.882699154661554</v>
+        <v>-2.853083219876401</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.694709928622601</v>
+        <v>1.706556302536663</v>
       </c>
       <c r="F1991" t="n">
         <v>1.265478871091864</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957618</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.807916893636542</v>
+        <v>-2.778300958851388</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.844735742250424</v>
+        <v>1.856582116164485</v>
       </c>
       <c r="F1992" t="n">
         <v>1.340261132116877</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998749</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.781832809372734</v>
+        <v>-2.75221687458758</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.846877351969806</v>
+        <v>1.858723725883867</v>
       </c>
       <c r="F1993" t="n">
         <v>1.340261132116877</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.693954896263613</v>
+        <v>-2.66433896147846</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.880221712797233</v>
+        <v>1.892068086711295</v>
       </c>
       <c r="F1994" t="n">
         <v>1.456186774540228</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959852</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.68506243487033</v>
+        <v>-2.655446500085176</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.901333103081338</v>
+        <v>1.913179476995399</v>
       </c>
       <c r="F1995" t="n">
         <v>1.456186774540228</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.853538551840208</v>
+        <v>-2.823922617055054</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.825797703697971</v>
+        <v>1.837644077612032</v>
       </c>
       <c r="F1996" t="n">
         <v>1.428238938823647</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.407282359210768</v>
+        <v>-2.377666424425614</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.985569877937609</v>
+        <v>1.99741625185167</v>
       </c>
       <c r="F1997" t="n">
         <v>1.333520269154014</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.384561255527615</v>
+        <v>-2.354945320742462</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.985322341907774</v>
+        <v>1.997168715821835</v>
       </c>
       <c r="F1998" t="n">
         <v>1.333520269154014</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.513763068821658</v>
+        <v>-2.484147134036504</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.092547742441326</v>
+        <v>2.104394116355388</v>
       </c>
       <c r="F1999" t="n">
         <v>1.204318455859972</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.539637467295683</v>
+        <v>-2.51002153251053</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.119275805545363</v>
+        <v>2.131122179459424</v>
       </c>
       <c r="F2000" t="n">
         <v>1.249230064571713</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.53258277708051</v>
+        <v>-2.502966842295356</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.118773037620977</v>
+        <v>2.130619411535038</v>
       </c>
       <c r="F2001" t="n">
         <v>1.256284754786887</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331111</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.505631552754022</v>
+        <v>-2.476015617968868</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.139559680996314</v>
+        <v>2.151406054910375</v>
       </c>
       <c r="F2002" t="n">
         <v>1.271165100814606</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.527175780584809</v>
+        <v>-2.497559845799656</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.315045122008959</v>
+        <v>2.32689149592302</v>
       </c>
       <c r="F2003" t="n">
         <v>1.271165100814606</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.549583898389681</v>
+        <v>-2.519967963604528</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.298198569790003</v>
+        <v>2.310044943704065</v>
       </c>
       <c r="F2004" t="n">
         <v>1.271165100814606</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.577808133967281</v>
+        <v>-2.548192199182128</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.2889628751086</v>
+        <v>2.300809249022662</v>
       </c>
       <c r="F2005" t="n">
         <v>1.289141853265915</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516197</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.587249059855811</v>
+        <v>-2.557633125070658</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.341440222475036</v>
+        <v>2.353286596389097</v>
       </c>
       <c r="F2006" t="n">
         <v>1.411568970809306</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321627</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.676125691024285</v>
+        <v>-2.646509756239132</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.308780664552947</v>
+        <v>2.320627038467008</v>
       </c>
       <c r="F2007" t="n">
         <v>1.322692339640832</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.752455668625191</v>
+        <v>-2.722839733840038</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.27636048640636</v>
+        <v>2.288206860320421</v>
       </c>
       <c r="F2008" t="n">
         <v>1.322692339640832</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.846119613302732</v>
+        <v>-2.816503678517579</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.233715138138206</v>
+        <v>2.245561512052267</v>
       </c>
       <c r="F2009" t="n">
         <v>1.229028394963291</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343059</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.007688038829988</v>
+        <v>-2.978072104044834</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.167521778137456</v>
+        <v>2.179368152051517</v>
       </c>
       <c r="F2010" t="n">
         <v>1.102245471165411</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389342</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.115988700700107</v>
+        <v>-3.086372765914954</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.137274920255327</v>
+        <v>2.149121294169388</v>
       </c>
       <c r="F2011" t="n">
         <v>1.102245471165411</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378385</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.133792672420851</v>
+        <v>-3.104176737635698</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.122158528349969</v>
+        <v>2.13400490226403</v>
       </c>
       <c r="F2012" t="n">
         <v>1.03171084826021</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006969</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.161693459530324</v>
+        <v>-3.132077524745171</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.109522254633182</v>
+        <v>2.121368628547243</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9971139241172757</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.284219562233218</v>
+        <v>-3.254603627448065</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.057276257529223</v>
+        <v>2.069122631443284</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8745878214143818</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.514734058418807</v>
+        <v>-3.485118123633653</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.031776418645491</v>
+        <v>2.043622792559552</v>
       </c>
       <c r="F2015" t="n">
         <v>0.6440733252287931</v>
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814659</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.863479143643251</v>
+        <v>-3.738116615814317</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.032590103557561</v>
+        <v>2.082735114689134</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5805783699817004</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.899533408114546</v>
+        <v>3.926685207317629</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.017465561419391</v>
+        <v>-3.892103033590457</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.039975805592745</v>
+        <v>2.090120816724318</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5805783699817004</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.968513677260185</v>
+        <v>3.995665476463269</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.966943657591725</v>
+        <v>-3.841581129762791</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.046235769243931</v>
+        <v>2.096380780375505</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5805783699817004</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.954564879380306</v>
+        <v>3.981716678583389</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.219418811599449</v>
+        <v>-4.094056283770516</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.957116196696256</v>
+        <v>2.007261207827829</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5805783699817004</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.96643536843572</v>
+        <v>3.993587167638803</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.512314568078861</v>
+        <v>-4.386952040249928</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.841168428623435</v>
+        <v>1.891313439755008</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.5805783699817004</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.967645902954664</v>
+        <v>3.994797702157747</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.698978696213669</v>
+        <v>-4.573616168384736</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.770624519596833</v>
+        <v>1.820769530728406</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5085864004853354</v>
+        <v>0.5538393991571405</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.95572426268725</v>
+        <v>3.982876061890332</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916195</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.844999383127631</v>
+        <v>-4.719636855298698</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.707294097567437</v>
+        <v>1.757439108699011</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5447563073632835</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.945352260347125</v>
+        <v>3.972504059550207</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830322</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.936713392237216</v>
+        <v>-4.811350864408283</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.832812550622648</v>
+        <v>1.882957561754221</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5447563073632835</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.107556317046169</v>
+        <v>4.134708116249252</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071545</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.968365051297186</v>
+        <v>-4.843002523468252</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.814998524962474</v>
+        <v>1.865143536094047</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4943348514470383</v>
+        <v>0.5395878501188434</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.099301880663319</v>
+        <v>4.126453679866402</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.050299869566069</v>
+        <v>-4.924937341737135</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.792454015223412</v>
+        <v>1.842599026354985</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4844001058599581</v>
+        <v>0.5296531045317632</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.103570450879562</v>
+        <v>4.130722250082645</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.152275991814476</v>
+        <v>-5.026913463985543</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.760589204779951</v>
+        <v>1.810734215911525</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3824239836115505</v>
+        <v>0.4276769822833556</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.051310415986419</v>
+        <v>4.078462215189503</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231801</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.042269708337255</v>
+        <v>-4.916907180508321</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.796744605415015</v>
+        <v>1.846889616546589</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4056285555288257</v>
+        <v>0.4508815542006308</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.057386046380961</v>
+        <v>4.084537845584043</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818516</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.899210132596329</v>
+        <v>-4.773847604767395</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.85821844643336</v>
+        <v>1.908363457564934</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.413641982118805</v>
+        <v>0.4588949807906101</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.066444113056922</v>
+        <v>4.093595912260005</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.597763407124491</v>
+        <v>-4.472400879295558</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.986058019504631</v>
+        <v>2.036203030636204</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7603417062624473</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.25457303122256</v>
+        <v>4.281724830425643</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.622353651359675</v>
+        <v>-4.496991123530742</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.977193099563268</v>
+        <v>2.027338110694842</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7603417062624473</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.255544208975271</v>
+        <v>4.282696008178354</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.571315275353155</v>
+        <v>-4.445952747524221</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.998451354345632</v>
+        <v>2.048596365477205</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7603417062624473</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.256387113355027</v>
+        <v>4.283538912558109</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.530175980486524</v>
+        <v>-4.40481345265759</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.03394517116643</v>
+        <v>2.084090182298003</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7562280024572731</v>
+        <v>0.8014810011290782</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.30010878914915</v>
+        <v>4.327260588352233</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.433541068467884</v>
+        <v>-4.30817854063895</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.88878313209782</v>
+        <v>1.938928143229393</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.852862914475913</v>
+        <v>0.8981159131477181</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.174273732484269</v>
+        <v>4.201425531687352</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.564121802998726</v>
+        <v>-4.438759275169793</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.840052882359447</v>
+        <v>1.890197893491021</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7222821799450705</v>
+        <v>0.7675351786168756</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.099427335839728</v>
+        <v>4.12657913504281</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.399625468807765</v>
+        <v>-4.274262940978831</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.890278235111915</v>
+        <v>1.940423246243488</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.9320315128078375</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.182551955430387</v>
+        <v>4.209703754633471</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.322526867265892</v>
+        <v>-4.197164339436958</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.920305386165094</v>
+        <v>1.970450397296667</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.9320315128078375</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.181739665866817</v>
+        <v>4.2088914650699</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.332912062155781</v>
+        <v>-4.207549534326848</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.92602008733421</v>
+        <v>1.976165098465783</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8763933192461431</v>
+        <v>0.9216463179179482</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.185377328057956</v>
+        <v>4.212529127261039</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.351500220878006</v>
+        <v>-4.226137693049073</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.989421829621745</v>
+        <v>2.039566840753318</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8578051605239176</v>
+        <v>0.9030581591957227</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.245061438601046</v>
+        <v>4.272213237804129</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.351798767574042</v>
+        <v>-4.226436239745109</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.986171421761629</v>
+        <v>2.036316432893202</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8575066138278817</v>
+        <v>0.9027596124996868</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.241751321401723</v>
+        <v>4.268903120604806</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.250975633883614</v>
+        <v>-4.125613106054681</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.031031570177192</v>
+        <v>2.081176581308765</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8699708293122356</v>
+        <v>0.9152238279840407</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.253760745631727</v>
+        <v>4.280912544834809</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.060194273131208</v>
+        <v>-3.934831745302274</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.107473367956698</v>
+        <v>2.157618379088271</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.060752190064643</v>
+        <v>1.106005188736448</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.368358815561714</v>
+        <v>4.395510614764797</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.953230915281786</v>
+        <v>-3.827868387452852</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.130095556834063</v>
+        <v>2.180240567965637</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.119216798024445</v>
+        <v>1.164469796696249</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.383274426075191</v>
+        <v>4.410426225278274</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.897900327380024</v>
+        <v>-3.77253779955109</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.187194728606826</v>
+        <v>2.2373397397384</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.174547385926207</v>
+        <v>1.219800384598011</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.451439715428307</v>
+        <v>4.478591514631391</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.885846200467061</v>
+        <v>-3.760483672638127</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.185702947273449</v>
+        <v>2.235847958405023</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.186601512839169</v>
+        <v>1.231854511510974</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.452358759477523</v>
+        <v>4.479510558680605</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.927001320035282</v>
+        <v>-3.801638792206348</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.171121529630296</v>
+        <v>2.22126654076187</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.145446393270948</v>
+        <v>1.190699391942753</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.429546317920726</v>
+        <v>4.456698117123809</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.858952757343752</v>
+        <v>-3.733590229514818</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.211191980584791</v>
+        <v>2.261336991716365</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.213494955962478</v>
+        <v>1.258747954634283</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.483226481413526</v>
+        <v>4.510378280616609</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.090553150513253</v>
+        <v>-3.965190622684319</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.138754493490585</v>
+        <v>2.188899504622158</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.213494955962478</v>
+        <v>1.258747954634283</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.50342915158712</v>
+        <v>4.530580950790204</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.140604696042473</v>
+        <v>-4.015242168213538</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.102340111345779</v>
+        <v>2.152485122477353</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.213494955962478</v>
+        <v>1.258747954634283</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.487035387654003</v>
+        <v>4.514187186857086</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.315711528618918</v>
+        <v>-4.190349000789983</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.992549291908667</v>
+        <v>2.042694303040242</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.213494955962478</v>
+        <v>1.258747954634283</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.447287301247469</v>
+        <v>4.474439100450552</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.119611375188395</v>
+        <v>-3.99424884735946</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.078011972277817</v>
+        <v>2.128156983409391</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.409595109393001</v>
+        <v>1.454848108064806</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.571970012302723</v>
+        <v>4.599121811505806</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.966585983075111</v>
+        <v>-3.841223455246176</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.238393128696035</v>
+        <v>2.288538139827609</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.562620501506285</v>
+        <v>1.60787350017809</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.762956247143598</v>
+        <v>4.790108046346681</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.994893296948381</v>
+        <v>-3.869530769119446</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.414536428055019</v>
+        <v>2.464681439186593</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.562620501506285</v>
+        <v>1.60787350017809</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.950422472051891</v>
+        <v>4.977574271254973</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.161486522061903</v>
+        <v>-4.036123994232968</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.317302089363693</v>
+        <v>2.367447100495267</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.396027276392763</v>
+        <v>1.441280275064568</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.81986948833786</v>
+        <v>4.847021287540942</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.138450728700337</v>
+        <v>-4.013088200871402</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.330192809370037</v>
+        <v>2.380337820501611</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.396027276392763</v>
+        <v>1.441280275064568</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.823545890999577</v>
+        <v>4.85069769020266</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.109204748244641</v>
+        <v>-3.983842220415706</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.339509256675811</v>
+        <v>2.389654267807384</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.396027276392763</v>
+        <v>1.441280275064568</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.821163946123072</v>
+        <v>4.848315745326155</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.216130296122492</v>
+        <v>-4.090767768293557</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.294032276682305</v>
+        <v>2.344177287813879</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.289101728514912</v>
+        <v>1.334354727186716</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.754301856553997</v>
+        <v>4.78145365575708</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.36114885462974</v>
+        <v>-4.235786326800806</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.23745365542264</v>
+        <v>2.287598666554214</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.144083170007663</v>
+        <v>1.189336168679468</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.668719523592881</v>
+        <v>4.695871322795965</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687017</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.479490620414458</v>
+        <v>-4.354128092585523</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.290048188366506</v>
+        <v>2.34019319949808</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.154769208570553</v>
+        <v>1.200022207242358</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.775062385988369</v>
+        <v>4.802214185191452</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790807</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.530901042735166</v>
+        <v>-4.405538514906231</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.267269716564162</v>
+        <v>2.317414727695735</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.154769208570553</v>
+        <v>1.200022207242358</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.772848083114307</v>
+        <v>4.79999988231739</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.610320493942917</v>
+        <v>-4.484957966113983</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.23540506415535</v>
+        <v>2.285550075286924</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.154769208570553</v>
+        <v>1.200022207242358</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.772751211188597</v>
+        <v>4.79990301039168</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298402</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.705783491860135</v>
+        <v>-4.580420964031201</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.197213758546507</v>
+        <v>2.247358769678081</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.154769208570553</v>
+        <v>1.200022207242358</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.77274510474664</v>
+        <v>4.799896903949723</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960218005</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.64140758100942</v>
+        <v>-4.516045053180486</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.221060519449404</v>
+        <v>2.271205530580978</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.219145119421268</v>
+        <v>1.264398118093073</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.80946704781968</v>
+        <v>4.836618847022763</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.696776743141614</v>
+        <v>-4.57141421531268</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.204646672344253</v>
+        <v>2.254791683475826</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.219145119421268</v>
+        <v>1.264398118093073</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.815200865567407</v>
+        <v>4.842352664770489</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113284</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.742214522972441</v>
+        <v>-4.616851995143507</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.186009923754854</v>
+        <v>2.236154934886428</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.176300128743109</v>
+        <v>1.221553127414914</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.789032234503443</v>
+        <v>4.816184033706526</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.654007688824863</v>
+        <v>-4.528645160995929</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.241167050264204</v>
+        <v>2.291312061395778</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.176300128743109</v>
+        <v>1.221553127414914</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.808906627353762</v>
+        <v>4.836058426556845</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.547972693619553</v>
+        <v>-4.422610165790619</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.267281748871055</v>
+        <v>2.317426760002629</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.176300128743109</v>
+        <v>1.221553127414914</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.79260732787849</v>
+        <v>4.819759127081573</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.364761030486458</v>
+        <v>-4.239398502657524</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.342997363588339</v>
+        <v>2.393142374719913</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.176300128743109</v>
+        <v>1.221553127414914</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.795038277342536</v>
+        <v>4.822190076545619</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.98447283409158</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.293039583472607</v>
+        <v>-4.1591980747412</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.26690057638879</v>
+        <v>2.391013731734332</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.248021575756959</v>
+        <v>1.301753555331238</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.733285779545756</v>
+        <v>4.836101519143302</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.931388580012752</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.270666557864901</v>
+        <v>-4.136825049133494</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.222765532553044</v>
+        <v>2.346878687898586</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.259277326869861</v>
+        <v>1.313009306444139</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.686954976134668</v>
+        <v>4.789770715732215</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456734</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.116586784898107</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.303682853775646</v>
+        <v>-4.169841345044238</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.394757219074101</v>
+        <v>2.518870374419644</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.189839950203109</v>
+        <v>1.243571929777388</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.830490755019973</v>
+        <v>4.933306494617519</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883681</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.108508010726356</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.292155218126037</v>
+        <v>-4.15831370939463</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.391289499162194</v>
+        <v>2.515402654507736</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.248840608404472</v>
+        <v>1.30257258797875</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.85781237576904</v>
+        <v>4.960628115366585</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.112176123248145</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.389496719468406</v>
+        <v>-4.255655210736998</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.356021011147035</v>
+        <v>2.480134166492578</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.204420426238983</v>
+        <v>1.258152405813262</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.834828378991535</v>
+        <v>4.937644118589081</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.113427205440983</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.475352748808373</v>
+        <v>-4.341511240076965</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.322929681603886</v>
+        <v>2.447042836949429</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.162044357012848</v>
+        <v>1.215776336587127</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.810653819648692</v>
+        <v>4.913469559246239</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.095846407261485</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.484189546224492</v>
+        <v>-4.350348037493085</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.301814164457941</v>
+        <v>2.425927319803483</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.154602184371498</v>
+        <v>1.208334163945776</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.788607717884384</v>
+        <v>4.89142345748193</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.106010918306534</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.575572108789951</v>
+        <v>-4.441730600058543</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.275425650476807</v>
+        <v>2.399538805822349</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.063219621806039</v>
+        <v>1.116951601380318</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.743942691390158</v>
+        <v>4.846758430987705</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.208139176130802</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.563865390802945</v>
+        <v>-4.430023882071537</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.382236595495876</v>
+        <v>2.506349750841419</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.074926339793046</v>
+        <v>1.128658319367324</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.853094980006629</v>
+        <v>4.955910719604177</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.211171514862206</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.464201886719282</v>
+        <v>-4.330360377987875</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.425134335860746</v>
+        <v>2.549247491206289</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.138113422996732</v>
+        <v>1.19184540257101</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.894039568660246</v>
+        <v>4.996855308257793</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.424076348140265</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.474517984885634</v>
+        <v>-4.340676476154226</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.633912729872264</v>
+        <v>2.758025885217807</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.138113422996732</v>
+        <v>1.19184540257101</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.106944401938304</v>
+        <v>5.209760141535851</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.423255015052354</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.474424016868261</v>
+        <v>-4.340582508136854</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.633128983991302</v>
+        <v>2.757242139336846</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.106344985658785</v>
+        <v>5.209160725256331</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988024</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.417487000996708</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.481642841068106</v>
+        <v>-4.347801332336698</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.624473440255718</v>
+        <v>2.748586595601262</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.100576971603139</v>
+        <v>5.203392711200685</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.417487000996708</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.480694417950067</v>
+        <v>-4.34685290921866</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.624852809502934</v>
+        <v>2.748965964848477</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.100576971603139</v>
+        <v>5.203392711200685</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.4302146089778</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.637762876205691</v>
+        <v>-4.503921367474284</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.574753034181776</v>
+        <v>2.698866189527319</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.113304579584231</v>
+        <v>5.216120319181777</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.432160607402188</v>
+        <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.63177062941688</v>
+        <v>-4.497929120685472</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.579095931321689</v>
+        <v>2.703209086667232</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.115250578008618</v>
+        <v>5.218066317606165</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149212</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.425814743419957</v>
+        <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.543212668286112</v>
+        <v>-4.515125141426933</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.608173251791764</v>
+        <v>2.689984814388416</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.108904714026387</v>
+        <v>5.211720453623934</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.630254641626907</v>
+        <v>3.786681104889066</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.483372627658114</v>
+        <v>4.555897324350735</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.543212668286112</v>
+        <v>-4.515125141426933</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.608173251791764</v>
+        <v>2.689984814388416</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.13848328434405</v>
+        <v>1.192215263918328</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.476436424644482</v>
+        <v>4.548961121337102</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.3%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.1%</t>
+          <t>-609.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.2%</t>
+          <t>-99.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.2%</t>
+          <t>-323.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-104.8%</t>
+          <t>-110.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>77.9%</t>
         </is>
       </c>
     </row>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.687861467446691</v>
+        <v>-3.645950670351579</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.218053538109544</v>
+        <v>1.234817856947589</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.715641865348044</v>
+        <v>-3.673731068252932</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.218438580717542</v>
+        <v>1.235202899555587</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.834022538078182</v>
+        <v>-3.79211174098307</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.00944203162614</v>
+        <v>1.026206350464185</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.942636616521514</v>
+        <v>-3.900725819426401</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.086146060968013</v>
+        <v>1.102910379806058</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.907227578273371</v>
+        <v>-3.865316781178258</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.114822702369593</v>
+        <v>1.131587021207638</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.86884391571522</v>
+        <v>-3.826933118620107</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.127595608735222</v>
+        <v>1.144359927573267</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.691727585680054</v>
+        <v>-3.649816788584941</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.195171169594591</v>
+        <v>1.211935488432635</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.736819830513599</v>
+        <v>-3.694909033418487</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.177817663423085</v>
+        <v>1.194581982261131</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.557444409274831</v>
+        <v>-3.515533612179719</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.243354807225007</v>
+        <v>1.260119126063052</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.602458622795437</v>
+        <v>-3.560547825700325</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.206156577148354</v>
+        <v>1.222920895986399</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.869463133067873</v>
+        <v>-3.827552335972761</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.105046335378326</v>
+        <v>1.121810654216371</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.970660914505046</v>
+        <v>-3.928750117409933</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.063771144699958</v>
+        <v>1.080535463538003</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.964149947890733</v>
+        <v>-3.922239150795621</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.0639754929</v>
+        <v>1.080739811738045</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.945111820183436</v>
+        <v>-3.903201023088323</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.068115463191164</v>
+        <v>1.084879782029209</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.997627622458256</v>
+        <v>-3.955716825363143</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.166403543915426</v>
+        <v>1.183167862753471</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.011494383792173</v>
+        <v>-3.969583586697061</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.161690168367993</v>
+        <v>1.178454487206038</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4473849384832159</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.971011391869828</v>
+        <v>-3.929100594774716</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.183891895533856</v>
+        <v>1.200656214371902</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4473849384832159</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.823268421634826</v>
+        <v>-3.781357624539714</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.140939304905057</v>
+        <v>1.157703623743102</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6151922957180991</v>
@@ -46792,10 +46792,10 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.907089642909524</v>
+        <v>-3.865178845814412</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110204437926659</v>
+        <v>1.126968756764704</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6151922957180991</v>
@@ -46815,10 +46815,10 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.90093693685674</v>
+        <v>-3.859026139761628</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.113327868739431</v>
+        <v>1.130092187577476</v>
       </c>
       <c r="F1968" t="n">
         <v>0.6213450017708834</v>
@@ -46838,10 +46838,10 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.917746235007241</v>
+        <v>-3.875835437912129</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.10568462621934</v>
+        <v>1.122448945057385</v>
       </c>
       <c r="F1969" t="n">
         <v>0.6045357036203818</v>
@@ -46861,10 +46861,10 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.85544823623112</v>
+        <v>-3.813537439136007</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.19693937952661</v>
+        <v>1.213703698364655</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6498299678948238</v>
@@ -46884,10 +46884,10 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.653658038565962</v>
+        <v>-3.611747241470849</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.0799474603068</v>
+        <v>1.096711779144845</v>
       </c>
       <c r="F1971" t="n">
         <v>0.8478481600639782</v>
@@ -46907,10 +46907,10 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.704544751252156</v>
+        <v>-3.662633954157044</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.129883007554498</v>
+        <v>1.146647326392543</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7969614473777837</v>
@@ -46930,10 +46930,10 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.617934008602349</v>
+        <v>-3.576023211507237</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.179155040730464</v>
+        <v>1.195919359568509</v>
       </c>
       <c r="F1973" t="n">
         <v>0.875587178582942</v>
@@ -46953,10 +46953,10 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.678143306607633</v>
+        <v>-3.636232509512521</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.153607302353022</v>
+        <v>1.170371621191067</v>
       </c>
       <c r="F1974" t="n">
         <v>0.8153778805776575</v>
@@ -46976,10 +46976,10 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.628956657923282</v>
+        <v>-3.58704586082817</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.171773579866691</v>
+        <v>1.188537898704736</v>
       </c>
       <c r="F1975" t="n">
         <v>0.8153778805776575</v>
@@ -46999,10 +46999,10 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.584583526284713</v>
+        <v>-3.542672729189601</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.189385699957555</v>
+        <v>1.2061500187956</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8597510122162261</v>
@@ -47022,10 +47022,10 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.607063877143598</v>
+        <v>-3.565153080048486</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.174787353752591</v>
+        <v>1.191551672590636</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8597510122162261</v>
@@ -47045,10 +47045,10 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.559408146582543</v>
+        <v>-3.517497349487431</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.200231403004818</v>
+        <v>1.216995721842863</v>
       </c>
       <c r="F1978" t="n">
         <v>0.9074067427772817</v>
@@ -47068,10 +47068,10 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.458889988083788</v>
+        <v>-3.416979190988676</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.245331039779045</v>
+        <v>1.26209535861709</v>
       </c>
       <c r="F1979" t="n">
         <v>1.007924901276036</v>
@@ -47091,10 +47091,10 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.442984658651436</v>
+        <v>-3.401073861556323</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.238447844027858</v>
+        <v>1.255212162865903</v>
       </c>
       <c r="F1980" t="n">
         <v>0.9288122405667973</v>
@@ -47114,10 +47114,10 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.398146257043038</v>
+        <v>-3.356235459947925</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.260480907281846</v>
+        <v>1.277245226119891</v>
       </c>
       <c r="F1981" t="n">
         <v>0.9333556735116668</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.417644713285046</v>
+        <v>-3.375733916189934</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.256842464416121</v>
+        <v>1.273606783254166</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8852710322317625</v>
@@ -47160,10 +47160,10 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.373441876199145</v>
+        <v>-3.331531079104033</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.280403201778318</v>
+        <v>1.297167520616363</v>
       </c>
       <c r="F1983" t="n">
         <v>0.929473869317663</v>
@@ -47183,10 +47183,10 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.381001542036192</v>
+        <v>-3.33909074494108</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.275789335912747</v>
+        <v>1.292553654750792</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9842772733274823</v>
@@ -47206,10 +47206,10 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.22271012449692</v>
+        <v>-3.180799327401808</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.390353668111495</v>
+        <v>1.40711798694954</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9842772733274823</v>
@@ -47229,10 +47229,10 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.015068120862444</v>
+        <v>-2.973157323767332</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.471851174159539</v>
+        <v>1.488615492997584</v>
       </c>
       <c r="F1986" t="n">
         <v>1.191919276961958</v>
@@ -47252,10 +47252,10 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.964036028139916</v>
+        <v>-2.922125231044804</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.48721223948682</v>
+        <v>1.503976558324865</v>
       </c>
       <c r="F1987" t="n">
         <v>1.242951369684486</v>
@@ -47275,10 +47275,10 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.89881184701271</v>
+        <v>-2.856901049917598</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.530489316030407</v>
+        <v>1.547253634868452</v>
       </c>
       <c r="F1988" t="n">
         <v>1.308175550811692</v>
@@ -47298,10 +47298,10 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.861384826941576</v>
+        <v>-2.819474029846464</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.541421096358141</v>
+        <v>1.558185415196186</v>
       </c>
       <c r="F1989" t="n">
         <v>1.313427088840874</v>
@@ -47321,10 +47321,10 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.881496482976285</v>
+        <v>-2.839585685881172</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.534633226275498</v>
+        <v>1.551397545113543</v>
       </c>
       <c r="F1990" t="n">
         <v>1.324454433838293</v>
@@ -47344,10 +47344,10 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.853083219876401</v>
+        <v>-2.811172422781289</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.706556302536663</v>
+        <v>1.723320621374707</v>
       </c>
       <c r="F1991" t="n">
         <v>1.265478871091864</v>
@@ -47367,10 +47367,10 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.778300958851388</v>
+        <v>-2.736390161756276</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.856582116164485</v>
+        <v>1.87334643500253</v>
       </c>
       <c r="F1992" t="n">
         <v>1.340261132116877</v>
@@ -47390,10 +47390,10 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.75221687458758</v>
+        <v>-2.710306077492468</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.858723725883867</v>
+        <v>1.875488044721912</v>
       </c>
       <c r="F1993" t="n">
         <v>1.340261132116877</v>
@@ -47413,10 +47413,10 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.66433896147846</v>
+        <v>-2.622428164383348</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.892068086711295</v>
+        <v>1.90883240554934</v>
       </c>
       <c r="F1994" t="n">
         <v>1.456186774540228</v>
@@ -47436,10 +47436,10 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.655446500085176</v>
+        <v>-2.613535702990064</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.913179476995399</v>
+        <v>1.929943795833444</v>
       </c>
       <c r="F1995" t="n">
         <v>1.456186774540228</v>
@@ -47459,10 +47459,10 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.823922617055054</v>
+        <v>-2.782011819959942</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.837644077612032</v>
+        <v>1.854408396450077</v>
       </c>
       <c r="F1996" t="n">
         <v>1.428238938823647</v>
@@ -47482,10 +47482,10 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.377666424425614</v>
+        <v>-2.335755627330502</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.99741625185167</v>
+        <v>2.014180570689715</v>
       </c>
       <c r="F1997" t="n">
         <v>1.333520269154014</v>
@@ -47505,10 +47505,10 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.354945320742462</v>
+        <v>-2.31303452364735</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.997168715821835</v>
+        <v>2.01393303465988</v>
       </c>
       <c r="F1998" t="n">
         <v>1.333520269154014</v>
@@ -47528,10 +47528,10 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.484147134036504</v>
+        <v>-2.442236336941392</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.104394116355388</v>
+        <v>2.121158435193433</v>
       </c>
       <c r="F1999" t="n">
         <v>1.204318455859972</v>
@@ -47551,10 +47551,10 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.51002153251053</v>
+        <v>-2.468110735415418</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.131122179459424</v>
+        <v>2.147886498297469</v>
       </c>
       <c r="F2000" t="n">
         <v>1.249230064571713</v>
@@ -47574,10 +47574,10 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.502966842295356</v>
+        <v>-2.461056045200244</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.130619411535038</v>
+        <v>2.147383730373083</v>
       </c>
       <c r="F2001" t="n">
         <v>1.256284754786887</v>
@@ -47597,10 +47597,10 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.476015617968868</v>
+        <v>-2.434104820873756</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.151406054910375</v>
+        <v>2.16817037374842</v>
       </c>
       <c r="F2002" t="n">
         <v>1.271165100814606</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.497559845799656</v>
+        <v>-2.455649048704543</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.32689149592302</v>
+        <v>2.343655814761065</v>
       </c>
       <c r="F2003" t="n">
         <v>1.271165100814606</v>
@@ -47643,10 +47643,10 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.519967963604528</v>
+        <v>-2.478057166509415</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.310044943704065</v>
+        <v>2.326809262542109</v>
       </c>
       <c r="F2004" t="n">
         <v>1.271165100814606</v>
@@ -47666,10 +47666,10 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.548192199182128</v>
+        <v>-2.506281402087016</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.300809249022662</v>
+        <v>2.317573567860706</v>
       </c>
       <c r="F2005" t="n">
         <v>1.289141853265915</v>
@@ -47689,10 +47689,10 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.557633125070658</v>
+        <v>-2.515722327975546</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.353286596389097</v>
+        <v>2.370050915227142</v>
       </c>
       <c r="F2006" t="n">
         <v>1.411568970809306</v>
@@ -47712,10 +47712,10 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.646509756239132</v>
+        <v>-2.60459895914402</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.320627038467008</v>
+        <v>2.337391357305053</v>
       </c>
       <c r="F2007" t="n">
         <v>1.322692339640832</v>
@@ -47735,10 +47735,10 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.722839733840038</v>
+        <v>-2.680928936744925</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.288206860320421</v>
+        <v>2.304971179158466</v>
       </c>
       <c r="F2008" t="n">
         <v>1.322692339640832</v>
@@ -47758,10 +47758,10 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.816503678517579</v>
+        <v>-2.774592881422467</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.245561512052267</v>
+        <v>2.262325830890312</v>
       </c>
       <c r="F2009" t="n">
         <v>1.229028394963291</v>
@@ -47781,10 +47781,10 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.978072104044834</v>
+        <v>-2.936161306949722</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.179368152051517</v>
+        <v>2.196132470889562</v>
       </c>
       <c r="F2010" t="n">
         <v>1.102245471165411</v>
@@ -47804,10 +47804,10 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.086372765914954</v>
+        <v>-3.044461968819841</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.149121294169388</v>
+        <v>2.165885613007433</v>
       </c>
       <c r="F2011" t="n">
         <v>1.102245471165411</v>
@@ -47827,10 +47827,10 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.104176737635698</v>
+        <v>-3.062265940540585</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.13400490226403</v>
+        <v>2.150769221102075</v>
       </c>
       <c r="F2012" t="n">
         <v>1.03171084826021</v>
@@ -47850,10 +47850,10 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.132077524745171</v>
+        <v>-3.090166727650058</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.121368628547243</v>
+        <v>2.138132947385288</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9971139241172757</v>
@@ -47873,10 +47873,10 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.254603627448065</v>
+        <v>-3.212692830352952</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.069122631443284</v>
+        <v>2.085886950281329</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8745878214143818</v>
@@ -47896,10 +47896,10 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.485118123633653</v>
+        <v>-3.443207326538541</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.043622792559552</v>
+        <v>2.060387111397597</v>
       </c>
       <c r="F2015" t="n">
         <v>0.6440733252287931</v>
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.738116615814317</v>
+        <v>-3.791952411762985</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.082735114689134</v>
+        <v>2.061200796309667</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5805783699817004</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.926685207317629</v>
+        <v>3.899533408114546</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.892103033590457</v>
+        <v>-3.945938829539125</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.090120816724318</v>
+        <v>2.068586498344851</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5805783699817004</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.995665476463269</v>
+        <v>3.968513677260185</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.841581129762791</v>
+        <v>-3.895416925711459</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.096380780375505</v>
+        <v>2.074846461996038</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5805783699817004</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.981716678583389</v>
+        <v>3.954564879380306</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.094056283770516</v>
+        <v>-4.147892079719184</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.007261207827829</v>
+        <v>1.985726889448362</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5805783699817004</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.993587167638803</v>
+        <v>3.96643536843572</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.386952040249928</v>
+        <v>-4.440787836198596</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.891313439755008</v>
+        <v>1.869779121375541</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5805783699817004</v>
+        <v>0.5353253713098953</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.994797702157747</v>
+        <v>3.967645902954664</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.573616168384736</v>
+        <v>-4.627451964333404</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.820769530728406</v>
+        <v>1.799235212348939</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5538393991571405</v>
+        <v>0.5085864004853354</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.982876061890332</v>
+        <v>3.95572426268725</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.719636855298698</v>
+        <v>-4.773472651247366</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.757439108699011</v>
+        <v>1.735904790319543</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5447563073632835</v>
+        <v>0.4995033086914784</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.972504059550207</v>
+        <v>3.945352260347125</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.811350864408283</v>
+        <v>-4.865186660356951</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.882957561754221</v>
+        <v>1.861423243374754</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5447563073632835</v>
+        <v>0.4995033086914784</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.134708116249252</v>
+        <v>4.107556317046169</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.843002523468252</v>
+        <v>-4.89683831941692</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.865143536094047</v>
+        <v>1.84360921771458</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5395878501188434</v>
+        <v>0.4943348514470383</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.126453679866402</v>
+        <v>4.099301880663319</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.924937341737135</v>
+        <v>-4.978773137685804</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.842599026354985</v>
+        <v>1.821064707975518</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5296531045317632</v>
+        <v>0.4844001058599581</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.130722250082645</v>
+        <v>4.103570450879562</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.026913463985543</v>
+        <v>-5.080749259934211</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.810734215911525</v>
+        <v>1.789199897532058</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4276769822833556</v>
+        <v>0.3824239836115505</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.078462215189503</v>
+        <v>4.051310415986419</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.916907180508321</v>
+        <v>-4.970742976456989</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.846889616546589</v>
+        <v>1.825355298167121</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4508815542006308</v>
+        <v>0.4056285555288257</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.084537845584043</v>
+        <v>4.057386046380961</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.773847604767395</v>
+        <v>-4.827683400716063</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.908363457564934</v>
+        <v>1.886829139185466</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4588949807906101</v>
+        <v>0.413641982118805</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.093595912260005</v>
+        <v>4.066444113056922</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.472400879295558</v>
+        <v>-4.526236675244226</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.036203030636204</v>
+        <v>2.014668712256737</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7603417062624473</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.281724830425643</v>
+        <v>4.25457303122256</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.496991123530742</v>
+        <v>-4.55082691947941</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.027338110694842</v>
+        <v>2.005803792315374</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7603417062624473</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.282696008178354</v>
+        <v>4.255544208975271</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.445952747524221</v>
+        <v>-4.499788543472889</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.048596365477205</v>
+        <v>2.027062047097738</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7603417062624473</v>
+        <v>0.7150887075906422</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.283538912558109</v>
+        <v>4.256387113355027</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.40481345265759</v>
+        <v>-4.458649248606259</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.084090182298003</v>
+        <v>2.062555863918536</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8014810011290782</v>
+        <v>0.7562280024572731</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.327260588352233</v>
+        <v>4.30010878914915</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.30817854063895</v>
+        <v>-4.362014336587619</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.938928143229393</v>
+        <v>1.917393824849926</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8981159131477181</v>
+        <v>0.852862914475913</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.201425531687352</v>
+        <v>4.174273732484269</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.438759275169793</v>
+        <v>-4.492595071118461</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.890197893491021</v>
+        <v>1.868663575111553</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7675351786168756</v>
+        <v>0.7222821799450705</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.12657913504281</v>
+        <v>4.099427335839728</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.274262940978831</v>
+        <v>-4.328098736927499</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.940423246243488</v>
+        <v>1.918888927864021</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9320315128078375</v>
+        <v>0.8867785141360324</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.209703754633471</v>
+        <v>4.182551955430387</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.197164339436958</v>
+        <v>-4.251000135385627</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.970450397296667</v>
+        <v>1.9489160789172</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9320315128078375</v>
+        <v>0.8867785141360324</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.2088914650699</v>
+        <v>4.181739665866817</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.207549534326848</v>
+        <v>-4.261385330275516</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.976165098465783</v>
+        <v>1.954630780086316</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9216463179179482</v>
+        <v>0.8763933192461431</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.212529127261039</v>
+        <v>4.185377328057956</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.226137693049073</v>
+        <v>-4.279973488997741</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.039566840753318</v>
+        <v>2.018032522373852</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9030581591957227</v>
+        <v>0.8578051605239176</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.272213237804129</v>
+        <v>4.245061438601046</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.226436239745109</v>
+        <v>-4.280272035693777</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.036316432893202</v>
+        <v>2.014782114513736</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9027596124996868</v>
+        <v>0.8575066138278817</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.268903120604806</v>
+        <v>4.241751321401723</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.125613106054681</v>
+        <v>-4.179448902003349</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.081176581308765</v>
+        <v>2.059642262929298</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9152238279840407</v>
+        <v>0.8699708293122356</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.280912544834809</v>
+        <v>4.253760745631727</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.934831745302274</v>
+        <v>-3.988667541250942</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.157618379088271</v>
+        <v>2.136084060708804</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.106005188736448</v>
+        <v>1.060752190064643</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.395510614764797</v>
+        <v>4.368358815561714</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.827868387452852</v>
+        <v>-3.88170418340152</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.180240567965637</v>
+        <v>2.15870624958617</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.164469796696249</v>
+        <v>1.119216798024445</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.410426225278274</v>
+        <v>4.383274426075191</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.77253779955109</v>
+        <v>-3.826373595499758</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.2373397397384</v>
+        <v>2.215805421358933</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.219800384598011</v>
+        <v>1.174547385926207</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.478591514631391</v>
+        <v>4.451439715428307</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.760483672638127</v>
+        <v>-3.814319468586795</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.235847958405023</v>
+        <v>2.214313640025556</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.231854511510974</v>
+        <v>1.186601512839169</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.479510558680605</v>
+        <v>4.452358759477523</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.801638792206348</v>
+        <v>-3.855474588155016</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.22126654076187</v>
+        <v>2.199732222382403</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.190699391942753</v>
+        <v>1.145446393270948</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.456698117123809</v>
+        <v>4.429546317920726</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.733590229514818</v>
+        <v>-3.787426025463486</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.261336991716365</v>
+        <v>2.239802673336897</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.258747954634283</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.510378280616609</v>
+        <v>4.483226481413526</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.965190622684319</v>
+        <v>-4.019026418632987</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.188899504622158</v>
+        <v>2.167365186242691</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.258747954634283</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.530580950790204</v>
+        <v>4.50342915158712</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.015242168213538</v>
+        <v>-4.069077964162206</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.152485122477353</v>
+        <v>2.130950804097886</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.258747954634283</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.514187186857086</v>
+        <v>4.487035387654003</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.190349000789983</v>
+        <v>-4.244184796738651</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.042694303040242</v>
+        <v>2.021159984660774</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.258747954634283</v>
+        <v>1.213494955962478</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.474439100450552</v>
+        <v>4.447287301247469</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-3.99424884735946</v>
+        <v>-4.048084643308128</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.128156983409391</v>
+        <v>2.106622665029923</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.454848108064806</v>
+        <v>1.409595109393001</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.599121811505806</v>
+        <v>4.571970012302723</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.841223455246176</v>
+        <v>-3.895059251194844</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.288538139827609</v>
+        <v>2.267003821448141</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.60787350017809</v>
+        <v>1.562620501506285</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.790108046346681</v>
+        <v>4.762956247143598</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.869530769119446</v>
+        <v>-3.884502794861214</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.464681439186593</v>
+        <v>2.458692628889886</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.60787350017809</v>
+        <v>1.562620501506285</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.977574271254973</v>
+        <v>4.950422472051891</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.036123994232968</v>
+        <v>-4.051096019974736</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.367447100495267</v>
+        <v>2.36145829019856</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.441280275064568</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.847021287540942</v>
+        <v>4.81986948833786</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.013088200871402</v>
+        <v>-4.02806022661317</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.380337820501611</v>
+        <v>2.374349010204904</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.441280275064568</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.85069769020266</v>
+        <v>4.823545890999577</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.983842220415706</v>
+        <v>-3.998814246157474</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.389654267807384</v>
+        <v>2.383665457510677</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.441280275064568</v>
+        <v>1.396027276392763</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.848315745326155</v>
+        <v>4.821163946123072</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.090767768293557</v>
+        <v>-4.105739794035325</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.344177287813879</v>
+        <v>2.338188477517172</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.334354727186716</v>
+        <v>1.289101728514912</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.78145365575708</v>
+        <v>4.754301856553997</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.235786326800806</v>
+        <v>-4.250758352542574</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.287598666554214</v>
+        <v>2.281609856257507</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.189336168679468</v>
+        <v>1.144083170007663</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.695871322795965</v>
+        <v>4.668719523592881</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.354128092585523</v>
+        <v>-4.369100118327292</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.34019319949808</v>
+        <v>2.334204389201373</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.200022207242358</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.802214185191452</v>
+        <v>4.775062385988369</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.405538514906231</v>
+        <v>-4.420510540647999</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.317414727695735</v>
+        <v>2.311425917399028</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.200022207242358</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.79999988231739</v>
+        <v>4.772848083114307</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.484957966113983</v>
+        <v>-4.499929991855751</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.285550075286924</v>
+        <v>2.279561264990217</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.200022207242358</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.79990301039168</v>
+        <v>4.772751211188597</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.580420964031201</v>
+        <v>-4.595392989772969</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.247358769678081</v>
+        <v>2.241369959381373</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.200022207242358</v>
+        <v>1.154769208570553</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.799896903949723</v>
+        <v>4.77274510474664</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.516045053180486</v>
+        <v>-4.531017078922254</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.271205530580978</v>
+        <v>2.26521672028427</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.264398118093073</v>
+        <v>1.219145119421268</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.836618847022763</v>
+        <v>4.80946704781968</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.57141421531268</v>
+        <v>-4.586386241054448</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.254791683475826</v>
+        <v>2.248802873179119</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.264398118093073</v>
+        <v>1.219145119421268</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.842352664770489</v>
+        <v>4.815200865567407</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.616851995143507</v>
+        <v>-4.631824020885275</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.236154934886428</v>
+        <v>2.23016612458972</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221553127414914</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.816184033706526</v>
+        <v>4.789032234503443</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.528645160995929</v>
+        <v>-4.543617186737697</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.291312061395778</v>
+        <v>2.28532325109907</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221553127414914</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.836058426556845</v>
+        <v>4.808906627353762</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.422610165790619</v>
+        <v>-4.437582191532387</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.317426760002629</v>
+        <v>2.311437949705923</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221553127414914</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.819759127081573</v>
+        <v>4.79260732787849</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.239398502657524</v>
+        <v>-4.254370528399292</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.393142374719913</v>
+        <v>2.387153564423206</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221553127414914</v>
+        <v>1.176300128743109</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.822190076545619</v>
+        <v>4.795038277342536</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.1591980747412</v>
+        <v>-4.182649081385441</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.391013731734332</v>
+        <v>2.381633329076636</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.301753555331238</v>
+        <v>1.248021575756959</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.836101519143302</v>
+        <v>4.803862331398736</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.136825049133494</v>
+        <v>-4.160276055777735</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.346878687898586</v>
+        <v>2.33749828524089</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.313009306444139</v>
+        <v>1.259277326869861</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.789770715732215</v>
+        <v>4.757531527987648</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.169841345044238</v>
+        <v>-4.19329235168848</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.518870374419644</v>
+        <v>2.509489971761948</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.243571929777388</v>
+        <v>1.189839950203109</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.933306494617519</v>
+        <v>4.901067306872952</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.15831370939463</v>
+        <v>-4.181764716038871</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.515402654507736</v>
+        <v>2.50602225185004</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.30257258797875</v>
+        <v>1.248840608404472</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.960628115366585</v>
+        <v>4.928388927622019</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.255655210736998</v>
+        <v>-4.27910621738124</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.480134166492578</v>
+        <v>2.470753763834881</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.258152405813262</v>
+        <v>1.204420426238983</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.937644118589081</v>
+        <v>4.905404930844514</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.341511240076965</v>
+        <v>-4.364962246721206</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.447042836949429</v>
+        <v>2.437662434291733</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.215776336587127</v>
+        <v>1.162044357012848</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.913469559246239</v>
+        <v>4.881230371501672</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.350348037493085</v>
+        <v>-4.373799044137326</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.425927319803483</v>
+        <v>2.416546917145786</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.208334163945776</v>
+        <v>1.154602184371498</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.89142345748193</v>
+        <v>4.859184269737363</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.441730600058543</v>
+        <v>-4.465181606702784</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.399538805822349</v>
+        <v>2.390158403164652</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.116951601380318</v>
+        <v>1.063219621806039</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.846758430987705</v>
+        <v>4.814519243243137</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.430023882071537</v>
+        <v>-4.453474888715778</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.506349750841419</v>
+        <v>2.496969348183723</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.128658319367324</v>
+        <v>1.074926339793046</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.955910719604177</v>
+        <v>4.923671531859609</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.330360377987875</v>
+        <v>-4.353811384632116</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.549247491206289</v>
+        <v>2.539867088548593</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.19184540257101</v>
+        <v>1.138113422996732</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.996855308257793</v>
+        <v>4.964616120513226</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.340676476154226</v>
+        <v>-4.364127482798468</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.758025885217807</v>
+        <v>2.74864548256011</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.19184540257101</v>
+        <v>1.138113422996732</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.209760141535851</v>
+        <v>5.177520953791285</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.340582508136854</v>
+        <v>-4.364033514781095</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.757242139336846</v>
+        <v>2.747861736679149</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.209160725256331</v>
+        <v>5.176921537511765</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.347801332336698</v>
+        <v>-4.371252338980939</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.748586595601262</v>
+        <v>2.739206192943565</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.203392711200685</v>
+        <v>5.171153523456119</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.34685290921866</v>
+        <v>-4.370303915862901</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.748965964848477</v>
+        <v>2.739585562190781</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.203392711200685</v>
+        <v>5.171153523456119</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.503921367474284</v>
+        <v>-4.527372374118524</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.698866189527319</v>
+        <v>2.689485786869623</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.216120319181777</v>
+        <v>5.183881131437211</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.497929120685472</v>
+        <v>-4.521380127329713</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.703209086667232</v>
+        <v>2.693828684009536</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.218066317606165</v>
+        <v>5.185827129861599</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.515125141426933</v>
+        <v>-4.432822166198945</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.689984814388416</v>
+        <v>2.722906004479611</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.211720453623934</v>
+        <v>5.179481265879367</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.786681104889066</v>
+        <v>3.905666596381566</v>
       </c>
       <c r="C2085" t="n">
         <v>4.555897324350735</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.515125141426933</v>
+        <v>-4.476266843155955</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.689984814388416</v>
+        <v>2.765034162774605</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.192215263918328</v>
+        <v>1.13848328434405</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.548961121337102</v>
+        <v>5.238987294957165</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240912.xlsx
+++ b/tame_output/ON/bt/strategyON_20240912.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>101.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>144.0%</t>
+          <t>137.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>423.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-609.2%</t>
+          <t>-618.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-109.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.0%</t>
+          <t>-322.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-110.1%</t>
+          <t>-95.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.645950670351579</v>
+        <v>-3.717477402231843</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.234817856947589</v>
+        <v>1.206207164195483</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.673731068252932</v>
+        <v>-3.745257800133196</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.235202899555587</v>
+        <v>1.206592206803481</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.79211174098307</v>
+        <v>-3.863638472863335</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.026206350464185</v>
+        <v>0.997595657712079</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.900725819426401</v>
+        <v>-3.972252551306666</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.102910379806058</v>
+        <v>1.074299687053952</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.865316781178258</v>
+        <v>-3.936843513058523</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.131587021207638</v>
+        <v>1.102976328455532</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.826933118620107</v>
+        <v>-3.898459850500372</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.144359927573267</v>
+        <v>1.115749234821161</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.649816788584941</v>
+        <v>-3.721343520465206</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.211935488432635</v>
+        <v>1.18332479568053</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.694909033418487</v>
+        <v>-3.766435765298751</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.194581982261131</v>
+        <v>1.165971289509025</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.515533612179719</v>
+        <v>-3.587060344059983</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.260119126063052</v>
+        <v>1.231508433310946</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.560547825700325</v>
+        <v>-3.63207455758059</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.222920895986399</v>
+        <v>1.194310203234293</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.827552335972761</v>
+        <v>-3.899079067853025</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.121810654216371</v>
+        <v>1.093199961464265</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.928750117409933</v>
+        <v>-4.000276849290198</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.080535463538003</v>
+        <v>1.051924770785897</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.922239150795621</v>
+        <v>-3.993765882675885</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.080739811738045</v>
+        <v>1.052129118985939</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.903201023088323</v>
+        <v>-3.974727754968588</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.084879782029209</v>
+        <v>1.056269089277103</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.955716825363143</v>
+        <v>-4.027243557243408</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.183167862753471</v>
+        <v>1.154557170001365</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.969583586697061</v>
+        <v>-4.066564293339617</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.178454487206038</v>
+        <v>1.139662204549015</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4473849384832159</v>
+        <v>0.5092628229542419</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.035075309288539</v>
+        <v>3.072202039971155</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.929100594774716</v>
+        <v>-4.026081301417272</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.200656214371902</v>
+        <v>1.161863931714879</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4473849384832159</v>
+        <v>0.5092628229542419</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.041083839685465</v>
+        <v>3.078210570368081</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.781357624539714</v>
+        <v>-3.87833833118227</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.157703623743102</v>
+        <v>1.118911341086079</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6151922957180991</v>
+        <v>0.677070180189125</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.039718475303594</v>
+        <v>3.07684520598621</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.865178845814412</v>
+        <v>-3.962159552456968</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.126968756764704</v>
+        <v>1.088176474107681</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6151922957180991</v>
+        <v>0.677070180189125</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.042512096835075</v>
+        <v>3.079638827517691</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.859026139761628</v>
+        <v>-3.956006846404184</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.130092187577476</v>
+        <v>1.091299904920453</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6213450017708834</v>
+        <v>0.6832228862419093</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.046866068858404</v>
+        <v>3.08399279954102</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.875835437912129</v>
+        <v>-3.972816144554685</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.122448945057385</v>
+        <v>1.083656662400363</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6045357036203818</v>
+        <v>0.6664135880914077</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.035860966708213</v>
+        <v>3.072987697390829</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.813537439136007</v>
+        <v>-3.910518145778563</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.213703698364655</v>
+        <v>1.174911415707633</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6498299678948238</v>
+        <v>0.7117078523658498</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.1293730790697</v>
+        <v>3.166499809752315</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.611747241470849</v>
+        <v>-3.708727948113405</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.096711779144845</v>
+        <v>1.057919496487823</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8478481600639782</v>
+        <v>0.9097260445350042</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.05047599608532</v>
+        <v>3.087602726767935</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.662633954157044</v>
+        <v>-3.7596146607996</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.146647326392543</v>
+        <v>1.10785504373552</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7969614473777837</v>
+        <v>0.8588393318488097</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.090234200795778</v>
+        <v>3.127360931478393</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.576023211507237</v>
+        <v>-3.673003918149793</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.195919359568509</v>
+        <v>1.157127076911487</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.875587178582942</v>
+        <v>0.9374650630539679</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.152037375634916</v>
+        <v>3.189164106317532</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.636232509512521</v>
+        <v>-3.733213216155077</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.170371621191067</v>
+        <v>1.131579338534045</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8153778805776575</v>
+        <v>0.8772557650486834</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.114447777656418</v>
+        <v>3.151574508339033</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.58704586082817</v>
+        <v>-3.684026567470726</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.188537898704736</v>
+        <v>1.149745616047714</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8153778805776575</v>
+        <v>0.8772557650486834</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.112939395696346</v>
+        <v>3.150066126378961</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316253</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.542672729189601</v>
+        <v>-3.639653435832157</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.2061500187956</v>
+        <v>1.167357736138577</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8597510122162261</v>
+        <v>0.921628896687252</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.139426142114923</v>
+        <v>3.176552872797539</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.565153080048486</v>
+        <v>-3.662133786691042</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.191551672590636</v>
+        <v>1.152759389933614</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8597510122162261</v>
+        <v>0.921628896687252</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.133819936253514</v>
+        <v>3.170946666936129</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.517497349487431</v>
+        <v>-3.614478056129986</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.216995721842863</v>
+        <v>1.178203439185841</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9074067427772817</v>
+        <v>0.9692846272483077</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.168795131617952</v>
+        <v>3.205921862300567</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.416979190988676</v>
+        <v>-3.513959897631231</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.26209535861709</v>
+        <v>1.223303075960068</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.007924901276036</v>
+        <v>1.069802785747062</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.23399840009193</v>
+        <v>3.271125130774545</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.401073861556323</v>
+        <v>-3.498054568198879</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.255212162865903</v>
+        <v>1.216419880208881</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9288122405667973</v>
+        <v>0.9906901250378233</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.173285476142258</v>
+        <v>3.210412206824874</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.356235459947925</v>
+        <v>-3.453216166590481</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.277245226119891</v>
+        <v>1.238452943462869</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9333556735116668</v>
+        <v>0.9952335579826928</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.180109238519809</v>
+        <v>3.217235969202424</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917052</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.375733916189934</v>
+        <v>-3.472714622832489</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.273606783254166</v>
+        <v>1.234814500597143</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8852710322317625</v>
+        <v>0.9471489167027884</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.155419393382944</v>
+        <v>3.19254612406556</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.331531079104033</v>
+        <v>-3.425639421592185</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.297167520616363</v>
+        <v>1.259524183621102</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.929473869317663</v>
+        <v>0.9942241179430924</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.187820698162321</v>
+        <v>3.226670847337579</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.33909074494108</v>
+        <v>-3.433199087429232</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.292553654750792</v>
+        <v>1.254910317755531</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9842772733274823</v>
+        <v>1.049027521952912</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.219112741037461</v>
+        <v>3.257962890212718</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.180799327401808</v>
+        <v>-3.27490766988996</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.40711798694954</v>
+        <v>1.369474649954279</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9842772733274823</v>
+        <v>1.049027521952912</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.2703605062205</v>
+        <v>3.309210655395758</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.973157323767332</v>
+        <v>-3.067265666255484</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.488615492997584</v>
+        <v>1.450972156002323</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.191919276961958</v>
+        <v>1.256669525587388</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.393386412995439</v>
+        <v>3.432236562170697</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.922125231044804</v>
+        <v>-3.016233573532956</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.503976558324865</v>
+        <v>1.466333221329604</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.242951369684486</v>
+        <v>1.307701618309916</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.418953896867226</v>
+        <v>3.457804046042483</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.856901049917598</v>
+        <v>-2.95100939240575</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.547253634868452</v>
+        <v>1.509610297873192</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.308175550811692</v>
+        <v>1.372925799437122</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.475275809636254</v>
+        <v>3.514125958811512</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.819474029846464</v>
+        <v>-2.913582372334616</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.558185415196186</v>
+        <v>1.520542078200925</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.313427088840874</v>
+        <v>1.378177337466303</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.474387704753044</v>
+        <v>3.513237853928301</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.839585685881172</v>
+        <v>-2.933694028369324</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.551397545113543</v>
+        <v>1.513754208118282</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.324454433838293</v>
+        <v>1.389204682463723</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.482260904082735</v>
+        <v>3.521111053257993</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.811172422781289</v>
+        <v>-2.905280765269441</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.723320621374707</v>
+        <v>1.685677284379447</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.265478871091864</v>
+        <v>1.330229119717294</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.607433337456089</v>
+        <v>3.646283486631347</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.736390161756276</v>
+        <v>-2.830498504244428</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.87334643500253</v>
+        <v>1.835703098007269</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.340261132116877</v>
+        <v>1.405011380742306</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.772415603288914</v>
+        <v>3.811265752464172</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.710306077492468</v>
+        <v>-2.80441441998062</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.875488044721912</v>
+        <v>1.837844707726651</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.340261132116877</v>
+        <v>1.405011380742306</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.764123579302773</v>
+        <v>3.802973728478031</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.622428164383348</v>
+        <v>-2.7165365068715</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.90883240554934</v>
+        <v>1.871189068554079</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.456186774540228</v>
+        <v>1.520937023165657</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.831872160340563</v>
+        <v>3.87072230951582</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.613535702990064</v>
+        <v>-2.707644045478216</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.929943795833444</v>
+        <v>1.892300458838184</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.456186774540228</v>
+        <v>1.520937023165657</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.849426566067354</v>
+        <v>3.888276715242612</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.782011819959942</v>
+        <v>-2.876120162448094</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.854408396450077</v>
+        <v>1.816765059454816</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.428238938823647</v>
+        <v>1.492989187449077</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.824512912041989</v>
+        <v>3.863363061217247</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.335755627330502</v>
+        <v>-2.429863969818654</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.014180570689715</v>
+        <v>1.976537233694454</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.333520269154014</v>
+        <v>1.398270517779444</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.748951407428072</v>
+        <v>3.78780155660333</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.31303452364735</v>
+        <v>-2.407142866135501</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.01393303465988</v>
+        <v>1.97628969766462</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.333520269154014</v>
+        <v>1.398270517779444</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.739615429924976</v>
+        <v>3.778465579100234</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.442236336941392</v>
+        <v>-2.536344679429544</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.121158435193433</v>
+        <v>2.083515098198172</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.204318455859972</v>
+        <v>1.269068704485402</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.82100046779972</v>
+        <v>3.859850616974978</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.468110735415418</v>
+        <v>-2.56221907790357</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.147886498297469</v>
+        <v>2.110243161302208</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.249230064571713</v>
+        <v>1.313980313197143</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.885025255520411</v>
+        <v>3.923875404695669</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.461056045200244</v>
+        <v>-2.555164387688396</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.147383730373083</v>
+        <v>2.109740393377822</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.256284754786887</v>
+        <v>1.321035003412317</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.885933425639061</v>
+        <v>3.924783574814318</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.434104820873756</v>
+        <v>-2.528213163361908</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.16817037374842</v>
+        <v>2.130527036753159</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.271165100814606</v>
+        <v>1.335915349440036</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.904867786900434</v>
+        <v>3.943717936075691</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.455649048704543</v>
+        <v>-2.549757391192695</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.343655814761065</v>
+        <v>2.306012477765804</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.271165100814606</v>
+        <v>1.335915349440036</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.088970919045393</v>
+        <v>4.127821068220651</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.478057166509415</v>
+        <v>-2.572165508997567</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.326809262542109</v>
+        <v>2.289165925546849</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.271165100814606</v>
+        <v>1.335915349440036</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.081087613948386</v>
+        <v>4.119937763123644</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.506281402087016</v>
+        <v>-2.600389744575168</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.317573567860706</v>
+        <v>2.279930230865446</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.289141853265915</v>
+        <v>1.353892101891344</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.093927664968809</v>
+        <v>4.132777814144067</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.515722327975546</v>
+        <v>-2.609830670463698</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.370050915227142</v>
+        <v>2.332407578231881</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.411568970809306</v>
+        <v>1.476319219434736</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.223637653216691</v>
+        <v>4.262487802391949</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.60459895914402</v>
+        <v>-2.698707301632171</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.337391357305053</v>
+        <v>2.299748020309792</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.322692339640832</v>
+        <v>1.387442588266262</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.173202769060908</v>
+        <v>4.212052918236165</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.680928936744925</v>
+        <v>-2.775037279233077</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304971179158466</v>
+        <v>2.267327842163205</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.322692339640832</v>
+        <v>1.387442588266262</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.171314581954683</v>
+        <v>4.21016473112994</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.774592881422467</v>
+        <v>-2.868701223910619</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.262325830890312</v>
+        <v>2.224682493895051</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.229028394963291</v>
+        <v>1.293778643588721</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10993644475102</v>
+        <v>4.148786593926278</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.936161306949722</v>
+        <v>-3.030269649437874</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.196132470889562</v>
+        <v>2.158489133894301</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.102245471165411</v>
+        <v>1.166995719790841</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.032300700682445</v>
+        <v>4.071150849857703</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.044461968819841</v>
+        <v>-3.138570311307993</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.165885613007433</v>
+        <v>2.128242276012172</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.102245471165411</v>
+        <v>1.166995719790841</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.045374107548364</v>
+        <v>4.084224256723622</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.062265940540585</v>
+        <v>-3.156374283028737</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.150769221102075</v>
+        <v>2.113125884106815</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.03171084826021</v>
+        <v>1.09646109688564</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.995058530588183</v>
+        <v>4.03390867976344</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.090166727650058</v>
+        <v>-3.18427507013821</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.138132947385288</v>
+        <v>2.100489610390027</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9971139241172757</v>
+        <v>1.061864172742705</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.972824417229424</v>
+        <v>4.011674566404682</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.212692830352952</v>
+        <v>-3.306801172841104</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.085886950281329</v>
+        <v>2.048243613286068</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8745878214143818</v>
+        <v>0.9393380700398115</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.896073199584887</v>
+        <v>3.934923348760145</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.443207326538541</v>
+        <v>-3.537315669026693</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.060387111397597</v>
+        <v>2.022743774402336</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6440733252287931</v>
+        <v>0.7088235738542228</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.824470461464037</v>
+        <v>3.863320610639295</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.791952411762985</v>
+        <v>-3.886060754251137</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.061200796309667</v>
+        <v>2.023557459314406</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.600075619935325</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.899533408114546</v>
+        <v>3.938383557289804</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.945938829539125</v>
+        <v>-4.040047172027277</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.068586498344851</v>
+        <v>2.030943161349589</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.600075619935325</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.968513677260185</v>
+        <v>4.007363826435443</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.895416925711459</v>
+        <v>-3.989525268199611</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.074846461996038</v>
+        <v>2.037203125000777</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.600075619935325</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.954564879380306</v>
+        <v>3.993415028555564</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.147892079719184</v>
+        <v>-4.242000422207336</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.985726889448362</v>
+        <v>1.948083552453101</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.600075619935325</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.96643536843572</v>
+        <v>4.005285517610978</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.440787836198596</v>
+        <v>-4.534896178686748</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.869779121375541</v>
+        <v>1.83213578438028</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5353253713098953</v>
+        <v>0.600075619935325</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.967645902954664</v>
+        <v>4.006496052129922</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.627451964333404</v>
+        <v>-4.721560306821556</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.799235212348939</v>
+        <v>1.761591875353678</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5085864004853354</v>
+        <v>0.5733366491107651</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.95572426268725</v>
+        <v>3.994574411862507</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.773472651247366</v>
+        <v>-4.867580993735518</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.735904790319543</v>
+        <v>1.698261453324283</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5642535573169081</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.945352260347125</v>
+        <v>3.984202409522382</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.865186660356951</v>
+        <v>-4.959295002845103</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.861423243374754</v>
+        <v>1.823779906379493</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4995033086914784</v>
+        <v>0.5642535573169081</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.107556317046169</v>
+        <v>4.146406466221427</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.89683831941692</v>
+        <v>-4.990946661905072</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.84360921771458</v>
+        <v>1.805965880719319</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4943348514470383</v>
+        <v>0.5590851000724679</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.099301880663319</v>
+        <v>4.138152029838577</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868151</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.978773137685804</v>
+        <v>-5.072881480173955</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.821064707975518</v>
+        <v>1.783421370980257</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4844001058599581</v>
+        <v>0.5491503544853877</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.103570450879562</v>
+        <v>4.14242060005482</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.080749259934211</v>
+        <v>-5.174857602422363</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.789199897532058</v>
+        <v>1.751556560536797</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3824239836115505</v>
+        <v>0.4471742322369802</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.051310415986419</v>
+        <v>4.090160565161677</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.970742976456989</v>
+        <v>-5.064851318945141</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.825355298167121</v>
+        <v>1.787711961171861</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4056285555288257</v>
+        <v>0.4703788041542554</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.057386046380961</v>
+        <v>4.096236195556218</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.827683400716063</v>
+        <v>-4.921791743204215</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.886829139185466</v>
+        <v>1.849185802190205</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.413641982118805</v>
+        <v>0.4783922307442346</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.066444113056922</v>
+        <v>4.10529426223218</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.526236675244226</v>
+        <v>-4.620345017732378</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.014668712256737</v>
+        <v>1.977025375261476</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7798389562160719</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.25457303122256</v>
+        <v>4.293423180397818</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.55082691947941</v>
+        <v>-4.644935261967562</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.005803792315374</v>
+        <v>1.968160455320113</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7798389562160719</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.255544208975271</v>
+        <v>4.294394358150528</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.499788543472889</v>
+        <v>-4.593896885961041</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.027062047097738</v>
+        <v>1.989418710102477</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7150887075906422</v>
+        <v>0.7798389562160719</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.256387113355027</v>
+        <v>4.295237262530284</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.458649248606259</v>
+        <v>-4.55275759109441</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.062555863918536</v>
+        <v>2.024912526923275</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7562280024572731</v>
+        <v>0.8209782510827027</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.30010878914915</v>
+        <v>4.338958938324408</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.362014336587619</v>
+        <v>-4.45612267907577</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.917393824849926</v>
+        <v>1.879750487854666</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.852862914475913</v>
+        <v>0.9176131631013427</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.174273732484269</v>
+        <v>4.213123881659527</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.492595071118461</v>
+        <v>-4.586703413606613</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.868663575111553</v>
+        <v>1.831020238116293</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7222821799450705</v>
+        <v>0.7870324285705002</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.099427335839728</v>
+        <v>4.138277485014985</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833461</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.328098736927499</v>
+        <v>-4.422207079415651</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.918888927864021</v>
+        <v>1.88124559086876</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.951528762761462</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.182551955430387</v>
+        <v>4.221402104605645</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.251000135385627</v>
+        <v>-4.345108477873779</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.9489160789172</v>
+        <v>1.911272741921939</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8867785141360324</v>
+        <v>0.951528762761462</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.181739665866817</v>
+        <v>4.220589815042075</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.261385330275516</v>
+        <v>-4.355493672763668</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.954630780086316</v>
+        <v>1.916987443091055</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8763933192461431</v>
+        <v>0.9411435678715727</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.185377328057956</v>
+        <v>4.224227477233214</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.279973488997741</v>
+        <v>-4.374081831485893</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.018032522373852</v>
+        <v>1.98038918537859</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8578051605239176</v>
+        <v>0.9225554091493473</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.245061438601046</v>
+        <v>4.283911587776304</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.280272035693777</v>
+        <v>-4.374380378181929</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.014782114513736</v>
+        <v>1.977138777518475</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8575066138278817</v>
+        <v>0.9222568624533114</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.241751321401723</v>
+        <v>4.280601470576981</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.179448902003349</v>
+        <v>-4.273557244491501</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.059642262929298</v>
+        <v>2.021998925934037</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8699708293122356</v>
+        <v>0.9347210779376652</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.253760745631727</v>
+        <v>4.292610894806984</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.988667541250942</v>
+        <v>-4.082775883739094</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.136084060708804</v>
+        <v>2.098440723713543</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.060752190064643</v>
+        <v>1.125502438690073</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.368358815561714</v>
+        <v>4.407208964736972</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.88170418340152</v>
+        <v>-3.975812525889673</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.15870624958617</v>
+        <v>2.121062912590908</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.119216798024445</v>
+        <v>1.183967046649874</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.383274426075191</v>
+        <v>4.422124575250449</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.826373595499758</v>
+        <v>-3.920481937987911</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.215805421358933</v>
+        <v>2.178162084363672</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.174547385926207</v>
+        <v>1.239297634551636</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.451439715428307</v>
+        <v>4.490289864603565</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.814319468586795</v>
+        <v>-3.908427811074948</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.214313640025556</v>
+        <v>2.176670303030295</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.186601512839169</v>
+        <v>1.251351761464599</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.452358759477523</v>
+        <v>4.491208908652781</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.855474588155016</v>
+        <v>-3.949582930643169</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.199732222382403</v>
+        <v>2.162088885387142</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.145446393270948</v>
+        <v>1.210196641896378</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.429546317920726</v>
+        <v>4.468396467095983</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.787426025463486</v>
+        <v>-3.881534367951639</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.239802673336897</v>
+        <v>2.202159336341636</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.213494955962478</v>
+        <v>1.278245204587908</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.483226481413526</v>
+        <v>4.522076630588784</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.019026418632987</v>
+        <v>-4.11313476112114</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.167365186242691</v>
+        <v>2.12972184924743</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.213494955962478</v>
+        <v>1.278245204587908</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.50342915158712</v>
+        <v>4.542279300762378</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.069077964162206</v>
+        <v>-4.16318630665036</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.130950804097886</v>
+        <v>2.093307467102624</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.213494955962478</v>
+        <v>1.278245204587908</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.487035387654003</v>
+        <v>4.525885536829261</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.244184796738651</v>
+        <v>-4.338293139226804</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.021159984660774</v>
+        <v>1.983516647665513</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.213494955962478</v>
+        <v>1.278245204587908</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.447287301247469</v>
+        <v>4.486137450422727</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.048084643308128</v>
+        <v>-4.142192985796282</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.106622665029923</v>
+        <v>2.068979328034662</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.409595109393001</v>
+        <v>1.474345358018431</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.571970012302723</v>
+        <v>4.610820161477981</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.895059251194844</v>
+        <v>-3.989167593682998</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.267003821448141</v>
+        <v>2.22936048445288</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.562620501506285</v>
+        <v>1.627370750131715</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.762956247143598</v>
+        <v>4.801806396318856</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.884502794861214</v>
+        <v>-4.017474907556267</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.458692628889886</v>
+        <v>2.405503783811865</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.562620501506285</v>
+        <v>1.627370750131715</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.950422472051891</v>
+        <v>4.989272621227149</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.051096019974736</v>
+        <v>-4.18406813266979</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.36145829019856</v>
+        <v>2.308269445120538</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.396027276392763</v>
+        <v>1.460777525018192</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.81986948833786</v>
+        <v>4.858719637513117</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.02806022661317</v>
+        <v>-4.161032339308224</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.374349010204904</v>
+        <v>2.321160165126882</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.396027276392763</v>
+        <v>1.460777525018192</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.823545890999577</v>
+        <v>4.862396040174835</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.998814246157474</v>
+        <v>-4.131786358852527</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.383665457510677</v>
+        <v>2.330476612432656</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.396027276392763</v>
+        <v>1.460777525018192</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.821163946123072</v>
+        <v>4.86001409529833</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.105739794035325</v>
+        <v>-4.238711906730378</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.338188477517172</v>
+        <v>2.284999632439151</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.289101728514912</v>
+        <v>1.353851977140341</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.754301856553997</v>
+        <v>4.793152005729254</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.250758352542574</v>
+        <v>-4.383730465237627</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.281609856257507</v>
+        <v>2.228421011179486</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.144083170007663</v>
+        <v>1.208833418633093</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.668719523592881</v>
+        <v>4.707569672768139</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687017</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.369100118327292</v>
+        <v>-4.502072231022344</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.334204389201373</v>
+        <v>2.281015544123352</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.154769208570553</v>
+        <v>1.219519457195983</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.775062385988369</v>
+        <v>4.813912535163626</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790807</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.420510540647999</v>
+        <v>-4.553482653343052</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.311425917399028</v>
+        <v>2.258237072321007</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.154769208570553</v>
+        <v>1.219519457195983</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.772848083114307</v>
+        <v>4.811698232289565</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.499929991855751</v>
+        <v>-4.632902104550804</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.279561264990217</v>
+        <v>2.226372419912196</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.154769208570553</v>
+        <v>1.219519457195983</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.772751211188597</v>
+        <v>4.811601360363855</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298402</v>
+        <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.595392989772969</v>
+        <v>-4.728365102468022</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.241369959381373</v>
+        <v>2.188181114303352</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.154769208570553</v>
+        <v>1.219519457195983</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.77274510474664</v>
+        <v>4.811595253921898</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218005</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.531017078922254</v>
+        <v>-4.663989191617307</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.26521672028427</v>
+        <v>2.212027875206249</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.219145119421268</v>
+        <v>1.283895368046698</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.80946704781968</v>
+        <v>4.848317196994937</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.586386241054448</v>
+        <v>-4.719358353749501</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.248802873179119</v>
+        <v>2.195614028101098</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.219145119421268</v>
+        <v>1.283895368046698</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.815200865567407</v>
+        <v>4.854051014742664</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113284</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.631824020885275</v>
+        <v>-4.764796133580328</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.23016612458972</v>
+        <v>2.176977279511699</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.176300128743109</v>
+        <v>1.241050377368538</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.789032234503443</v>
+        <v>4.827882383678701</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.543617186737697</v>
+        <v>-4.67658929943275</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.28532325109907</v>
+        <v>2.23213440602105</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.176300128743109</v>
+        <v>1.241050377368538</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.808906627353762</v>
+        <v>4.84775677652902</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.437582191532387</v>
+        <v>-4.57055430422744</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.311437949705923</v>
+        <v>2.258249104627901</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.176300128743109</v>
+        <v>1.241050377368538</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.79260732787849</v>
+        <v>4.831457477053748</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.254370528399292</v>
+        <v>-4.387342641094345</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.387153564423206</v>
+        <v>2.333964719345185</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.176300128743109</v>
+        <v>1.241050377368538</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.795038277342536</v>
+        <v>4.833888426517793</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.182649081385441</v>
+        <v>-4.315621194080494</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.381633329076636</v>
+        <v>2.328444483998615</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.248021575756959</v>
+        <v>1.312771824382389</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.803862331398736</v>
+        <v>4.842712480573993</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.160276055777735</v>
+        <v>-4.293248168472788</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.33749828524089</v>
+        <v>2.284309440162868</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.259277326869861</v>
+        <v>1.324027575495291</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.757531527987648</v>
+        <v>4.796381677162906</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456734</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.19329235168848</v>
+        <v>-4.326264464383533</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.509489971761948</v>
+        <v>2.456301126683926</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.189839950203109</v>
+        <v>1.254590198828539</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.901067306872952</v>
+        <v>4.93991745604821</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883681</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.181764716038871</v>
+        <v>-4.314736828733924</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.50602225185004</v>
+        <v>2.452833406772019</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.248840608404472</v>
+        <v>1.313590857029902</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.928388927622019</v>
+        <v>4.967239076797277</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.27910621738124</v>
+        <v>-4.412078330076293</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.470753763834881</v>
+        <v>2.41756491875686</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.204420426238983</v>
+        <v>1.269170674864413</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.905404930844514</v>
+        <v>4.944255080019772</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427689</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.364962246721206</v>
+        <v>-4.497934359416259</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.437662434291733</v>
+        <v>2.384473589213711</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.162044357012848</v>
+        <v>1.226794605638278</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.881230371501672</v>
+        <v>4.92008052067693</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.373799044137326</v>
+        <v>-4.506771156832379</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.416546917145786</v>
+        <v>2.363358072067765</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.154602184371498</v>
+        <v>1.219352432996927</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.859184269737363</v>
+        <v>4.898034418912621</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.465181606702784</v>
+        <v>-4.598153719397837</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.390158403164652</v>
+        <v>2.336969558086631</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.063219621806039</v>
+        <v>1.127969870431469</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.814519243243137</v>
+        <v>4.853369392418395</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889196</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.453474888715778</v>
+        <v>-4.586447001410831</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.496969348183723</v>
+        <v>2.443780503105702</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.074926339793046</v>
+        <v>1.139676588418475</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.923671531859609</v>
+        <v>4.962521681034867</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.353811384632116</v>
+        <v>-4.486783497327169</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.539867088548593</v>
+        <v>2.486678243470572</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.138113422996732</v>
+        <v>1.202863671622162</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.964616120513226</v>
+        <v>5.003466269688484</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.364127482798468</v>
+        <v>-4.497099595493521</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.74864548256011</v>
+        <v>2.695456637482089</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.138113422996732</v>
+        <v>1.202863671622162</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.177520953791285</v>
+        <v>5.216371102966542</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.364033514781095</v>
+        <v>-4.497005627476148</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.747861736679149</v>
+        <v>2.694672891601128</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.13848328434405</v>
+        <v>1.20323353296948</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.176921537511765</v>
+        <v>5.215771686687022</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988024</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.371252338980939</v>
+        <v>-4.504224451675992</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.739206192943565</v>
+        <v>2.686017347865544</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.13848328434405</v>
+        <v>1.20323353296948</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.171153523456119</v>
+        <v>5.210003672631377</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.370303915862901</v>
+        <v>-4.503276028557954</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.739585562190781</v>
+        <v>2.68639671711276</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.13848328434405</v>
+        <v>1.20323353296948</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.171153523456119</v>
+        <v>5.210003672631377</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.527372374118524</v>
+        <v>-4.660344486813578</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.689485786869623</v>
+        <v>2.636296941791602</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.13848328434405</v>
+        <v>1.20323353296948</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.183881131437211</v>
+        <v>5.222731280612468</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.521380127329713</v>
+        <v>-4.654352240024767</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.693828684009536</v>
+        <v>2.640639838931514</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.13848328434405</v>
+        <v>1.20323353296948</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.185827129861599</v>
+        <v>5.224677279036856</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.432822166198945</v>
+        <v>-4.584936010150683</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.722906004479611</v>
+        <v>2.662060466898916</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.13848328434405</v>
+        <v>1.20323353296948</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.179481265879367</v>
+        <v>5.218331415054625</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.905666596381566</v>
+        <v>3.876081000789533</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.555897324350735</v>
+        <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.476266843155955</v>
+        <v>-4.573592286942374</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.765034162774605</v>
+        <v>2.665906633621235</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.13848328434405</v>
+        <v>1.283389694146453</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.238987294957165</v>
+        <v>5.265733789199805</v>
       </c>
     </row>
   </sheetData>
